--- a/Master list - Ministries and Departments.xlsx
+++ b/Master list - Ministries and Departments.xlsx
@@ -17,10 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="dd-mm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -432,49 +431,49 @@
           <t>Organisation Type</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>J</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>K</t>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Selected Vacancy URL</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Deputation Vacancy URL</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Deputation Page (Same / Separate)</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Deputation Vacancies Available (Yes/No)</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Confidence Level</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Last Verified Date</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Dedicated Recruitment Portal (Yes/No)</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Source Type</t>
         </is>
       </c>
     </row>

--- a/Master list - Ministries and Departments.xlsx
+++ b/Master list - Ministries and Departments.xlsx
@@ -433,7 +433,7 @@
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>Selected Vacancy URL</t>
+          <t>Vacancy / Recruitment Advertisement Page URL</t>
         </is>
       </c>
       <c r="F1" s="4" t="inlineStr">
@@ -443,7 +443,7 @@
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
-          <t>Deputation Page (Same / Separate)</t>
+          <t>Deputation Page Same as Vacancy Page</t>
         </is>
       </c>
       <c r="H1" s="4" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H3" s="11" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="G4" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H4" s="11" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" s="11" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="G7" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H7" s="11" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="G8" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="G9" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G10" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="G13" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="G14" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="G15" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G16" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="G17" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="G18" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H18" s="11" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="G19" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="G20" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H20" s="11" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="G21" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H21" s="11" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G22" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="G23" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H23" s="11" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="G24" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H24" s="11" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="G25" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="G27" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G28" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H28" s="11" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="G29" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="G30" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="G31" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="G32" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H32" s="11" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="G33" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="G34" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H34" s="11" t="inlineStr">
@@ -18176,7 +18176,7 @@
       </c>
       <c r="G553" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H553" s="11" t="inlineStr">
@@ -18240,7 +18240,7 @@
       </c>
       <c r="G554" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H554" s="11" t="inlineStr">
@@ -18304,7 +18304,7 @@
       </c>
       <c r="G555" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H555" s="11" t="inlineStr">
@@ -18368,7 +18368,7 @@
       </c>
       <c r="G556" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H556" s="11" t="inlineStr">
@@ -18432,7 +18432,7 @@
       </c>
       <c r="G557" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H557" s="11" t="inlineStr">
@@ -18496,7 +18496,7 @@
       </c>
       <c r="G558" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H558" s="11" t="inlineStr">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="G559" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H559" s="11" t="inlineStr">
@@ -18624,7 +18624,7 @@
       </c>
       <c r="G560" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H560" s="11" t="inlineStr">
@@ -18688,7 +18688,7 @@
       </c>
       <c r="G561" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H561" s="11" t="inlineStr">
@@ -18752,7 +18752,7 @@
       </c>
       <c r="G562" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H562" s="11" t="inlineStr">
@@ -18846,7 +18846,7 @@
       </c>
       <c r="G564" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H564" s="11" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="G565" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H565" s="11" t="inlineStr">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="G566" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H566" s="11" t="inlineStr">
@@ -19038,7 +19038,7 @@
       </c>
       <c r="G567" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H567" s="11" t="inlineStr">
@@ -19102,7 +19102,7 @@
       </c>
       <c r="G568" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H568" s="11" t="inlineStr">
@@ -19166,7 +19166,7 @@
       </c>
       <c r="G569" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H569" s="11" t="inlineStr">
@@ -19230,7 +19230,7 @@
       </c>
       <c r="G570" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H570" s="11" t="inlineStr">
@@ -19294,7 +19294,7 @@
       </c>
       <c r="G571" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H571" s="11" t="inlineStr">
@@ -19358,7 +19358,7 @@
       </c>
       <c r="G572" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H572" s="11" t="inlineStr">
@@ -19422,7 +19422,7 @@
       </c>
       <c r="G573" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H573" s="11" t="inlineStr">
@@ -19486,7 +19486,7 @@
       </c>
       <c r="G574" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H574" s="11" t="inlineStr">
@@ -19550,7 +19550,7 @@
       </c>
       <c r="G575" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H575" s="11" t="inlineStr">
@@ -19644,7 +19644,7 @@
       </c>
       <c r="G577" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H577" s="11" t="inlineStr">
@@ -19708,7 +19708,7 @@
       </c>
       <c r="G578" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H578" s="11" t="inlineStr">
@@ -19772,7 +19772,7 @@
       </c>
       <c r="G579" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H579" s="11" t="inlineStr">
@@ -19836,7 +19836,7 @@
       </c>
       <c r="G580" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H580" s="11" t="inlineStr">
@@ -19900,7 +19900,7 @@
       </c>
       <c r="G581" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H581" s="11" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="G582" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H582" s="11" t="inlineStr">
@@ -20028,7 +20028,7 @@
       </c>
       <c r="G583" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H583" s="11" t="inlineStr">
@@ -20092,7 +20092,7 @@
       </c>
       <c r="G584" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H584" s="11" t="inlineStr">
@@ -20156,7 +20156,7 @@
       </c>
       <c r="G585" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H585" s="11" t="inlineStr">
@@ -20220,7 +20220,7 @@
       </c>
       <c r="G586" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H586" s="11" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="G588" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H588" s="11" t="inlineStr">
@@ -20378,7 +20378,7 @@
       </c>
       <c r="G589" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H589" s="11" t="inlineStr">
@@ -20442,7 +20442,7 @@
       </c>
       <c r="G590" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H590" s="11" t="inlineStr">
@@ -20506,7 +20506,7 @@
       </c>
       <c r="G591" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H591" s="11" t="inlineStr">
@@ -20570,7 +20570,7 @@
       </c>
       <c r="G592" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H592" s="11" t="inlineStr">
@@ -20634,7 +20634,7 @@
       </c>
       <c r="G593" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H593" s="11" t="inlineStr">
@@ -20698,7 +20698,7 @@
       </c>
       <c r="G594" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H594" s="11" t="inlineStr">
@@ -20762,7 +20762,7 @@
       </c>
       <c r="G595" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H595" s="11" t="inlineStr">
@@ -20856,7 +20856,7 @@
       </c>
       <c r="G597" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H597" s="11" t="inlineStr">
@@ -20920,7 +20920,7 @@
       </c>
       <c r="G598" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H598" s="11" t="inlineStr">
@@ -20984,7 +20984,7 @@
       </c>
       <c r="G599" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H599" s="11" t="inlineStr">
@@ -21048,7 +21048,7 @@
       </c>
       <c r="G600" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H600" s="11" t="inlineStr">
@@ -21112,7 +21112,7 @@
       </c>
       <c r="G601" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H601" s="11" t="inlineStr">
@@ -21176,7 +21176,7 @@
       </c>
       <c r="G602" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H602" s="11" t="inlineStr">
@@ -21270,7 +21270,7 @@
       </c>
       <c r="G604" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H604" s="11" t="inlineStr">
@@ -21334,7 +21334,7 @@
       </c>
       <c r="G605" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H605" s="11" t="inlineStr">
@@ -21398,7 +21398,7 @@
       </c>
       <c r="G606" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H606" s="11" t="inlineStr">
@@ -21462,7 +21462,7 @@
       </c>
       <c r="G607" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H607" s="11" t="inlineStr">
@@ -21526,7 +21526,7 @@
       </c>
       <c r="G608" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H608" s="11" t="inlineStr">
@@ -21590,7 +21590,7 @@
       </c>
       <c r="G609" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H609" s="11" t="inlineStr">
@@ -21654,7 +21654,7 @@
       </c>
       <c r="G610" s="11" t="inlineStr">
         <is>
-          <t>Same Page</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H610" s="11" t="inlineStr">

--- a/Master list - Ministries and Departments.xlsx
+++ b/Master list - Ministries and Departments.xlsx
@@ -398,7 +398,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X610"/>
+  <dimension ref="A1:V610"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="7.5" customWidth="1" style="16" min="1" max="1"/>
@@ -448,30 +448,20 @@
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
-          <t>Deputation Vacancies Available (Yes/No)</t>
+          <t>Confidence Level</t>
         </is>
       </c>
       <c r="I1" s="4" t="inlineStr">
         <is>
-          <t>Confidence Level</t>
+          <t>Remarks</t>
         </is>
       </c>
       <c r="J1" s="4" t="inlineStr">
         <is>
-          <t>Remarks</t>
+          <t>Last Verified Date</t>
         </is>
       </c>
       <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>Last Verified Date</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
-        <is>
-          <t>Dedicated Recruitment Portal (Yes/No)</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Source Type</t>
         </is>
@@ -504,8 +494,6 @@
       <c r="I2" s="11" t="n"/>
       <c r="J2" s="11" t="n"/>
       <c r="K2" s="11" t="n"/>
-      <c r="L2" s="11" t="n"/>
-      <c r="M2" s="11" t="n"/>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="16">
       <c r="A3" s="4">
@@ -544,28 +532,18 @@
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I3" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J3" s="11" t="inlineStr">
-        <is>
           <t>Re-aligned: DAHD's own vacancy/recruitment advertisement page (was pointing to agriwelfare).</t>
         </is>
       </c>
-      <c r="K3" s="17" t="n">
+      <c r="J3" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L3" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M3" s="11" t="inlineStr">
+      <c r="K3" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -608,28 +586,18 @@
       </c>
       <c r="H4" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J4" s="11" t="inlineStr">
-        <is>
           <t>Re-aligned: Dept of Fisheries dedicated recruitment page.</t>
         </is>
       </c>
-      <c r="K4" s="17" t="n">
+      <c r="J4" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L4" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M4" s="11" t="inlineStr">
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -672,28 +640,18 @@
       </c>
       <c r="H5" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
           <t>DARE has no separate recruitment page; positions handled via ICAR vacancies.</t>
         </is>
       </c>
-      <c r="K5" s="17" t="n">
+      <c r="J5" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L5" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M5" s="11" t="inlineStr">
+      <c r="K5" s="11" t="inlineStr">
         <is>
           <t>Portal</t>
         </is>
@@ -736,28 +694,18 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
           <t>Re-aligned: ICAR official vacancies page.</t>
         </is>
       </c>
-      <c r="K6" s="17" t="n">
+      <c r="J6" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L6" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="K6" s="11" t="inlineStr">
         <is>
           <t>Portal</t>
         </is>
@@ -800,28 +748,18 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr">
-        <is>
           <t>Re-aligned: MANAGE (NIAEM) vacancies page.</t>
         </is>
       </c>
-      <c r="K7" s="17" t="n">
+      <c r="J7" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L7" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M7" s="11" t="inlineStr">
+      <c r="K7" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -864,28 +802,18 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
           <t>Re-aligned: NRAA recruitment page.</t>
         </is>
       </c>
-      <c r="K8" s="17" t="n">
+      <c r="J8" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M8" s="11" t="inlineStr">
+      <c r="K8" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -928,28 +856,18 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="inlineStr">
-        <is>
           <t>CIB&amp;RC functions under DPPQS; vacancy circulars on DPPQS employee corner.</t>
         </is>
       </c>
-      <c r="K9" s="17" t="n">
+      <c r="J9" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M9" s="11" t="inlineStr">
+      <c r="K9" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -992,28 +910,18 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
           <t>CFQC&amp;TI is under Dept of Agriculture &amp; Farmers Welfare; recruitment via parent department portal.</t>
         </is>
       </c>
-      <c r="K10" s="17" t="n">
+      <c r="J10" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -1044,10 +952,8 @@
       <c r="G11" s="11" t="n"/>
       <c r="H11" s="11" t="n"/>
       <c r="I11" s="11" t="n"/>
-      <c r="J11" s="11" t="n"/>
-      <c r="K11" s="7" t="n"/>
-      <c r="L11" s="11" t="n"/>
-      <c r="M11" s="11" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="K11" s="11" t="n"/>
     </row>
     <row r="12" ht="15.75" customHeight="1" s="16">
       <c r="A12" s="4">
@@ -1086,28 +992,18 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
           <t>Dedicated Ministry of AYUSH recruitment portal.</t>
         </is>
       </c>
-      <c r="K12" s="17" t="n">
+      <c r="J12" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M12" s="11" t="inlineStr">
+      <c r="K12" s="11" t="inlineStr">
         <is>
           <t>Portal</t>
         </is>
@@ -1150,28 +1046,18 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
           <t>AIIA posts recruitment notices on its official site; stable deep recruitment URL not confirmed.</t>
         </is>
       </c>
-      <c r="K13" s="17" t="n">
+      <c r="J13" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L13" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M13" s="11" t="inlineStr">
+      <c r="K13" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -1214,28 +1100,18 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
           <t>NIA Jaipur recruitment page.</t>
         </is>
       </c>
-      <c r="K14" s="17" t="n">
+      <c r="J14" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L14" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M14" s="11" t="inlineStr">
+      <c r="K14" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -1278,28 +1154,18 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
           <t>NIUM recruitment notices on official site; dedicated page not auto-confirmed.</t>
         </is>
       </c>
-      <c r="K15" s="17" t="n">
+      <c r="J15" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L15" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="K15" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -1342,28 +1208,18 @@
       </c>
       <c r="H16" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J16" s="11" t="inlineStr">
-        <is>
           <t>National Institute of Siddha recruitment page.</t>
         </is>
       </c>
-      <c r="K16" s="17" t="n">
+      <c r="J16" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M16" s="11" t="inlineStr">
+      <c r="K16" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -1406,28 +1262,18 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J17" s="11" t="inlineStr">
-        <is>
           <t>NIH Kolkata recruitment notices on official site; dedicated page not auto-confirmed.</t>
         </is>
       </c>
-      <c r="K17" s="17" t="n">
+      <c r="J17" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L17" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M17" s="11" t="inlineStr">
+      <c r="K17" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -1470,28 +1316,18 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J18" s="11" t="inlineStr">
-        <is>
           <t>CCRAS vacancies page.</t>
         </is>
       </c>
-      <c r="K18" s="17" t="n">
+      <c r="J18" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L18" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M18" s="11" t="inlineStr">
+      <c r="K18" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -1534,28 +1370,18 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="inlineStr">
-        <is>
           <t>CCRUM recruitment page.</t>
         </is>
       </c>
-      <c r="K19" s="17" t="n">
+      <c r="J19" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L19" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M19" s="11" t="inlineStr">
+      <c r="K19" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -1598,28 +1424,18 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J20" s="11" t="inlineStr">
-        <is>
           <t>Official CCRS domain; site not reachable for deep-link confirmation from here.</t>
         </is>
       </c>
-      <c r="K20" s="17" t="n">
+      <c r="J20" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L20" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M20" s="11" t="inlineStr">
+      <c r="K20" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -1662,28 +1478,18 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
           <t>Official CCRH domain; deep recruitment link not auto-confirmed.</t>
         </is>
       </c>
-      <c r="K21" s="17" t="n">
+      <c r="J21" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L21" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M21" s="11" t="inlineStr">
+      <c r="K21" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -1726,28 +1532,18 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J22" s="11" t="inlineStr">
-        <is>
           <t>Official CCRYN domain; deep recruitment link not auto-confirmed.</t>
         </is>
       </c>
-      <c r="K22" s="17" t="n">
+      <c r="J22" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L22" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M22" s="11" t="inlineStr">
+      <c r="K22" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -1790,28 +1586,18 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J23" s="11" t="inlineStr">
-        <is>
           <t>CCIM superseded by NCISM (National Commission for Indian System of Medicine); link points to NCISM.</t>
         </is>
       </c>
-      <c r="K23" s="17" t="n">
+      <c r="J23" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L23" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M23" s="11" t="inlineStr">
+      <c r="K23" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -1854,28 +1640,18 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J24" s="11" t="inlineStr">
-        <is>
           <t>CCH superseded by NCH (National Commission for Homoeopathy); recruitments page.</t>
         </is>
       </c>
-      <c r="K24" s="17" t="n">
+      <c r="J24" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L24" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M24" s="11" t="inlineStr">
+      <c r="K24" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -1918,28 +1694,18 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J25" s="11" t="inlineStr">
-        <is>
           <t>PCIM&amp;H official site; dedicated recruitment page not auto-confirmed.</t>
         </is>
       </c>
-      <c r="K25" s="17" t="n">
+      <c r="J25" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L25" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M25" s="11" t="inlineStr">
+      <c r="K25" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -1970,10 +1736,8 @@
       <c r="G26" s="11" t="n"/>
       <c r="H26" s="11" t="n"/>
       <c r="I26" s="11" t="n"/>
-      <c r="J26" s="11" t="n"/>
-      <c r="K26" s="7" t="n"/>
-      <c r="L26" s="11" t="n"/>
-      <c r="M26" s="11" t="n"/>
+      <c r="J26" s="7" t="n"/>
+      <c r="K26" s="11" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="16">
       <c r="A27" s="4">
@@ -2012,28 +1776,18 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J27" s="11" t="inlineStr">
-        <is>
           <t>Re-aligned: Dept of Chemicals &amp; Petrochemicals recruitments page.</t>
         </is>
       </c>
-      <c r="K27" s="17" t="n">
+      <c r="J27" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L27" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M27" s="11" t="inlineStr">
+      <c r="K27" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -2076,28 +1830,18 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J28" s="11" t="inlineStr">
-        <is>
           <t>Re-aligned: Dept of Fertilizers vacancies page.</t>
         </is>
       </c>
-      <c r="K28" s="17" t="n">
+      <c r="J28" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L28" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M28" s="11" t="inlineStr">
+      <c r="K28" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -2140,28 +1884,18 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J29" s="11" t="inlineStr">
-        <is>
           <t>Re-aligned: Dept of Pharmaceuticals recruitment page.</t>
         </is>
       </c>
-      <c r="K29" s="17" t="n">
+      <c r="J29" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L29" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M29" s="11" t="inlineStr">
+      <c r="K29" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -2204,28 +1938,18 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J30" s="11" t="inlineStr">
-        <is>
           <t>Re-aligned: CIPET job opportunities page.</t>
         </is>
       </c>
-      <c r="K30" s="17" t="n">
+      <c r="J30" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L30" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M30" s="11" t="inlineStr">
+      <c r="K30" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -2268,28 +1992,18 @@
       </c>
       <c r="H31" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J31" s="11" t="inlineStr">
-        <is>
           <t>CFQC&amp;TI under Dept of Fertilizers; recruitment via department vacancies page.</t>
         </is>
       </c>
-      <c r="K31" s="17" t="n">
+      <c r="J31" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L31" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M31" s="11" t="inlineStr">
+      <c r="K31" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -2332,28 +2046,18 @@
       </c>
       <c r="H32" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J32" s="11" t="inlineStr">
-        <is>
           <t>FQCLs under Dept of Fertilizers; recruitment via department vacancies page.</t>
         </is>
       </c>
-      <c r="K32" s="17" t="n">
+      <c r="J32" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L32" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M32" s="11" t="inlineStr">
+      <c r="K32" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -2396,28 +2100,18 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J33" s="11" t="inlineStr">
-        <is>
           <t>Pharmacy Council of India official site; deep recruitment link not auto-confirmed.</t>
         </is>
       </c>
-      <c r="K33" s="17" t="n">
+      <c r="J33" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L33" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M33" s="11" t="inlineStr">
+      <c r="K33" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -2460,28 +2154,18 @@
       </c>
       <c r="H34" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J34" s="11" t="inlineStr">
-        <is>
           <t>Re-aligned: NPPA recruitment page.</t>
         </is>
       </c>
-      <c r="K34" s="17" t="n">
+      <c r="J34" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L34" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M34" s="11" t="inlineStr">
+      <c r="K34" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -2514,8 +2198,6 @@
       <c r="I35" s="11" t="n"/>
       <c r="J35" s="11" t="n"/>
       <c r="K35" s="11" t="n"/>
-      <c r="L35" s="11" t="n"/>
-      <c r="M35" s="11" t="n"/>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="16">
       <c r="A36" s="4">
@@ -2544,8 +2226,6 @@
       <c r="I36" s="11" t="n"/>
       <c r="J36" s="11" t="n"/>
       <c r="K36" s="11" t="n"/>
-      <c r="L36" s="11" t="n"/>
-      <c r="M36" s="11" t="n"/>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="16">
       <c r="A37" s="4">
@@ -2574,8 +2254,6 @@
       <c r="I37" s="11" t="n"/>
       <c r="J37" s="11" t="n"/>
       <c r="K37" s="11" t="n"/>
-      <c r="L37" s="11" t="n"/>
-      <c r="M37" s="11" t="n"/>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="16">
       <c r="A38" s="4">
@@ -2604,8 +2282,6 @@
       <c r="I38" s="11" t="n"/>
       <c r="J38" s="11" t="n"/>
       <c r="K38" s="11" t="n"/>
-      <c r="L38" s="11" t="n"/>
-      <c r="M38" s="11" t="n"/>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="16">
       <c r="A39" s="4">
@@ -2634,8 +2310,6 @@
       <c r="I39" s="11" t="n"/>
       <c r="J39" s="11" t="n"/>
       <c r="K39" s="11" t="n"/>
-      <c r="L39" s="11" t="n"/>
-      <c r="M39" s="11" t="n"/>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="16">
       <c r="A40" s="4">
@@ -2664,8 +2338,6 @@
       <c r="I40" s="11" t="n"/>
       <c r="J40" s="11" t="n"/>
       <c r="K40" s="11" t="n"/>
-      <c r="L40" s="11" t="n"/>
-      <c r="M40" s="11" t="n"/>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="16">
       <c r="A41" s="4">
@@ -2694,8 +2366,6 @@
       <c r="I41" s="11" t="n"/>
       <c r="J41" s="11" t="n"/>
       <c r="K41" s="11" t="n"/>
-      <c r="L41" s="11" t="n"/>
-      <c r="M41" s="11" t="n"/>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="16">
       <c r="A42" s="4">
@@ -2724,8 +2394,6 @@
       <c r="I42" s="11" t="n"/>
       <c r="J42" s="11" t="n"/>
       <c r="K42" s="11" t="n"/>
-      <c r="L42" s="11" t="n"/>
-      <c r="M42" s="11" t="n"/>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="16">
       <c r="A43" s="4">
@@ -2754,8 +2422,6 @@
       <c r="I43" s="11" t="n"/>
       <c r="J43" s="11" t="n"/>
       <c r="K43" s="11" t="n"/>
-      <c r="L43" s="11" t="n"/>
-      <c r="M43" s="11" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="16">
       <c r="A44" s="4">
@@ -2784,8 +2450,6 @@
       <c r="I44" s="11" t="n"/>
       <c r="J44" s="11" t="n"/>
       <c r="K44" s="11" t="n"/>
-      <c r="L44" s="11" t="n"/>
-      <c r="M44" s="11" t="n"/>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="16">
       <c r="A45" s="4">
@@ -2814,8 +2478,6 @@
       <c r="I45" s="11" t="n"/>
       <c r="J45" s="11" t="n"/>
       <c r="K45" s="11" t="n"/>
-      <c r="L45" s="11" t="n"/>
-      <c r="M45" s="11" t="n"/>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="16">
       <c r="A46" s="4">
@@ -2844,8 +2506,6 @@
       <c r="I46" s="11" t="n"/>
       <c r="J46" s="11" t="n"/>
       <c r="K46" s="11" t="n"/>
-      <c r="L46" s="11" t="n"/>
-      <c r="M46" s="11" t="n"/>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="16">
       <c r="A47" s="4">
@@ -2874,8 +2534,6 @@
       <c r="I47" s="11" t="n"/>
       <c r="J47" s="11" t="n"/>
       <c r="K47" s="11" t="n"/>
-      <c r="L47" s="11" t="n"/>
-      <c r="M47" s="11" t="n"/>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="16">
       <c r="A48" s="4">
@@ -2904,8 +2562,6 @@
       <c r="I48" s="11" t="n"/>
       <c r="J48" s="11" t="n"/>
       <c r="K48" s="11" t="n"/>
-      <c r="L48" s="11" t="n"/>
-      <c r="M48" s="11" t="n"/>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="16">
       <c r="A49" s="4">
@@ -2934,8 +2590,6 @@
       <c r="I49" s="11" t="n"/>
       <c r="J49" s="11" t="n"/>
       <c r="K49" s="11" t="n"/>
-      <c r="L49" s="11" t="n"/>
-      <c r="M49" s="11" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="16">
       <c r="A50" s="4">
@@ -2964,8 +2618,6 @@
       <c r="I50" s="11" t="n"/>
       <c r="J50" s="11" t="n"/>
       <c r="K50" s="11" t="n"/>
-      <c r="L50" s="11" t="n"/>
-      <c r="M50" s="11" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="16">
       <c r="A51" s="4">
@@ -2994,8 +2646,6 @@
       <c r="I51" s="11" t="n"/>
       <c r="J51" s="11" t="n"/>
       <c r="K51" s="11" t="n"/>
-      <c r="L51" s="11" t="n"/>
-      <c r="M51" s="11" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="16">
       <c r="A52" s="4">
@@ -3024,8 +2674,6 @@
       <c r="I52" s="11" t="n"/>
       <c r="J52" s="11" t="n"/>
       <c r="K52" s="11" t="n"/>
-      <c r="L52" s="11" t="n"/>
-      <c r="M52" s="11" t="n"/>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="16">
       <c r="A53" s="4">
@@ -3054,8 +2702,6 @@
       <c r="I53" s="11" t="n"/>
       <c r="J53" s="11" t="n"/>
       <c r="K53" s="11" t="n"/>
-      <c r="L53" s="11" t="n"/>
-      <c r="M53" s="11" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="16">
       <c r="A54" s="4">
@@ -3084,8 +2730,6 @@
       <c r="I54" s="11" t="n"/>
       <c r="J54" s="11" t="n"/>
       <c r="K54" s="11" t="n"/>
-      <c r="L54" s="11" t="n"/>
-      <c r="M54" s="11" t="n"/>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="16">
       <c r="A55" s="4">
@@ -3114,8 +2758,6 @@
       <c r="I55" s="11" t="n"/>
       <c r="J55" s="11" t="n"/>
       <c r="K55" s="11" t="n"/>
-      <c r="L55" s="11" t="n"/>
-      <c r="M55" s="11" t="n"/>
     </row>
     <row r="56" ht="15.75" customHeight="1" s="16">
       <c r="A56" s="4">
@@ -3144,8 +2786,6 @@
       <c r="I56" s="11" t="n"/>
       <c r="J56" s="11" t="n"/>
       <c r="K56" s="11" t="n"/>
-      <c r="L56" s="11" t="n"/>
-      <c r="M56" s="11" t="n"/>
     </row>
     <row r="57" ht="15.75" customHeight="1" s="16">
       <c r="A57" s="4">
@@ -3174,8 +2814,6 @@
       <c r="I57" s="11" t="n"/>
       <c r="J57" s="11" t="n"/>
       <c r="K57" s="11" t="n"/>
-      <c r="L57" s="11" t="n"/>
-      <c r="M57" s="11" t="n"/>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="16">
       <c r="A58" s="4">
@@ -3204,8 +2842,6 @@
       <c r="I58" s="11" t="n"/>
       <c r="J58" s="11" t="n"/>
       <c r="K58" s="11" t="n"/>
-      <c r="L58" s="11" t="n"/>
-      <c r="M58" s="11" t="n"/>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="16">
       <c r="A59" s="4">
@@ -3234,8 +2870,6 @@
       <c r="I59" s="11" t="n"/>
       <c r="J59" s="11" t="n"/>
       <c r="K59" s="11" t="n"/>
-      <c r="L59" s="11" t="n"/>
-      <c r="M59" s="11" t="n"/>
     </row>
     <row r="60" ht="15.75" customHeight="1" s="16">
       <c r="A60" s="4">
@@ -3264,8 +2898,6 @@
       <c r="I60" s="11" t="n"/>
       <c r="J60" s="11" t="n"/>
       <c r="K60" s="11" t="n"/>
-      <c r="L60" s="11" t="n"/>
-      <c r="M60" s="11" t="n"/>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="16">
       <c r="A61" s="4">
@@ -3294,8 +2926,6 @@
       <c r="I61" s="11" t="n"/>
       <c r="J61" s="11" t="n"/>
       <c r="K61" s="11" t="n"/>
-      <c r="L61" s="11" t="n"/>
-      <c r="M61" s="11" t="n"/>
     </row>
     <row r="62" ht="15.75" customHeight="1" s="16">
       <c r="A62" s="4">
@@ -3324,8 +2954,6 @@
       <c r="I62" s="11" t="n"/>
       <c r="J62" s="11" t="n"/>
       <c r="K62" s="11" t="n"/>
-      <c r="L62" s="11" t="n"/>
-      <c r="M62" s="11" t="n"/>
     </row>
     <row r="63" ht="15.75" customHeight="1" s="16">
       <c r="A63" s="4">
@@ -3354,8 +2982,6 @@
       <c r="I63" s="11" t="n"/>
       <c r="J63" s="11" t="n"/>
       <c r="K63" s="11" t="n"/>
-      <c r="L63" s="11" t="n"/>
-      <c r="M63" s="11" t="n"/>
     </row>
     <row r="64" ht="15.75" customHeight="1" s="16">
       <c r="A64" s="4">
@@ -3384,8 +3010,6 @@
       <c r="I64" s="11" t="n"/>
       <c r="J64" s="11" t="n"/>
       <c r="K64" s="11" t="n"/>
-      <c r="L64" s="11" t="n"/>
-      <c r="M64" s="11" t="n"/>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="16">
       <c r="A65" s="4">
@@ -3414,8 +3038,6 @@
       <c r="I65" s="11" t="n"/>
       <c r="J65" s="11" t="n"/>
       <c r="K65" s="11" t="n"/>
-      <c r="L65" s="11" t="n"/>
-      <c r="M65" s="11" t="n"/>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="16">
       <c r="A66" s="4">
@@ -3444,8 +3066,6 @@
       <c r="I66" s="11" t="n"/>
       <c r="J66" s="11" t="n"/>
       <c r="K66" s="11" t="n"/>
-      <c r="L66" s="11" t="n"/>
-      <c r="M66" s="11" t="n"/>
     </row>
     <row r="67" ht="15.75" customHeight="1" s="16">
       <c r="A67" s="4">
@@ -3474,8 +3094,6 @@
       <c r="I67" s="11" t="n"/>
       <c r="J67" s="11" t="n"/>
       <c r="K67" s="11" t="n"/>
-      <c r="L67" s="11" t="n"/>
-      <c r="M67" s="11" t="n"/>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="16">
       <c r="A68" s="4">
@@ -3504,8 +3122,6 @@
       <c r="I68" s="11" t="n"/>
       <c r="J68" s="11" t="n"/>
       <c r="K68" s="11" t="n"/>
-      <c r="L68" s="11" t="n"/>
-      <c r="M68" s="11" t="n"/>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="16">
       <c r="A69" s="4">
@@ -3534,8 +3150,6 @@
       <c r="I69" s="11" t="n"/>
       <c r="J69" s="11" t="n"/>
       <c r="K69" s="11" t="n"/>
-      <c r="L69" s="11" t="n"/>
-      <c r="M69" s="11" t="n"/>
     </row>
     <row r="70" ht="15.75" customHeight="1" s="16">
       <c r="A70" s="4">
@@ -3564,8 +3178,6 @@
       <c r="I70" s="11" t="n"/>
       <c r="J70" s="11" t="n"/>
       <c r="K70" s="11" t="n"/>
-      <c r="L70" s="11" t="n"/>
-      <c r="M70" s="11" t="n"/>
     </row>
     <row r="71" ht="15.75" customHeight="1" s="16">
       <c r="A71" s="4">
@@ -3594,8 +3206,6 @@
       <c r="I71" s="11" t="n"/>
       <c r="J71" s="11" t="n"/>
       <c r="K71" s="11" t="n"/>
-      <c r="L71" s="11" t="n"/>
-      <c r="M71" s="11" t="n"/>
     </row>
     <row r="72" ht="15.75" customHeight="1" s="16">
       <c r="A72" s="4">
@@ -3624,8 +3234,6 @@
       <c r="I72" s="11" t="n"/>
       <c r="J72" s="11" t="n"/>
       <c r="K72" s="11" t="n"/>
-      <c r="L72" s="11" t="n"/>
-      <c r="M72" s="11" t="n"/>
     </row>
     <row r="73" ht="15.75" customHeight="1" s="16">
       <c r="A73" s="4">
@@ -3654,8 +3262,6 @@
       <c r="I73" s="11" t="n"/>
       <c r="J73" s="11" t="n"/>
       <c r="K73" s="11" t="n"/>
-      <c r="L73" s="11" t="n"/>
-      <c r="M73" s="11" t="n"/>
     </row>
     <row r="74" ht="15.75" customHeight="1" s="16">
       <c r="A74" s="4">
@@ -3684,8 +3290,6 @@
       <c r="I74" s="11" t="n"/>
       <c r="J74" s="11" t="n"/>
       <c r="K74" s="11" t="n"/>
-      <c r="L74" s="11" t="n"/>
-      <c r="M74" s="11" t="n"/>
     </row>
     <row r="75" ht="15.75" customHeight="1" s="16">
       <c r="A75" s="4">
@@ -3714,8 +3318,6 @@
       <c r="I75" s="11" t="n"/>
       <c r="J75" s="11" t="n"/>
       <c r="K75" s="11" t="n"/>
-      <c r="L75" s="11" t="n"/>
-      <c r="M75" s="11" t="n"/>
     </row>
     <row r="76" ht="15.75" customHeight="1" s="16">
       <c r="A76" s="4">
@@ -3744,8 +3346,6 @@
       <c r="I76" s="11" t="n"/>
       <c r="J76" s="11" t="n"/>
       <c r="K76" s="11" t="n"/>
-      <c r="L76" s="11" t="n"/>
-      <c r="M76" s="11" t="n"/>
     </row>
     <row r="77" ht="15.75" customHeight="1" s="16">
       <c r="A77" s="4">
@@ -3774,8 +3374,6 @@
       <c r="I77" s="11" t="n"/>
       <c r="J77" s="11" t="n"/>
       <c r="K77" s="11" t="n"/>
-      <c r="L77" s="11" t="n"/>
-      <c r="M77" s="11" t="n"/>
     </row>
     <row r="78" ht="15.75" customHeight="1" s="16">
       <c r="A78" s="4">
@@ -3804,8 +3402,6 @@
       <c r="I78" s="11" t="n"/>
       <c r="J78" s="11" t="n"/>
       <c r="K78" s="11" t="n"/>
-      <c r="L78" s="11" t="n"/>
-      <c r="M78" s="11" t="n"/>
     </row>
     <row r="79" ht="15.75" customHeight="1" s="16">
       <c r="A79" s="4">
@@ -3834,8 +3430,6 @@
       <c r="I79" s="11" t="n"/>
       <c r="J79" s="11" t="n"/>
       <c r="K79" s="11" t="n"/>
-      <c r="L79" s="11" t="n"/>
-      <c r="M79" s="11" t="n"/>
     </row>
     <row r="80" ht="15.75" customHeight="1" s="16">
       <c r="A80" s="4">
@@ -3864,8 +3458,6 @@
       <c r="I80" s="11" t="n"/>
       <c r="J80" s="11" t="n"/>
       <c r="K80" s="11" t="n"/>
-      <c r="L80" s="11" t="n"/>
-      <c r="M80" s="11" t="n"/>
     </row>
     <row r="81" ht="15.75" customHeight="1" s="16">
       <c r="A81" s="4">
@@ -3894,8 +3486,6 @@
       <c r="I81" s="11" t="n"/>
       <c r="J81" s="11" t="n"/>
       <c r="K81" s="11" t="n"/>
-      <c r="L81" s="11" t="n"/>
-      <c r="M81" s="11" t="n"/>
     </row>
     <row r="82" ht="15.75" customHeight="1" s="16">
       <c r="A82" s="4">
@@ -3924,8 +3514,6 @@
       <c r="I82" s="11" t="n"/>
       <c r="J82" s="11" t="n"/>
       <c r="K82" s="11" t="n"/>
-      <c r="L82" s="11" t="n"/>
-      <c r="M82" s="11" t="n"/>
     </row>
     <row r="83" ht="15.75" customHeight="1" s="16">
       <c r="A83" s="4">
@@ -3954,8 +3542,6 @@
       <c r="I83" s="11" t="n"/>
       <c r="J83" s="11" t="n"/>
       <c r="K83" s="11" t="n"/>
-      <c r="L83" s="11" t="n"/>
-      <c r="M83" s="11" t="n"/>
     </row>
     <row r="84" ht="15.75" customHeight="1" s="16">
       <c r="A84" s="4">
@@ -3984,8 +3570,6 @@
       <c r="I84" s="11" t="n"/>
       <c r="J84" s="11" t="n"/>
       <c r="K84" s="11" t="n"/>
-      <c r="L84" s="11" t="n"/>
-      <c r="M84" s="11" t="n"/>
     </row>
     <row r="85" ht="15.75" customHeight="1" s="16">
       <c r="A85" s="4">
@@ -4014,8 +3598,6 @@
       <c r="I85" s="11" t="n"/>
       <c r="J85" s="11" t="n"/>
       <c r="K85" s="11" t="n"/>
-      <c r="L85" s="11" t="n"/>
-      <c r="M85" s="11" t="n"/>
     </row>
     <row r="86" ht="15.75" customHeight="1" s="16">
       <c r="A86" s="4">
@@ -4044,8 +3626,6 @@
       <c r="I86" s="11" t="n"/>
       <c r="J86" s="11" t="n"/>
       <c r="K86" s="11" t="n"/>
-      <c r="L86" s="11" t="n"/>
-      <c r="M86" s="11" t="n"/>
     </row>
     <row r="87" ht="15.75" customHeight="1" s="16">
       <c r="A87" s="4">
@@ -4074,8 +3654,6 @@
       <c r="I87" s="11" t="n"/>
       <c r="J87" s="11" t="n"/>
       <c r="K87" s="11" t="n"/>
-      <c r="L87" s="11" t="n"/>
-      <c r="M87" s="11" t="n"/>
     </row>
     <row r="88" ht="15.75" customHeight="1" s="16">
       <c r="A88" s="4">
@@ -4104,8 +3682,6 @@
       <c r="I88" s="11" t="n"/>
       <c r="J88" s="11" t="n"/>
       <c r="K88" s="11" t="n"/>
-      <c r="L88" s="11" t="n"/>
-      <c r="M88" s="11" t="n"/>
     </row>
     <row r="89" ht="15.75" customHeight="1" s="16">
       <c r="A89" s="4">
@@ -4134,8 +3710,6 @@
       <c r="I89" s="11" t="n"/>
       <c r="J89" s="11" t="n"/>
       <c r="K89" s="11" t="n"/>
-      <c r="L89" s="11" t="n"/>
-      <c r="M89" s="11" t="n"/>
     </row>
     <row r="90" ht="15.75" customHeight="1" s="16">
       <c r="A90" s="4">
@@ -4164,8 +3738,6 @@
       <c r="I90" s="11" t="n"/>
       <c r="J90" s="11" t="n"/>
       <c r="K90" s="11" t="n"/>
-      <c r="L90" s="11" t="n"/>
-      <c r="M90" s="11" t="n"/>
     </row>
     <row r="91" ht="15.75" customHeight="1" s="16">
       <c r="A91" s="4">
@@ -4194,8 +3766,6 @@
       <c r="I91" s="11" t="n"/>
       <c r="J91" s="11" t="n"/>
       <c r="K91" s="11" t="n"/>
-      <c r="L91" s="11" t="n"/>
-      <c r="M91" s="11" t="n"/>
     </row>
     <row r="92" ht="15.75" customHeight="1" s="16">
       <c r="A92" s="4">
@@ -4224,8 +3794,6 @@
       <c r="I92" s="11" t="n"/>
       <c r="J92" s="11" t="n"/>
       <c r="K92" s="11" t="n"/>
-      <c r="L92" s="11" t="n"/>
-      <c r="M92" s="11" t="n"/>
     </row>
     <row r="93" ht="15.75" customHeight="1" s="16">
       <c r="A93" s="4">
@@ -4254,8 +3822,6 @@
       <c r="I93" s="11" t="n"/>
       <c r="J93" s="11" t="n"/>
       <c r="K93" s="11" t="n"/>
-      <c r="L93" s="11" t="n"/>
-      <c r="M93" s="11" t="n"/>
     </row>
     <row r="94" ht="15.75" customHeight="1" s="16">
       <c r="A94" s="4">
@@ -4284,8 +3850,6 @@
       <c r="I94" s="11" t="n"/>
       <c r="J94" s="11" t="n"/>
       <c r="K94" s="11" t="n"/>
-      <c r="L94" s="11" t="n"/>
-      <c r="M94" s="11" t="n"/>
     </row>
     <row r="95" ht="15.75" customHeight="1" s="16">
       <c r="A95" s="4">
@@ -4314,8 +3878,6 @@
       <c r="I95" s="11" t="n"/>
       <c r="J95" s="11" t="n"/>
       <c r="K95" s="11" t="n"/>
-      <c r="L95" s="11" t="n"/>
-      <c r="M95" s="11" t="n"/>
     </row>
     <row r="96" ht="15.75" customHeight="1" s="16">
       <c r="A96" s="4">
@@ -4344,8 +3906,6 @@
       <c r="I96" s="11" t="n"/>
       <c r="J96" s="11" t="n"/>
       <c r="K96" s="11" t="n"/>
-      <c r="L96" s="11" t="n"/>
-      <c r="M96" s="11" t="n"/>
     </row>
     <row r="97" ht="15.75" customHeight="1" s="16">
       <c r="A97" s="4">
@@ -4374,8 +3934,6 @@
       <c r="I97" s="11" t="n"/>
       <c r="J97" s="11" t="n"/>
       <c r="K97" s="11" t="n"/>
-      <c r="L97" s="11" t="n"/>
-      <c r="M97" s="11" t="n"/>
     </row>
     <row r="98" ht="15.75" customHeight="1" s="16">
       <c r="A98" s="4">
@@ -4404,8 +3962,6 @@
       <c r="I98" s="11" t="n"/>
       <c r="J98" s="11" t="n"/>
       <c r="K98" s="11" t="n"/>
-      <c r="L98" s="11" t="n"/>
-      <c r="M98" s="11" t="n"/>
     </row>
     <row r="99" ht="15.75" customHeight="1" s="16">
       <c r="A99" s="4">
@@ -4434,8 +3990,6 @@
       <c r="I99" s="11" t="n"/>
       <c r="J99" s="11" t="n"/>
       <c r="K99" s="11" t="n"/>
-      <c r="L99" s="11" t="n"/>
-      <c r="M99" s="11" t="n"/>
     </row>
     <row r="100" ht="15.75" customHeight="1" s="16">
       <c r="A100" s="4">
@@ -4464,8 +4018,6 @@
       <c r="I100" s="11" t="n"/>
       <c r="J100" s="11" t="n"/>
       <c r="K100" s="11" t="n"/>
-      <c r="L100" s="11" t="n"/>
-      <c r="M100" s="11" t="n"/>
     </row>
     <row r="101" ht="15.75" customHeight="1" s="16">
       <c r="A101" s="4">
@@ -4494,8 +4046,6 @@
       <c r="I101" s="11" t="n"/>
       <c r="J101" s="11" t="n"/>
       <c r="K101" s="11" t="n"/>
-      <c r="L101" s="11" t="n"/>
-      <c r="M101" s="11" t="n"/>
     </row>
     <row r="102" ht="15.75" customHeight="1" s="16">
       <c r="A102" s="4">
@@ -4524,8 +4074,6 @@
       <c r="I102" s="11" t="n"/>
       <c r="J102" s="11" t="n"/>
       <c r="K102" s="11" t="n"/>
-      <c r="L102" s="11" t="n"/>
-      <c r="M102" s="11" t="n"/>
     </row>
     <row r="103" ht="15.75" customHeight="1" s="16">
       <c r="A103" s="4">
@@ -4554,8 +4102,6 @@
       <c r="I103" s="11" t="n"/>
       <c r="J103" s="11" t="n"/>
       <c r="K103" s="11" t="n"/>
-      <c r="L103" s="11" t="n"/>
-      <c r="M103" s="11" t="n"/>
     </row>
     <row r="104" ht="15.75" customHeight="1" s="16">
       <c r="A104" s="4">
@@ -4584,8 +4130,6 @@
       <c r="I104" s="11" t="n"/>
       <c r="J104" s="11" t="n"/>
       <c r="K104" s="11" t="n"/>
-      <c r="L104" s="11" t="n"/>
-      <c r="M104" s="11" t="n"/>
     </row>
     <row r="105" ht="15.75" customHeight="1" s="16">
       <c r="A105" s="4">
@@ -4614,8 +4158,6 @@
       <c r="I105" s="11" t="n"/>
       <c r="J105" s="11" t="n"/>
       <c r="K105" s="11" t="n"/>
-      <c r="L105" s="11" t="n"/>
-      <c r="M105" s="11" t="n"/>
     </row>
     <row r="106" ht="15.75" customHeight="1" s="16">
       <c r="A106" s="4">
@@ -4644,8 +4186,6 @@
       <c r="I106" s="11" t="n"/>
       <c r="J106" s="11" t="n"/>
       <c r="K106" s="11" t="n"/>
-      <c r="L106" s="11" t="n"/>
-      <c r="M106" s="11" t="n"/>
     </row>
     <row r="107" ht="15.75" customHeight="1" s="16">
       <c r="A107" s="4">
@@ -4674,8 +4214,6 @@
       <c r="I107" s="11" t="n"/>
       <c r="J107" s="11" t="n"/>
       <c r="K107" s="11" t="n"/>
-      <c r="L107" s="11" t="n"/>
-      <c r="M107" s="11" t="n"/>
     </row>
     <row r="108" ht="15.75" customHeight="1" s="16">
       <c r="A108" s="4">
@@ -4704,8 +4242,6 @@
       <c r="I108" s="11" t="n"/>
       <c r="J108" s="11" t="n"/>
       <c r="K108" s="11" t="n"/>
-      <c r="L108" s="11" t="n"/>
-      <c r="M108" s="11" t="n"/>
     </row>
     <row r="109" ht="15.75" customHeight="1" s="16">
       <c r="A109" s="4">
@@ -4734,8 +4270,6 @@
       <c r="I109" s="11" t="n"/>
       <c r="J109" s="11" t="n"/>
       <c r="K109" s="11" t="n"/>
-      <c r="L109" s="11" t="n"/>
-      <c r="M109" s="11" t="n"/>
     </row>
     <row r="110" ht="15.75" customHeight="1" s="16">
       <c r="A110" s="4">
@@ -4764,8 +4298,6 @@
       <c r="I110" s="11" t="n"/>
       <c r="J110" s="11" t="n"/>
       <c r="K110" s="11" t="n"/>
-      <c r="L110" s="11" t="n"/>
-      <c r="M110" s="11" t="n"/>
     </row>
     <row r="111" ht="15.75" customHeight="1" s="16">
       <c r="A111" s="4">
@@ -4794,8 +4326,6 @@
       <c r="I111" s="11" t="n"/>
       <c r="J111" s="11" t="n"/>
       <c r="K111" s="11" t="n"/>
-      <c r="L111" s="11" t="n"/>
-      <c r="M111" s="11" t="n"/>
     </row>
     <row r="112" ht="15.75" customHeight="1" s="16">
       <c r="A112" s="4">
@@ -4824,8 +4354,6 @@
       <c r="I112" s="11" t="n"/>
       <c r="J112" s="11" t="n"/>
       <c r="K112" s="11" t="n"/>
-      <c r="L112" s="11" t="n"/>
-      <c r="M112" s="11" t="n"/>
     </row>
     <row r="113" ht="15.75" customHeight="1" s="16">
       <c r="A113" s="4">
@@ -4854,8 +4382,6 @@
       <c r="I113" s="11" t="n"/>
       <c r="J113" s="11" t="n"/>
       <c r="K113" s="11" t="n"/>
-      <c r="L113" s="11" t="n"/>
-      <c r="M113" s="11" t="n"/>
     </row>
     <row r="114" ht="15.75" customHeight="1" s="16">
       <c r="A114" s="4">
@@ -4884,8 +4410,6 @@
       <c r="I114" s="11" t="n"/>
       <c r="J114" s="11" t="n"/>
       <c r="K114" s="11" t="n"/>
-      <c r="L114" s="11" t="n"/>
-      <c r="M114" s="11" t="n"/>
     </row>
     <row r="115" ht="15.75" customHeight="1" s="16">
       <c r="A115" s="4">
@@ -4914,8 +4438,6 @@
       <c r="I115" s="11" t="n"/>
       <c r="J115" s="11" t="n"/>
       <c r="K115" s="11" t="n"/>
-      <c r="L115" s="11" t="n"/>
-      <c r="M115" s="11" t="n"/>
     </row>
     <row r="116" ht="15.75" customHeight="1" s="16">
       <c r="A116" s="4">
@@ -4944,8 +4466,6 @@
       <c r="I116" s="11" t="n"/>
       <c r="J116" s="11" t="n"/>
       <c r="K116" s="11" t="n"/>
-      <c r="L116" s="11" t="n"/>
-      <c r="M116" s="11" t="n"/>
     </row>
     <row r="117" ht="15.75" customHeight="1" s="16">
       <c r="A117" s="4">
@@ -4974,8 +4494,6 @@
       <c r="I117" s="11" t="n"/>
       <c r="J117" s="11" t="n"/>
       <c r="K117" s="11" t="n"/>
-      <c r="L117" s="11" t="n"/>
-      <c r="M117" s="11" t="n"/>
     </row>
     <row r="118" ht="15.75" customHeight="1" s="16">
       <c r="A118" s="4">
@@ -5004,8 +4522,6 @@
       <c r="I118" s="11" t="n"/>
       <c r="J118" s="11" t="n"/>
       <c r="K118" s="11" t="n"/>
-      <c r="L118" s="11" t="n"/>
-      <c r="M118" s="11" t="n"/>
     </row>
     <row r="119" ht="15.75" customHeight="1" s="16">
       <c r="A119" s="4">
@@ -5034,8 +4550,6 @@
       <c r="I119" s="11" t="n"/>
       <c r="J119" s="11" t="n"/>
       <c r="K119" s="11" t="n"/>
-      <c r="L119" s="11" t="n"/>
-      <c r="M119" s="11" t="n"/>
     </row>
     <row r="120" ht="15.75" customHeight="1" s="16">
       <c r="A120" s="4">
@@ -5064,8 +4578,6 @@
       <c r="I120" s="11" t="n"/>
       <c r="J120" s="11" t="n"/>
       <c r="K120" s="11" t="n"/>
-      <c r="L120" s="11" t="n"/>
-      <c r="M120" s="11" t="n"/>
     </row>
     <row r="121" ht="15.75" customHeight="1" s="16">
       <c r="A121" s="4">
@@ -5094,8 +4606,6 @@
       <c r="I121" s="11" t="n"/>
       <c r="J121" s="11" t="n"/>
       <c r="K121" s="11" t="n"/>
-      <c r="L121" s="11" t="n"/>
-      <c r="M121" s="11" t="n"/>
     </row>
     <row r="122" ht="15.75" customHeight="1" s="16">
       <c r="A122" s="4">
@@ -5124,8 +4634,6 @@
       <c r="I122" s="11" t="n"/>
       <c r="J122" s="11" t="n"/>
       <c r="K122" s="11" t="n"/>
-      <c r="L122" s="11" t="n"/>
-      <c r="M122" s="11" t="n"/>
     </row>
     <row r="123" ht="15.75" customHeight="1" s="16">
       <c r="A123" s="4">
@@ -5154,8 +4662,6 @@
       <c r="I123" s="11" t="n"/>
       <c r="J123" s="11" t="n"/>
       <c r="K123" s="11" t="n"/>
-      <c r="L123" s="11" t="n"/>
-      <c r="M123" s="11" t="n"/>
     </row>
     <row r="124" ht="15.75" customHeight="1" s="16">
       <c r="A124" s="4">
@@ -5184,8 +4690,6 @@
       <c r="I124" s="11" t="n"/>
       <c r="J124" s="11" t="n"/>
       <c r="K124" s="11" t="n"/>
-      <c r="L124" s="11" t="n"/>
-      <c r="M124" s="11" t="n"/>
     </row>
     <row r="125" ht="15.75" customHeight="1" s="16">
       <c r="A125" s="4">
@@ -5214,8 +4718,6 @@
       <c r="I125" s="11" t="n"/>
       <c r="J125" s="11" t="n"/>
       <c r="K125" s="11" t="n"/>
-      <c r="L125" s="11" t="n"/>
-      <c r="M125" s="11" t="n"/>
     </row>
     <row r="126" ht="15.75" customHeight="1" s="16">
       <c r="A126" s="4">
@@ -5244,8 +4746,6 @@
       <c r="I126" s="11" t="n"/>
       <c r="J126" s="11" t="n"/>
       <c r="K126" s="11" t="n"/>
-      <c r="L126" s="11" t="n"/>
-      <c r="M126" s="11" t="n"/>
     </row>
     <row r="127" ht="15.75" customHeight="1" s="16">
       <c r="A127" s="4">
@@ -5274,8 +4774,6 @@
       <c r="I127" s="11" t="n"/>
       <c r="J127" s="11" t="n"/>
       <c r="K127" s="11" t="n"/>
-      <c r="L127" s="11" t="n"/>
-      <c r="M127" s="11" t="n"/>
     </row>
     <row r="128" ht="15.75" customHeight="1" s="16">
       <c r="A128" s="4">
@@ -5304,8 +4802,6 @@
       <c r="I128" s="11" t="n"/>
       <c r="J128" s="11" t="n"/>
       <c r="K128" s="11" t="n"/>
-      <c r="L128" s="11" t="n"/>
-      <c r="M128" s="11" t="n"/>
     </row>
     <row r="129" ht="15.75" customHeight="1" s="16">
       <c r="A129" s="4">
@@ -5334,8 +4830,6 @@
       <c r="I129" s="11" t="n"/>
       <c r="J129" s="11" t="n"/>
       <c r="K129" s="11" t="n"/>
-      <c r="L129" s="11" t="n"/>
-      <c r="M129" s="11" t="n"/>
     </row>
     <row r="130" ht="15.75" customHeight="1" s="16">
       <c r="A130" s="4">
@@ -5364,8 +4858,6 @@
       <c r="I130" s="11" t="n"/>
       <c r="J130" s="11" t="n"/>
       <c r="K130" s="11" t="n"/>
-      <c r="L130" s="11" t="n"/>
-      <c r="M130" s="11" t="n"/>
     </row>
     <row r="131" ht="15.75" customHeight="1" s="16">
       <c r="A131" s="4">
@@ -5394,8 +4886,6 @@
       <c r="I131" s="11" t="n"/>
       <c r="J131" s="11" t="n"/>
       <c r="K131" s="11" t="n"/>
-      <c r="L131" s="11" t="n"/>
-      <c r="M131" s="11" t="n"/>
     </row>
     <row r="132" ht="15.75" customHeight="1" s="16">
       <c r="A132" s="4">
@@ -5424,8 +4914,6 @@
       <c r="I132" s="11" t="n"/>
       <c r="J132" s="11" t="n"/>
       <c r="K132" s="11" t="n"/>
-      <c r="L132" s="11" t="n"/>
-      <c r="M132" s="11" t="n"/>
     </row>
     <row r="133" ht="15.75" customHeight="1" s="16">
       <c r="A133" s="4">
@@ -5454,8 +4942,6 @@
       <c r="I133" s="11" t="n"/>
       <c r="J133" s="11" t="n"/>
       <c r="K133" s="11" t="n"/>
-      <c r="L133" s="11" t="n"/>
-      <c r="M133" s="11" t="n"/>
     </row>
     <row r="134" ht="15.75" customHeight="1" s="16">
       <c r="A134" s="4">
@@ -5484,8 +4970,6 @@
       <c r="I134" s="11" t="n"/>
       <c r="J134" s="11" t="n"/>
       <c r="K134" s="11" t="n"/>
-      <c r="L134" s="11" t="n"/>
-      <c r="M134" s="11" t="n"/>
     </row>
     <row r="135" ht="15.75" customHeight="1" s="16">
       <c r="A135" s="4">
@@ -5514,8 +4998,6 @@
       <c r="I135" s="11" t="n"/>
       <c r="J135" s="11" t="n"/>
       <c r="K135" s="11" t="n"/>
-      <c r="L135" s="11" t="n"/>
-      <c r="M135" s="11" t="n"/>
     </row>
     <row r="136" ht="15.75" customHeight="1" s="16">
       <c r="A136" s="4">
@@ -5544,8 +5026,6 @@
       <c r="I136" s="11" t="n"/>
       <c r="J136" s="11" t="n"/>
       <c r="K136" s="11" t="n"/>
-      <c r="L136" s="11" t="n"/>
-      <c r="M136" s="11" t="n"/>
     </row>
     <row r="137" ht="15.75" customHeight="1" s="16">
       <c r="A137" s="4">
@@ -5574,8 +5054,6 @@
       <c r="I137" s="11" t="n"/>
       <c r="J137" s="11" t="n"/>
       <c r="K137" s="11" t="n"/>
-      <c r="L137" s="11" t="n"/>
-      <c r="M137" s="11" t="n"/>
     </row>
     <row r="138" ht="15.75" customHeight="1" s="16">
       <c r="A138" s="4">
@@ -5604,8 +5082,6 @@
       <c r="I138" s="11" t="n"/>
       <c r="J138" s="11" t="n"/>
       <c r="K138" s="11" t="n"/>
-      <c r="L138" s="11" t="n"/>
-      <c r="M138" s="11" t="n"/>
     </row>
     <row r="139" ht="15.75" customHeight="1" s="16">
       <c r="A139" s="4">
@@ -5634,8 +5110,6 @@
       <c r="I139" s="11" t="n"/>
       <c r="J139" s="11" t="n"/>
       <c r="K139" s="11" t="n"/>
-      <c r="L139" s="11" t="n"/>
-      <c r="M139" s="11" t="n"/>
     </row>
     <row r="140" ht="15.75" customHeight="1" s="16">
       <c r="A140" s="4">
@@ -5664,8 +5138,6 @@
       <c r="I140" s="11" t="n"/>
       <c r="J140" s="11" t="n"/>
       <c r="K140" s="11" t="n"/>
-      <c r="L140" s="11" t="n"/>
-      <c r="M140" s="11" t="n"/>
     </row>
     <row r="141" ht="15.75" customHeight="1" s="16">
       <c r="A141" s="4">
@@ -5694,8 +5166,6 @@
       <c r="I141" s="11" t="n"/>
       <c r="J141" s="11" t="n"/>
       <c r="K141" s="11" t="n"/>
-      <c r="L141" s="11" t="n"/>
-      <c r="M141" s="11" t="n"/>
     </row>
     <row r="142" ht="15.75" customHeight="1" s="16">
       <c r="A142" s="4">
@@ -5724,8 +5194,6 @@
       <c r="I142" s="11" t="n"/>
       <c r="J142" s="11" t="n"/>
       <c r="K142" s="11" t="n"/>
-      <c r="L142" s="11" t="n"/>
-      <c r="M142" s="11" t="n"/>
     </row>
     <row r="143" ht="15.75" customHeight="1" s="16">
       <c r="A143" s="4">
@@ -5754,8 +5222,6 @@
       <c r="I143" s="11" t="n"/>
       <c r="J143" s="11" t="n"/>
       <c r="K143" s="11" t="n"/>
-      <c r="L143" s="11" t="n"/>
-      <c r="M143" s="11" t="n"/>
     </row>
     <row r="144" ht="15.75" customHeight="1" s="16">
       <c r="A144" s="4">
@@ -5784,8 +5250,6 @@
       <c r="I144" s="11" t="n"/>
       <c r="J144" s="11" t="n"/>
       <c r="K144" s="11" t="n"/>
-      <c r="L144" s="11" t="n"/>
-      <c r="M144" s="11" t="n"/>
     </row>
     <row r="145" ht="15.75" customHeight="1" s="16">
       <c r="A145" s="4">
@@ -5814,8 +5278,6 @@
       <c r="I145" s="11" t="n"/>
       <c r="J145" s="11" t="n"/>
       <c r="K145" s="11" t="n"/>
-      <c r="L145" s="11" t="n"/>
-      <c r="M145" s="11" t="n"/>
     </row>
     <row r="146" ht="15.75" customHeight="1" s="16">
       <c r="A146" s="4">
@@ -5844,8 +5306,6 @@
       <c r="I146" s="11" t="n"/>
       <c r="J146" s="11" t="n"/>
       <c r="K146" s="11" t="n"/>
-      <c r="L146" s="11" t="n"/>
-      <c r="M146" s="11" t="n"/>
     </row>
     <row r="147" ht="15.75" customHeight="1" s="16">
       <c r="A147" s="4">
@@ -5874,8 +5334,6 @@
       <c r="I147" s="11" t="n"/>
       <c r="J147" s="11" t="n"/>
       <c r="K147" s="11" t="n"/>
-      <c r="L147" s="11" t="n"/>
-      <c r="M147" s="11" t="n"/>
     </row>
     <row r="148" ht="15.75" customHeight="1" s="16">
       <c r="A148" s="4">
@@ -5904,8 +5362,6 @@
       <c r="I148" s="11" t="n"/>
       <c r="J148" s="11" t="n"/>
       <c r="K148" s="11" t="n"/>
-      <c r="L148" s="11" t="n"/>
-      <c r="M148" s="11" t="n"/>
     </row>
     <row r="149" ht="15.75" customHeight="1" s="16">
       <c r="A149" s="4">
@@ -5934,8 +5390,6 @@
       <c r="I149" s="11" t="n"/>
       <c r="J149" s="11" t="n"/>
       <c r="K149" s="11" t="n"/>
-      <c r="L149" s="11" t="n"/>
-      <c r="M149" s="11" t="n"/>
     </row>
     <row r="150" ht="15.75" customHeight="1" s="16">
       <c r="A150" s="4">
@@ -5964,8 +5418,6 @@
       <c r="I150" s="11" t="n"/>
       <c r="J150" s="11" t="n"/>
       <c r="K150" s="11" t="n"/>
-      <c r="L150" s="11" t="n"/>
-      <c r="M150" s="11" t="n"/>
     </row>
     <row r="151" ht="15.75" customHeight="1" s="16">
       <c r="A151" s="4">
@@ -5994,8 +5446,6 @@
       <c r="I151" s="11" t="n"/>
       <c r="J151" s="11" t="n"/>
       <c r="K151" s="11" t="n"/>
-      <c r="L151" s="11" t="n"/>
-      <c r="M151" s="11" t="n"/>
     </row>
     <row r="152" ht="15.75" customHeight="1" s="16">
       <c r="A152" s="4">
@@ -6024,8 +5474,6 @@
       <c r="I152" s="11" t="n"/>
       <c r="J152" s="11" t="n"/>
       <c r="K152" s="11" t="n"/>
-      <c r="L152" s="11" t="n"/>
-      <c r="M152" s="11" t="n"/>
     </row>
     <row r="153" ht="15.75" customHeight="1" s="16">
       <c r="A153" s="4">
@@ -6054,8 +5502,6 @@
       <c r="I153" s="11" t="n"/>
       <c r="J153" s="11" t="n"/>
       <c r="K153" s="11" t="n"/>
-      <c r="L153" s="11" t="n"/>
-      <c r="M153" s="11" t="n"/>
     </row>
     <row r="154" ht="15.75" customHeight="1" s="16">
       <c r="A154" s="4">
@@ -6084,8 +5530,6 @@
       <c r="I154" s="11" t="n"/>
       <c r="J154" s="11" t="n"/>
       <c r="K154" s="11" t="n"/>
-      <c r="L154" s="11" t="n"/>
-      <c r="M154" s="11" t="n"/>
     </row>
     <row r="155" ht="15.75" customHeight="1" s="16">
       <c r="A155" s="4">
@@ -6114,8 +5558,6 @@
       <c r="I155" s="11" t="n"/>
       <c r="J155" s="11" t="n"/>
       <c r="K155" s="11" t="n"/>
-      <c r="L155" s="11" t="n"/>
-      <c r="M155" s="11" t="n"/>
     </row>
     <row r="156" ht="15.75" customHeight="1" s="16">
       <c r="A156" s="4">
@@ -6144,8 +5586,6 @@
       <c r="I156" s="11" t="n"/>
       <c r="J156" s="11" t="n"/>
       <c r="K156" s="11" t="n"/>
-      <c r="L156" s="11" t="n"/>
-      <c r="M156" s="11" t="n"/>
     </row>
     <row r="157" ht="15.75" customHeight="1" s="16">
       <c r="A157" s="4">
@@ -6174,8 +5614,6 @@
       <c r="I157" s="11" t="n"/>
       <c r="J157" s="11" t="n"/>
       <c r="K157" s="11" t="n"/>
-      <c r="L157" s="11" t="n"/>
-      <c r="M157" s="11" t="n"/>
     </row>
     <row r="158" ht="15.75" customHeight="1" s="16">
       <c r="A158" s="4">
@@ -6204,8 +5642,6 @@
       <c r="I158" s="11" t="n"/>
       <c r="J158" s="11" t="n"/>
       <c r="K158" s="11" t="n"/>
-      <c r="L158" s="11" t="n"/>
-      <c r="M158" s="11" t="n"/>
     </row>
     <row r="159" ht="15.75" customHeight="1" s="16">
       <c r="A159" s="4">
@@ -6234,8 +5670,6 @@
       <c r="I159" s="11" t="n"/>
       <c r="J159" s="11" t="n"/>
       <c r="K159" s="11" t="n"/>
-      <c r="L159" s="11" t="n"/>
-      <c r="M159" s="11" t="n"/>
     </row>
     <row r="160" ht="15.75" customHeight="1" s="16">
       <c r="A160" s="4">
@@ -6264,8 +5698,6 @@
       <c r="I160" s="11" t="n"/>
       <c r="J160" s="11" t="n"/>
       <c r="K160" s="11" t="n"/>
-      <c r="L160" s="11" t="n"/>
-      <c r="M160" s="11" t="n"/>
     </row>
     <row r="161" ht="15.75" customHeight="1" s="16">
       <c r="A161" s="4">
@@ -6294,8 +5726,6 @@
       <c r="I161" s="11" t="n"/>
       <c r="J161" s="11" t="n"/>
       <c r="K161" s="11" t="n"/>
-      <c r="L161" s="11" t="n"/>
-      <c r="M161" s="11" t="n"/>
     </row>
     <row r="162" ht="15.75" customHeight="1" s="16">
       <c r="A162" s="4">
@@ -6324,8 +5754,6 @@
       <c r="I162" s="11" t="n"/>
       <c r="J162" s="11" t="n"/>
       <c r="K162" s="11" t="n"/>
-      <c r="L162" s="11" t="n"/>
-      <c r="M162" s="11" t="n"/>
     </row>
     <row r="163" ht="15.75" customHeight="1" s="16">
       <c r="A163" s="4">
@@ -6354,8 +5782,6 @@
       <c r="I163" s="11" t="n"/>
       <c r="J163" s="11" t="n"/>
       <c r="K163" s="11" t="n"/>
-      <c r="L163" s="11" t="n"/>
-      <c r="M163" s="11" t="n"/>
     </row>
     <row r="164" ht="15.75" customHeight="1" s="16">
       <c r="A164" s="4">
@@ -6384,8 +5810,6 @@
       <c r="I164" s="11" t="n"/>
       <c r="J164" s="11" t="n"/>
       <c r="K164" s="11" t="n"/>
-      <c r="L164" s="11" t="n"/>
-      <c r="M164" s="11" t="n"/>
     </row>
     <row r="165" ht="15.75" customHeight="1" s="16">
       <c r="A165" s="4">
@@ -6414,8 +5838,6 @@
       <c r="I165" s="11" t="n"/>
       <c r="J165" s="11" t="n"/>
       <c r="K165" s="11" t="n"/>
-      <c r="L165" s="11" t="n"/>
-      <c r="M165" s="11" t="n"/>
     </row>
     <row r="166" ht="15.75" customHeight="1" s="16">
       <c r="A166" s="4">
@@ -6444,8 +5866,6 @@
       <c r="I166" s="11" t="n"/>
       <c r="J166" s="11" t="n"/>
       <c r="K166" s="11" t="n"/>
-      <c r="L166" s="11" t="n"/>
-      <c r="M166" s="11" t="n"/>
     </row>
     <row r="167" ht="15.75" customHeight="1" s="16">
       <c r="A167" s="4">
@@ -6474,8 +5894,6 @@
       <c r="I167" s="11" t="n"/>
       <c r="J167" s="11" t="n"/>
       <c r="K167" s="11" t="n"/>
-      <c r="L167" s="11" t="n"/>
-      <c r="M167" s="11" t="n"/>
     </row>
     <row r="168" ht="15.75" customHeight="1" s="16">
       <c r="A168" s="4">
@@ -6504,8 +5922,6 @@
       <c r="I168" s="11" t="n"/>
       <c r="J168" s="11" t="n"/>
       <c r="K168" s="11" t="n"/>
-      <c r="L168" s="11" t="n"/>
-      <c r="M168" s="11" t="n"/>
     </row>
     <row r="169" ht="15.75" customHeight="1" s="16">
       <c r="A169" s="4">
@@ -6534,8 +5950,6 @@
       <c r="I169" s="11" t="n"/>
       <c r="J169" s="11" t="n"/>
       <c r="K169" s="11" t="n"/>
-      <c r="L169" s="11" t="n"/>
-      <c r="M169" s="11" t="n"/>
     </row>
     <row r="170" ht="15.75" customHeight="1" s="16">
       <c r="A170" s="4">
@@ -6564,8 +5978,6 @@
       <c r="I170" s="11" t="n"/>
       <c r="J170" s="11" t="n"/>
       <c r="K170" s="11" t="n"/>
-      <c r="L170" s="11" t="n"/>
-      <c r="M170" s="11" t="n"/>
     </row>
     <row r="171" ht="15.75" customHeight="1" s="16">
       <c r="A171" s="4">
@@ -6594,8 +6006,6 @@
       <c r="I171" s="11" t="n"/>
       <c r="J171" s="11" t="n"/>
       <c r="K171" s="11" t="n"/>
-      <c r="L171" s="11" t="n"/>
-      <c r="M171" s="11" t="n"/>
     </row>
     <row r="172" ht="15.75" customHeight="1" s="16">
       <c r="A172" s="4">
@@ -6624,8 +6034,6 @@
       <c r="I172" s="11" t="n"/>
       <c r="J172" s="11" t="n"/>
       <c r="K172" s="11" t="n"/>
-      <c r="L172" s="11" t="n"/>
-      <c r="M172" s="11" t="n"/>
     </row>
     <row r="173" ht="15.75" customHeight="1" s="16">
       <c r="A173" s="4">
@@ -6654,8 +6062,6 @@
       <c r="I173" s="11" t="n"/>
       <c r="J173" s="11" t="n"/>
       <c r="K173" s="11" t="n"/>
-      <c r="L173" s="11" t="n"/>
-      <c r="M173" s="11" t="n"/>
     </row>
     <row r="174" ht="15.75" customHeight="1" s="16">
       <c r="A174" s="4">
@@ -6684,8 +6090,6 @@
       <c r="I174" s="11" t="n"/>
       <c r="J174" s="11" t="n"/>
       <c r="K174" s="11" t="n"/>
-      <c r="L174" s="11" t="n"/>
-      <c r="M174" s="11" t="n"/>
     </row>
     <row r="175" ht="15.75" customHeight="1" s="16">
       <c r="A175" s="4">
@@ -6714,8 +6118,6 @@
       <c r="I175" s="11" t="n"/>
       <c r="J175" s="11" t="n"/>
       <c r="K175" s="11" t="n"/>
-      <c r="L175" s="11" t="n"/>
-      <c r="M175" s="11" t="n"/>
     </row>
     <row r="176" ht="15.75" customHeight="1" s="16">
       <c r="A176" s="4">
@@ -6744,8 +6146,6 @@
       <c r="I176" s="11" t="n"/>
       <c r="J176" s="11" t="n"/>
       <c r="K176" s="11" t="n"/>
-      <c r="L176" s="11" t="n"/>
-      <c r="M176" s="11" t="n"/>
     </row>
     <row r="177" ht="15.75" customHeight="1" s="16">
       <c r="A177" s="4">
@@ -6774,8 +6174,6 @@
       <c r="I177" s="11" t="n"/>
       <c r="J177" s="11" t="n"/>
       <c r="K177" s="11" t="n"/>
-      <c r="L177" s="11" t="n"/>
-      <c r="M177" s="11" t="n"/>
     </row>
     <row r="178" ht="15.75" customHeight="1" s="16">
       <c r="A178" s="4">
@@ -6804,8 +6202,6 @@
       <c r="I178" s="11" t="n"/>
       <c r="J178" s="11" t="n"/>
       <c r="K178" s="11" t="n"/>
-      <c r="L178" s="11" t="n"/>
-      <c r="M178" s="11" t="n"/>
     </row>
     <row r="179" ht="15.75" customHeight="1" s="16">
       <c r="A179" s="4">
@@ -6834,8 +6230,6 @@
       <c r="I179" s="11" t="n"/>
       <c r="J179" s="11" t="n"/>
       <c r="K179" s="11" t="n"/>
-      <c r="L179" s="11" t="n"/>
-      <c r="M179" s="11" t="n"/>
     </row>
     <row r="180" ht="15.75" customHeight="1" s="16">
       <c r="A180" s="4">
@@ -6864,8 +6258,6 @@
       <c r="I180" s="11" t="n"/>
       <c r="J180" s="11" t="n"/>
       <c r="K180" s="11" t="n"/>
-      <c r="L180" s="11" t="n"/>
-      <c r="M180" s="11" t="n"/>
     </row>
     <row r="181" ht="15.75" customHeight="1" s="16">
       <c r="A181" s="4">
@@ -6894,8 +6286,6 @@
       <c r="I181" s="11" t="n"/>
       <c r="J181" s="11" t="n"/>
       <c r="K181" s="11" t="n"/>
-      <c r="L181" s="11" t="n"/>
-      <c r="M181" s="11" t="n"/>
     </row>
     <row r="182" ht="15.75" customHeight="1" s="16">
       <c r="A182" s="4">
@@ -6924,8 +6314,6 @@
       <c r="I182" s="11" t="n"/>
       <c r="J182" s="11" t="n"/>
       <c r="K182" s="11" t="n"/>
-      <c r="L182" s="11" t="n"/>
-      <c r="M182" s="11" t="n"/>
     </row>
     <row r="183" ht="15.75" customHeight="1" s="16">
       <c r="A183" s="4">
@@ -6954,8 +6342,6 @@
       <c r="I183" s="11" t="n"/>
       <c r="J183" s="11" t="n"/>
       <c r="K183" s="11" t="n"/>
-      <c r="L183" s="11" t="n"/>
-      <c r="M183" s="11" t="n"/>
     </row>
     <row r="184" ht="15.75" customHeight="1" s="16">
       <c r="A184" s="4">
@@ -6984,8 +6370,6 @@
       <c r="I184" s="11" t="n"/>
       <c r="J184" s="11" t="n"/>
       <c r="K184" s="11" t="n"/>
-      <c r="L184" s="11" t="n"/>
-      <c r="M184" s="11" t="n"/>
     </row>
     <row r="185" ht="15.75" customHeight="1" s="16">
       <c r="A185" s="4">
@@ -7014,8 +6398,6 @@
       <c r="I185" s="11" t="n"/>
       <c r="J185" s="11" t="n"/>
       <c r="K185" s="11" t="n"/>
-      <c r="L185" s="11" t="n"/>
-      <c r="M185" s="11" t="n"/>
     </row>
     <row r="186" ht="15.75" customHeight="1" s="16">
       <c r="A186" s="4">
@@ -7044,8 +6426,6 @@
       <c r="I186" s="11" t="n"/>
       <c r="J186" s="11" t="n"/>
       <c r="K186" s="11" t="n"/>
-      <c r="L186" s="11" t="n"/>
-      <c r="M186" s="11" t="n"/>
     </row>
     <row r="187" ht="15.75" customHeight="1" s="16">
       <c r="A187" s="4">
@@ -7074,8 +6454,6 @@
       <c r="I187" s="11" t="n"/>
       <c r="J187" s="11" t="n"/>
       <c r="K187" s="11" t="n"/>
-      <c r="L187" s="11" t="n"/>
-      <c r="M187" s="11" t="n"/>
     </row>
     <row r="188" ht="15.75" customHeight="1" s="16">
       <c r="A188" s="4">
@@ -7104,8 +6482,6 @@
       <c r="I188" s="11" t="n"/>
       <c r="J188" s="11" t="n"/>
       <c r="K188" s="11" t="n"/>
-      <c r="L188" s="11" t="n"/>
-      <c r="M188" s="11" t="n"/>
     </row>
     <row r="189" ht="15.75" customHeight="1" s="16">
       <c r="A189" s="4">
@@ -7134,8 +6510,6 @@
       <c r="I189" s="11" t="n"/>
       <c r="J189" s="11" t="n"/>
       <c r="K189" s="11" t="n"/>
-      <c r="L189" s="11" t="n"/>
-      <c r="M189" s="11" t="n"/>
     </row>
     <row r="190" ht="15.75" customHeight="1" s="16">
       <c r="A190" s="4">
@@ -7164,8 +6538,6 @@
       <c r="I190" s="11" t="n"/>
       <c r="J190" s="11" t="n"/>
       <c r="K190" s="11" t="n"/>
-      <c r="L190" s="11" t="n"/>
-      <c r="M190" s="11" t="n"/>
     </row>
     <row r="191" ht="15.75" customHeight="1" s="16">
       <c r="A191" s="4">
@@ -7194,8 +6566,6 @@
       <c r="I191" s="11" t="n"/>
       <c r="J191" s="11" t="n"/>
       <c r="K191" s="11" t="n"/>
-      <c r="L191" s="11" t="n"/>
-      <c r="M191" s="11" t="n"/>
     </row>
     <row r="192" ht="15.75" customHeight="1" s="16">
       <c r="A192" s="4">
@@ -7224,8 +6594,6 @@
       <c r="I192" s="11" t="n"/>
       <c r="J192" s="11" t="n"/>
       <c r="K192" s="11" t="n"/>
-      <c r="L192" s="11" t="n"/>
-      <c r="M192" s="11" t="n"/>
     </row>
     <row r="193" ht="15.75" customHeight="1" s="16">
       <c r="A193" s="4">
@@ -7254,8 +6622,6 @@
       <c r="I193" s="11" t="n"/>
       <c r="J193" s="11" t="n"/>
       <c r="K193" s="11" t="n"/>
-      <c r="L193" s="11" t="n"/>
-      <c r="M193" s="11" t="n"/>
     </row>
     <row r="194" ht="15.75" customHeight="1" s="16">
       <c r="A194" s="4">
@@ -7284,8 +6650,6 @@
       <c r="I194" s="11" t="n"/>
       <c r="J194" s="11" t="n"/>
       <c r="K194" s="11" t="n"/>
-      <c r="L194" s="11" t="n"/>
-      <c r="M194" s="11" t="n"/>
     </row>
     <row r="195" ht="15.75" customHeight="1" s="16">
       <c r="A195" s="4">
@@ -7314,8 +6678,6 @@
       <c r="I195" s="11" t="n"/>
       <c r="J195" s="11" t="n"/>
       <c r="K195" s="11" t="n"/>
-      <c r="L195" s="11" t="n"/>
-      <c r="M195" s="11" t="n"/>
     </row>
     <row r="196" ht="15.75" customHeight="1" s="16">
       <c r="A196" s="4">
@@ -7344,8 +6706,6 @@
       <c r="I196" s="11" t="n"/>
       <c r="J196" s="11" t="n"/>
       <c r="K196" s="11" t="n"/>
-      <c r="L196" s="11" t="n"/>
-      <c r="M196" s="11" t="n"/>
     </row>
     <row r="197" ht="15.75" customHeight="1" s="16">
       <c r="A197" s="4">
@@ -7374,8 +6734,6 @@
       <c r="I197" s="11" t="n"/>
       <c r="J197" s="11" t="n"/>
       <c r="K197" s="11" t="n"/>
-      <c r="L197" s="11" t="n"/>
-      <c r="M197" s="11" t="n"/>
     </row>
     <row r="198" ht="15.75" customHeight="1" s="16">
       <c r="A198" s="4">
@@ -7404,8 +6762,6 @@
       <c r="I198" s="11" t="n"/>
       <c r="J198" s="11" t="n"/>
       <c r="K198" s="11" t="n"/>
-      <c r="L198" s="11" t="n"/>
-      <c r="M198" s="11" t="n"/>
     </row>
     <row r="199" ht="15.75" customHeight="1" s="16">
       <c r="A199" s="4">
@@ -7434,8 +6790,6 @@
       <c r="I199" s="11" t="n"/>
       <c r="J199" s="11" t="n"/>
       <c r="K199" s="11" t="n"/>
-      <c r="L199" s="11" t="n"/>
-      <c r="M199" s="11" t="n"/>
     </row>
     <row r="200" ht="15.75" customHeight="1" s="16">
       <c r="A200" s="4">
@@ -7464,8 +6818,6 @@
       <c r="I200" s="11" t="n"/>
       <c r="J200" s="11" t="n"/>
       <c r="K200" s="11" t="n"/>
-      <c r="L200" s="11" t="n"/>
-      <c r="M200" s="11" t="n"/>
     </row>
     <row r="201" ht="15.75" customHeight="1" s="16">
       <c r="A201" s="4">
@@ -7494,8 +6846,6 @@
       <c r="I201" s="11" t="n"/>
       <c r="J201" s="11" t="n"/>
       <c r="K201" s="11" t="n"/>
-      <c r="L201" s="11" t="n"/>
-      <c r="M201" s="11" t="n"/>
     </row>
     <row r="202" ht="15.75" customHeight="1" s="16">
       <c r="A202" s="4">
@@ -7524,8 +6874,6 @@
       <c r="I202" s="11" t="n"/>
       <c r="J202" s="11" t="n"/>
       <c r="K202" s="11" t="n"/>
-      <c r="L202" s="11" t="n"/>
-      <c r="M202" s="11" t="n"/>
     </row>
     <row r="203" ht="15.75" customHeight="1" s="16">
       <c r="A203" s="4">
@@ -7554,8 +6902,6 @@
       <c r="I203" s="11" t="n"/>
       <c r="J203" s="11" t="n"/>
       <c r="K203" s="11" t="n"/>
-      <c r="L203" s="11" t="n"/>
-      <c r="M203" s="11" t="n"/>
     </row>
     <row r="204" ht="15.75" customHeight="1" s="16">
       <c r="A204" s="4">
@@ -7584,8 +6930,6 @@
       <c r="I204" s="11" t="n"/>
       <c r="J204" s="11" t="n"/>
       <c r="K204" s="11" t="n"/>
-      <c r="L204" s="11" t="n"/>
-      <c r="M204" s="11" t="n"/>
     </row>
     <row r="205" ht="15.75" customHeight="1" s="16">
       <c r="A205" s="4">
@@ -7614,8 +6958,6 @@
       <c r="I205" s="11" t="n"/>
       <c r="J205" s="11" t="n"/>
       <c r="K205" s="11" t="n"/>
-      <c r="L205" s="11" t="n"/>
-      <c r="M205" s="11" t="n"/>
     </row>
     <row r="206" ht="15.75" customHeight="1" s="16">
       <c r="A206" s="4">
@@ -7644,8 +6986,6 @@
       <c r="I206" s="11" t="n"/>
       <c r="J206" s="11" t="n"/>
       <c r="K206" s="11" t="n"/>
-      <c r="L206" s="11" t="n"/>
-      <c r="M206" s="11" t="n"/>
     </row>
     <row r="207" ht="15.75" customHeight="1" s="16">
       <c r="A207" s="4">
@@ -7674,8 +7014,6 @@
       <c r="I207" s="11" t="n"/>
       <c r="J207" s="11" t="n"/>
       <c r="K207" s="11" t="n"/>
-      <c r="L207" s="11" t="n"/>
-      <c r="M207" s="11" t="n"/>
     </row>
     <row r="208" ht="15.75" customHeight="1" s="16">
       <c r="A208" s="4">
@@ -7704,8 +7042,6 @@
       <c r="I208" s="11" t="n"/>
       <c r="J208" s="11" t="n"/>
       <c r="K208" s="11" t="n"/>
-      <c r="L208" s="11" t="n"/>
-      <c r="M208" s="11" t="n"/>
     </row>
     <row r="209" ht="15.75" customHeight="1" s="16">
       <c r="A209" s="4">
@@ -7734,8 +7070,6 @@
       <c r="I209" s="11" t="n"/>
       <c r="J209" s="11" t="n"/>
       <c r="K209" s="11" t="n"/>
-      <c r="L209" s="11" t="n"/>
-      <c r="M209" s="11" t="n"/>
     </row>
     <row r="210" ht="15.75" customHeight="1" s="16">
       <c r="A210" s="4">
@@ -7764,8 +7098,6 @@
       <c r="I210" s="11" t="n"/>
       <c r="J210" s="11" t="n"/>
       <c r="K210" s="11" t="n"/>
-      <c r="L210" s="11" t="n"/>
-      <c r="M210" s="11" t="n"/>
     </row>
     <row r="211" ht="15.75" customHeight="1" s="16">
       <c r="A211" s="4">
@@ -7794,8 +7126,6 @@
       <c r="I211" s="11" t="n"/>
       <c r="J211" s="11" t="n"/>
       <c r="K211" s="11" t="n"/>
-      <c r="L211" s="11" t="n"/>
-      <c r="M211" s="11" t="n"/>
     </row>
     <row r="212" ht="15.75" customHeight="1" s="16">
       <c r="A212" s="4">
@@ -7824,8 +7154,6 @@
       <c r="I212" s="11" t="n"/>
       <c r="J212" s="11" t="n"/>
       <c r="K212" s="11" t="n"/>
-      <c r="L212" s="11" t="n"/>
-      <c r="M212" s="11" t="n"/>
     </row>
     <row r="213" ht="15.75" customHeight="1" s="16">
       <c r="A213" s="4">
@@ -7854,8 +7182,6 @@
       <c r="I213" s="11" t="n"/>
       <c r="J213" s="11" t="n"/>
       <c r="K213" s="11" t="n"/>
-      <c r="L213" s="11" t="n"/>
-      <c r="M213" s="11" t="n"/>
     </row>
     <row r="214" ht="15.75" customHeight="1" s="16">
       <c r="A214" s="4">
@@ -7884,8 +7210,6 @@
       <c r="I214" s="11" t="n"/>
       <c r="J214" s="11" t="n"/>
       <c r="K214" s="11" t="n"/>
-      <c r="L214" s="11" t="n"/>
-      <c r="M214" s="11" t="n"/>
     </row>
     <row r="215" ht="15.75" customHeight="1" s="16">
       <c r="A215" s="4">
@@ -7914,8 +7238,6 @@
       <c r="I215" s="11" t="n"/>
       <c r="J215" s="11" t="n"/>
       <c r="K215" s="11" t="n"/>
-      <c r="L215" s="11" t="n"/>
-      <c r="M215" s="11" t="n"/>
     </row>
     <row r="216" ht="15.75" customHeight="1" s="16">
       <c r="A216" s="4">
@@ -7944,8 +7266,6 @@
       <c r="I216" s="11" t="n"/>
       <c r="J216" s="11" t="n"/>
       <c r="K216" s="11" t="n"/>
-      <c r="L216" s="11" t="n"/>
-      <c r="M216" s="11" t="n"/>
     </row>
     <row r="217" ht="15.75" customHeight="1" s="16">
       <c r="A217" s="4">
@@ -7974,8 +7294,6 @@
       <c r="I217" s="11" t="n"/>
       <c r="J217" s="11" t="n"/>
       <c r="K217" s="11" t="n"/>
-      <c r="L217" s="11" t="n"/>
-      <c r="M217" s="11" t="n"/>
     </row>
     <row r="218" ht="15.75" customHeight="1" s="16">
       <c r="A218" s="4">
@@ -8004,8 +7322,6 @@
       <c r="I218" s="11" t="n"/>
       <c r="J218" s="11" t="n"/>
       <c r="K218" s="11" t="n"/>
-      <c r="L218" s="11" t="n"/>
-      <c r="M218" s="11" t="n"/>
     </row>
     <row r="219" ht="15.75" customHeight="1" s="16">
       <c r="A219" s="4">
@@ -8030,8 +7346,6 @@
       <c r="I219" s="11" t="n"/>
       <c r="J219" s="11" t="n"/>
       <c r="K219" s="11" t="n"/>
-      <c r="L219" s="11" t="n"/>
-      <c r="M219" s="11" t="n"/>
     </row>
     <row r="220" ht="15.75" customHeight="1" s="16">
       <c r="A220" s="4">
@@ -8060,8 +7374,6 @@
       <c r="I220" s="11" t="n"/>
       <c r="J220" s="11" t="n"/>
       <c r="K220" s="11" t="n"/>
-      <c r="L220" s="11" t="n"/>
-      <c r="M220" s="11" t="n"/>
     </row>
     <row r="221" ht="15.75" customHeight="1" s="16">
       <c r="A221" s="4">
@@ -8090,8 +7402,6 @@
       <c r="I221" s="11" t="n"/>
       <c r="J221" s="11" t="n"/>
       <c r="K221" s="11" t="n"/>
-      <c r="L221" s="11" t="n"/>
-      <c r="M221" s="11" t="n"/>
     </row>
     <row r="222" ht="15.75" customHeight="1" s="16">
       <c r="A222" s="4">
@@ -8120,8 +7430,6 @@
       <c r="I222" s="11" t="n"/>
       <c r="J222" s="11" t="n"/>
       <c r="K222" s="11" t="n"/>
-      <c r="L222" s="11" t="n"/>
-      <c r="M222" s="11" t="n"/>
     </row>
     <row r="223" ht="15.75" customHeight="1" s="16">
       <c r="A223" s="4">
@@ -8150,8 +7458,6 @@
       <c r="I223" s="11" t="n"/>
       <c r="J223" s="11" t="n"/>
       <c r="K223" s="11" t="n"/>
-      <c r="L223" s="11" t="n"/>
-      <c r="M223" s="11" t="n"/>
     </row>
     <row r="224" ht="15.75" customHeight="1" s="16">
       <c r="A224" s="4">
@@ -8180,8 +7486,6 @@
       <c r="I224" s="11" t="n"/>
       <c r="J224" s="11" t="n"/>
       <c r="K224" s="11" t="n"/>
-      <c r="L224" s="11" t="n"/>
-      <c r="M224" s="11" t="n"/>
     </row>
     <row r="225" ht="15.75" customHeight="1" s="16">
       <c r="A225" s="4">
@@ -8210,8 +7514,6 @@
       <c r="I225" s="11" t="n"/>
       <c r="J225" s="11" t="n"/>
       <c r="K225" s="11" t="n"/>
-      <c r="L225" s="11" t="n"/>
-      <c r="M225" s="11" t="n"/>
     </row>
     <row r="226" ht="15.75" customHeight="1" s="16">
       <c r="A226" s="4">
@@ -8240,8 +7542,6 @@
       <c r="I226" s="11" t="n"/>
       <c r="J226" s="11" t="n"/>
       <c r="K226" s="11" t="n"/>
-      <c r="L226" s="11" t="n"/>
-      <c r="M226" s="11" t="n"/>
     </row>
     <row r="227" ht="15.75" customHeight="1" s="16">
       <c r="A227" s="4">
@@ -8270,8 +7570,6 @@
       <c r="I227" s="11" t="n"/>
       <c r="J227" s="11" t="n"/>
       <c r="K227" s="11" t="n"/>
-      <c r="L227" s="11" t="n"/>
-      <c r="M227" s="11" t="n"/>
     </row>
     <row r="228" ht="15.75" customHeight="1" s="16">
       <c r="A228" s="4">
@@ -8300,8 +7598,6 @@
       <c r="I228" s="11" t="n"/>
       <c r="J228" s="11" t="n"/>
       <c r="K228" s="11" t="n"/>
-      <c r="L228" s="11" t="n"/>
-      <c r="M228" s="11" t="n"/>
     </row>
     <row r="229" ht="15.75" customHeight="1" s="16">
       <c r="A229" s="4">
@@ -8330,8 +7626,6 @@
       <c r="I229" s="11" t="n"/>
       <c r="J229" s="11" t="n"/>
       <c r="K229" s="11" t="n"/>
-      <c r="L229" s="11" t="n"/>
-      <c r="M229" s="11" t="n"/>
     </row>
     <row r="230" ht="15.75" customHeight="1" s="16">
       <c r="A230" s="4">
@@ -8360,8 +7654,6 @@
       <c r="I230" s="11" t="n"/>
       <c r="J230" s="11" t="n"/>
       <c r="K230" s="11" t="n"/>
-      <c r="L230" s="11" t="n"/>
-      <c r="M230" s="11" t="n"/>
     </row>
     <row r="231" ht="15.75" customHeight="1" s="16">
       <c r="A231" s="4">
@@ -8390,8 +7682,6 @@
       <c r="I231" s="11" t="n"/>
       <c r="J231" s="11" t="n"/>
       <c r="K231" s="11" t="n"/>
-      <c r="L231" s="11" t="n"/>
-      <c r="M231" s="11" t="n"/>
     </row>
     <row r="232" ht="15.75" customHeight="1" s="16">
       <c r="A232" s="4">
@@ -8420,8 +7710,6 @@
       <c r="I232" s="11" t="n"/>
       <c r="J232" s="11" t="n"/>
       <c r="K232" s="11" t="n"/>
-      <c r="L232" s="11" t="n"/>
-      <c r="M232" s="11" t="n"/>
     </row>
     <row r="233" ht="15.75" customHeight="1" s="16">
       <c r="A233" s="4">
@@ -8450,8 +7738,6 @@
       <c r="I233" s="11" t="n"/>
       <c r="J233" s="11" t="n"/>
       <c r="K233" s="11" t="n"/>
-      <c r="L233" s="11" t="n"/>
-      <c r="M233" s="11" t="n"/>
     </row>
     <row r="234" ht="15.75" customHeight="1" s="16">
       <c r="A234" s="4">
@@ -8480,8 +7766,6 @@
       <c r="I234" s="11" t="n"/>
       <c r="J234" s="11" t="n"/>
       <c r="K234" s="11" t="n"/>
-      <c r="L234" s="11" t="n"/>
-      <c r="M234" s="11" t="n"/>
     </row>
     <row r="235" ht="15.75" customHeight="1" s="16">
       <c r="A235" s="4">
@@ -8510,8 +7794,6 @@
       <c r="I235" s="11" t="n"/>
       <c r="J235" s="11" t="n"/>
       <c r="K235" s="11" t="n"/>
-      <c r="L235" s="11" t="n"/>
-      <c r="M235" s="11" t="n"/>
     </row>
     <row r="236" ht="15.75" customHeight="1" s="16">
       <c r="A236" s="4">
@@ -8540,8 +7822,6 @@
       <c r="I236" s="11" t="n"/>
       <c r="J236" s="11" t="n"/>
       <c r="K236" s="11" t="n"/>
-      <c r="L236" s="11" t="n"/>
-      <c r="M236" s="11" t="n"/>
     </row>
     <row r="237" ht="15.75" customHeight="1" s="16">
       <c r="A237" s="4">
@@ -8570,8 +7850,6 @@
       <c r="I237" s="11" t="n"/>
       <c r="J237" s="11" t="n"/>
       <c r="K237" s="11" t="n"/>
-      <c r="L237" s="11" t="n"/>
-      <c r="M237" s="11" t="n"/>
     </row>
     <row r="238" ht="15.75" customHeight="1" s="16">
       <c r="A238" s="4">
@@ -8600,8 +7878,6 @@
       <c r="I238" s="11" t="n"/>
       <c r="J238" s="11" t="n"/>
       <c r="K238" s="11" t="n"/>
-      <c r="L238" s="11" t="n"/>
-      <c r="M238" s="11" t="n"/>
     </row>
     <row r="239" ht="15.75" customHeight="1" s="16">
       <c r="A239" s="4">
@@ -8630,8 +7906,6 @@
       <c r="I239" s="11" t="n"/>
       <c r="J239" s="11" t="n"/>
       <c r="K239" s="11" t="n"/>
-      <c r="L239" s="11" t="n"/>
-      <c r="M239" s="11" t="n"/>
     </row>
     <row r="240" ht="15.75" customHeight="1" s="16">
       <c r="A240" s="4">
@@ -8660,8 +7934,6 @@
       <c r="I240" s="11" t="n"/>
       <c r="J240" s="11" t="n"/>
       <c r="K240" s="11" t="n"/>
-      <c r="L240" s="11" t="n"/>
-      <c r="M240" s="11" t="n"/>
     </row>
     <row r="241" ht="15.75" customHeight="1" s="16">
       <c r="A241" s="4">
@@ -8690,8 +7962,6 @@
       <c r="I241" s="11" t="n"/>
       <c r="J241" s="11" t="n"/>
       <c r="K241" s="11" t="n"/>
-      <c r="L241" s="11" t="n"/>
-      <c r="M241" s="11" t="n"/>
     </row>
     <row r="242" ht="15.75" customHeight="1" s="16">
       <c r="A242" s="4">
@@ -8720,8 +7990,6 @@
       <c r="I242" s="11" t="n"/>
       <c r="J242" s="11" t="n"/>
       <c r="K242" s="11" t="n"/>
-      <c r="L242" s="11" t="n"/>
-      <c r="M242" s="11" t="n"/>
     </row>
     <row r="243" ht="15.75" customHeight="1" s="16">
       <c r="A243" s="4">
@@ -8750,8 +8018,6 @@
       <c r="I243" s="11" t="n"/>
       <c r="J243" s="11" t="n"/>
       <c r="K243" s="11" t="n"/>
-      <c r="L243" s="11" t="n"/>
-      <c r="M243" s="11" t="n"/>
     </row>
     <row r="244" ht="15.75" customHeight="1" s="16">
       <c r="A244" s="4">
@@ -8780,8 +8046,6 @@
       <c r="I244" s="11" t="n"/>
       <c r="J244" s="11" t="n"/>
       <c r="K244" s="11" t="n"/>
-      <c r="L244" s="11" t="n"/>
-      <c r="M244" s="11" t="n"/>
     </row>
     <row r="245" ht="15.75" customHeight="1" s="16">
       <c r="A245" s="4">
@@ -8810,8 +8074,6 @@
       <c r="I245" s="11" t="n"/>
       <c r="J245" s="11" t="n"/>
       <c r="K245" s="11" t="n"/>
-      <c r="L245" s="11" t="n"/>
-      <c r="M245" s="11" t="n"/>
     </row>
     <row r="246" ht="15.75" customHeight="1" s="16">
       <c r="A246" s="4">
@@ -8840,8 +8102,6 @@
       <c r="I246" s="11" t="n"/>
       <c r="J246" s="11" t="n"/>
       <c r="K246" s="11" t="n"/>
-      <c r="L246" s="11" t="n"/>
-      <c r="M246" s="11" t="n"/>
     </row>
     <row r="247" ht="15.75" customHeight="1" s="16">
       <c r="A247" s="4">
@@ -8870,8 +8130,6 @@
       <c r="I247" s="11" t="n"/>
       <c r="J247" s="11" t="n"/>
       <c r="K247" s="11" t="n"/>
-      <c r="L247" s="11" t="n"/>
-      <c r="M247" s="11" t="n"/>
     </row>
     <row r="248" ht="15.75" customHeight="1" s="16">
       <c r="A248" s="4">
@@ -8900,8 +8158,6 @@
       <c r="I248" s="11" t="n"/>
       <c r="J248" s="11" t="n"/>
       <c r="K248" s="11" t="n"/>
-      <c r="L248" s="11" t="n"/>
-      <c r="M248" s="11" t="n"/>
     </row>
     <row r="249" ht="15.75" customHeight="1" s="16">
       <c r="A249" s="4">
@@ -8930,8 +8186,6 @@
       <c r="I249" s="11" t="n"/>
       <c r="J249" s="11" t="n"/>
       <c r="K249" s="11" t="n"/>
-      <c r="L249" s="11" t="n"/>
-      <c r="M249" s="11" t="n"/>
     </row>
     <row r="250" ht="15.75" customHeight="1" s="16">
       <c r="A250" s="4">
@@ -8960,8 +8214,6 @@
       <c r="I250" s="11" t="n"/>
       <c r="J250" s="11" t="n"/>
       <c r="K250" s="11" t="n"/>
-      <c r="L250" s="11" t="n"/>
-      <c r="M250" s="11" t="n"/>
     </row>
     <row r="251" ht="15.75" customHeight="1" s="16">
       <c r="A251" s="4">
@@ -8990,8 +8242,6 @@
       <c r="I251" s="11" t="n"/>
       <c r="J251" s="11" t="n"/>
       <c r="K251" s="11" t="n"/>
-      <c r="L251" s="11" t="n"/>
-      <c r="M251" s="11" t="n"/>
     </row>
     <row r="252" ht="15.75" customHeight="1" s="16">
       <c r="A252" s="4">
@@ -9020,8 +8270,6 @@
       <c r="I252" s="11" t="n"/>
       <c r="J252" s="11" t="n"/>
       <c r="K252" s="11" t="n"/>
-      <c r="L252" s="11" t="n"/>
-      <c r="M252" s="11" t="n"/>
     </row>
     <row r="253" ht="15.75" customHeight="1" s="16">
       <c r="A253" s="4">
@@ -9050,8 +8298,6 @@
       <c r="I253" s="11" t="n"/>
       <c r="J253" s="11" t="n"/>
       <c r="K253" s="11" t="n"/>
-      <c r="L253" s="11" t="n"/>
-      <c r="M253" s="11" t="n"/>
     </row>
     <row r="254" ht="15.75" customHeight="1" s="16">
       <c r="A254" s="4">
@@ -9080,8 +8326,6 @@
       <c r="I254" s="11" t="n"/>
       <c r="J254" s="11" t="n"/>
       <c r="K254" s="11" t="n"/>
-      <c r="L254" s="11" t="n"/>
-      <c r="M254" s="11" t="n"/>
     </row>
     <row r="255" ht="15.75" customHeight="1" s="16">
       <c r="A255" s="4">
@@ -9110,8 +8354,6 @@
       <c r="I255" s="11" t="n"/>
       <c r="J255" s="11" t="n"/>
       <c r="K255" s="11" t="n"/>
-      <c r="L255" s="11" t="n"/>
-      <c r="M255" s="11" t="n"/>
     </row>
     <row r="256" ht="15.75" customHeight="1" s="16">
       <c r="A256" s="4">
@@ -9140,8 +8382,6 @@
       <c r="I256" s="11" t="n"/>
       <c r="J256" s="11" t="n"/>
       <c r="K256" s="11" t="n"/>
-      <c r="L256" s="11" t="n"/>
-      <c r="M256" s="11" t="n"/>
     </row>
     <row r="257" ht="15.75" customHeight="1" s="16">
       <c r="A257" s="4">
@@ -9170,8 +8410,6 @@
       <c r="I257" s="11" t="n"/>
       <c r="J257" s="11" t="n"/>
       <c r="K257" s="11" t="n"/>
-      <c r="L257" s="11" t="n"/>
-      <c r="M257" s="11" t="n"/>
     </row>
     <row r="258" ht="15.75" customHeight="1" s="16">
       <c r="A258" s="4">
@@ -9200,8 +8438,8 @@
       <c r="I258" s="11" t="n"/>
       <c r="J258" s="11" t="n"/>
       <c r="K258" s="11" t="n"/>
-      <c r="L258" s="11" t="n"/>
-      <c r="M258" s="11" t="n"/>
+      <c r="L258" s="14" t="n"/>
+      <c r="M258" s="14" t="n"/>
       <c r="N258" s="14" t="n"/>
       <c r="O258" s="14" t="n"/>
       <c r="P258" s="14" t="n"/>
@@ -9211,8 +8449,6 @@
       <c r="T258" s="14" t="n"/>
       <c r="U258" s="14" t="n"/>
       <c r="V258" s="14" t="n"/>
-      <c r="W258" s="14" t="n"/>
-      <c r="X258" s="14" t="n"/>
     </row>
     <row r="259" ht="15.75" customHeight="1" s="16">
       <c r="A259" s="4">
@@ -9241,8 +8477,8 @@
       <c r="I259" s="11" t="n"/>
       <c r="J259" s="11" t="n"/>
       <c r="K259" s="11" t="n"/>
-      <c r="L259" s="11" t="n"/>
-      <c r="M259" s="11" t="n"/>
+      <c r="L259" s="14" t="n"/>
+      <c r="M259" s="14" t="n"/>
       <c r="N259" s="14" t="n"/>
       <c r="O259" s="14" t="n"/>
       <c r="P259" s="14" t="n"/>
@@ -9252,8 +8488,6 @@
       <c r="T259" s="14" t="n"/>
       <c r="U259" s="14" t="n"/>
       <c r="V259" s="14" t="n"/>
-      <c r="W259" s="14" t="n"/>
-      <c r="X259" s="14" t="n"/>
     </row>
     <row r="260" ht="15.75" customHeight="1" s="16">
       <c r="A260" s="4">
@@ -9282,8 +8516,8 @@
       <c r="I260" s="11" t="n"/>
       <c r="J260" s="11" t="n"/>
       <c r="K260" s="11" t="n"/>
-      <c r="L260" s="11" t="n"/>
-      <c r="M260" s="11" t="n"/>
+      <c r="L260" s="14" t="n"/>
+      <c r="M260" s="14" t="n"/>
       <c r="N260" s="14" t="n"/>
       <c r="O260" s="14" t="n"/>
       <c r="P260" s="14" t="n"/>
@@ -9293,8 +8527,6 @@
       <c r="T260" s="14" t="n"/>
       <c r="U260" s="14" t="n"/>
       <c r="V260" s="14" t="n"/>
-      <c r="W260" s="14" t="n"/>
-      <c r="X260" s="14" t="n"/>
     </row>
     <row r="261" ht="15.75" customHeight="1" s="16">
       <c r="A261" s="4">
@@ -9323,8 +8555,8 @@
       <c r="I261" s="11" t="n"/>
       <c r="J261" s="11" t="n"/>
       <c r="K261" s="11" t="n"/>
-      <c r="L261" s="11" t="n"/>
-      <c r="M261" s="11" t="n"/>
+      <c r="L261" s="14" t="n"/>
+      <c r="M261" s="14" t="n"/>
       <c r="N261" s="14" t="n"/>
       <c r="O261" s="14" t="n"/>
       <c r="P261" s="14" t="n"/>
@@ -9334,8 +8566,6 @@
       <c r="T261" s="14" t="n"/>
       <c r="U261" s="14" t="n"/>
       <c r="V261" s="14" t="n"/>
-      <c r="W261" s="14" t="n"/>
-      <c r="X261" s="14" t="n"/>
     </row>
     <row r="262" ht="15.75" customHeight="1" s="16">
       <c r="A262" s="4">
@@ -9364,8 +8594,8 @@
       <c r="I262" s="11" t="n"/>
       <c r="J262" s="11" t="n"/>
       <c r="K262" s="11" t="n"/>
-      <c r="L262" s="11" t="n"/>
-      <c r="M262" s="11" t="n"/>
+      <c r="L262" s="14" t="n"/>
+      <c r="M262" s="14" t="n"/>
       <c r="N262" s="14" t="n"/>
       <c r="O262" s="14" t="n"/>
       <c r="P262" s="14" t="n"/>
@@ -9375,8 +8605,6 @@
       <c r="T262" s="14" t="n"/>
       <c r="U262" s="14" t="n"/>
       <c r="V262" s="14" t="n"/>
-      <c r="W262" s="14" t="n"/>
-      <c r="X262" s="14" t="n"/>
     </row>
     <row r="263" ht="15.75" customHeight="1" s="16">
       <c r="A263" s="4">
@@ -9405,8 +8633,8 @@
       <c r="I263" s="11" t="n"/>
       <c r="J263" s="11" t="n"/>
       <c r="K263" s="11" t="n"/>
-      <c r="L263" s="11" t="n"/>
-      <c r="M263" s="11" t="n"/>
+      <c r="L263" s="14" t="n"/>
+      <c r="M263" s="14" t="n"/>
       <c r="N263" s="14" t="n"/>
       <c r="O263" s="14" t="n"/>
       <c r="P263" s="14" t="n"/>
@@ -9416,8 +8644,6 @@
       <c r="T263" s="14" t="n"/>
       <c r="U263" s="14" t="n"/>
       <c r="V263" s="14" t="n"/>
-      <c r="W263" s="14" t="n"/>
-      <c r="X263" s="14" t="n"/>
     </row>
     <row r="264" ht="15.75" customHeight="1" s="16">
       <c r="A264" s="4">
@@ -9446,8 +8672,8 @@
       <c r="I264" s="11" t="n"/>
       <c r="J264" s="11" t="n"/>
       <c r="K264" s="11" t="n"/>
-      <c r="L264" s="11" t="n"/>
-      <c r="M264" s="11" t="n"/>
+      <c r="L264" s="14" t="n"/>
+      <c r="M264" s="14" t="n"/>
       <c r="N264" s="14" t="n"/>
       <c r="O264" s="14" t="n"/>
       <c r="P264" s="14" t="n"/>
@@ -9457,8 +8683,6 @@
       <c r="T264" s="14" t="n"/>
       <c r="U264" s="14" t="n"/>
       <c r="V264" s="14" t="n"/>
-      <c r="W264" s="14" t="n"/>
-      <c r="X264" s="14" t="n"/>
     </row>
     <row r="265" ht="15.75" customHeight="1" s="16">
       <c r="A265" s="4">
@@ -9487,8 +8711,8 @@
       <c r="I265" s="11" t="n"/>
       <c r="J265" s="11" t="n"/>
       <c r="K265" s="11" t="n"/>
-      <c r="L265" s="11" t="n"/>
-      <c r="M265" s="11" t="n"/>
+      <c r="L265" s="14" t="n"/>
+      <c r="M265" s="14" t="n"/>
       <c r="N265" s="14" t="n"/>
       <c r="O265" s="14" t="n"/>
       <c r="P265" s="14" t="n"/>
@@ -9498,8 +8722,6 @@
       <c r="T265" s="14" t="n"/>
       <c r="U265" s="14" t="n"/>
       <c r="V265" s="14" t="n"/>
-      <c r="W265" s="14" t="n"/>
-      <c r="X265" s="14" t="n"/>
     </row>
     <row r="266" ht="15.75" customHeight="1" s="16">
       <c r="A266" s="4">
@@ -9528,8 +8750,8 @@
       <c r="I266" s="11" t="n"/>
       <c r="J266" s="11" t="n"/>
       <c r="K266" s="11" t="n"/>
-      <c r="L266" s="11" t="n"/>
-      <c r="M266" s="11" t="n"/>
+      <c r="L266" s="14" t="n"/>
+      <c r="M266" s="14" t="n"/>
       <c r="N266" s="14" t="n"/>
       <c r="O266" s="14" t="n"/>
       <c r="P266" s="14" t="n"/>
@@ -9539,8 +8761,6 @@
       <c r="T266" s="14" t="n"/>
       <c r="U266" s="14" t="n"/>
       <c r="V266" s="14" t="n"/>
-      <c r="W266" s="14" t="n"/>
-      <c r="X266" s="14" t="n"/>
     </row>
     <row r="267" ht="15.75" customHeight="1" s="16">
       <c r="A267" s="4">
@@ -9569,8 +8789,8 @@
       <c r="I267" s="11" t="n"/>
       <c r="J267" s="11" t="n"/>
       <c r="K267" s="11" t="n"/>
-      <c r="L267" s="11" t="n"/>
-      <c r="M267" s="11" t="n"/>
+      <c r="L267" s="14" t="n"/>
+      <c r="M267" s="14" t="n"/>
       <c r="N267" s="14" t="n"/>
       <c r="O267" s="14" t="n"/>
       <c r="P267" s="14" t="n"/>
@@ -9580,8 +8800,6 @@
       <c r="T267" s="14" t="n"/>
       <c r="U267" s="14" t="n"/>
       <c r="V267" s="14" t="n"/>
-      <c r="W267" s="14" t="n"/>
-      <c r="X267" s="14" t="n"/>
     </row>
     <row r="268" ht="15.75" customHeight="1" s="16">
       <c r="A268" s="4">
@@ -9610,8 +8828,8 @@
       <c r="I268" s="11" t="n"/>
       <c r="J268" s="11" t="n"/>
       <c r="K268" s="11" t="n"/>
-      <c r="L268" s="11" t="n"/>
-      <c r="M268" s="11" t="n"/>
+      <c r="L268" s="14" t="n"/>
+      <c r="M268" s="14" t="n"/>
       <c r="N268" s="14" t="n"/>
       <c r="O268" s="14" t="n"/>
       <c r="P268" s="14" t="n"/>
@@ -9621,8 +8839,6 @@
       <c r="T268" s="14" t="n"/>
       <c r="U268" s="14" t="n"/>
       <c r="V268" s="14" t="n"/>
-      <c r="W268" s="14" t="n"/>
-      <c r="X268" s="14" t="n"/>
     </row>
     <row r="269" ht="15.75" customHeight="1" s="16">
       <c r="A269" s="4">
@@ -9651,8 +8867,6 @@
       <c r="I269" s="11" t="n"/>
       <c r="J269" s="11" t="n"/>
       <c r="K269" s="11" t="n"/>
-      <c r="L269" s="11" t="n"/>
-      <c r="M269" s="11" t="n"/>
     </row>
     <row r="270" ht="15.75" customHeight="1" s="16">
       <c r="A270" s="4">
@@ -9681,8 +8895,6 @@
       <c r="I270" s="11" t="n"/>
       <c r="J270" s="11" t="n"/>
       <c r="K270" s="11" t="n"/>
-      <c r="L270" s="11" t="n"/>
-      <c r="M270" s="11" t="n"/>
     </row>
     <row r="271" ht="15.75" customHeight="1" s="16">
       <c r="A271" s="4">
@@ -9711,8 +8923,6 @@
       <c r="I271" s="11" t="n"/>
       <c r="J271" s="11" t="n"/>
       <c r="K271" s="11" t="n"/>
-      <c r="L271" s="11" t="n"/>
-      <c r="M271" s="11" t="n"/>
     </row>
     <row r="272" ht="15.75" customHeight="1" s="16">
       <c r="A272" s="4">
@@ -9741,8 +8951,6 @@
       <c r="I272" s="11" t="n"/>
       <c r="J272" s="11" t="n"/>
       <c r="K272" s="11" t="n"/>
-      <c r="L272" s="11" t="n"/>
-      <c r="M272" s="11" t="n"/>
     </row>
     <row r="273" ht="15.75" customHeight="1" s="16">
       <c r="A273" s="4">
@@ -9771,8 +8979,6 @@
       <c r="I273" s="11" t="n"/>
       <c r="J273" s="11" t="n"/>
       <c r="K273" s="11" t="n"/>
-      <c r="L273" s="11" t="n"/>
-      <c r="M273" s="11" t="n"/>
     </row>
     <row r="274" ht="15.75" customHeight="1" s="16">
       <c r="A274" s="4">
@@ -9801,8 +9007,6 @@
       <c r="I274" s="11" t="n"/>
       <c r="J274" s="11" t="n"/>
       <c r="K274" s="11" t="n"/>
-      <c r="L274" s="11" t="n"/>
-      <c r="M274" s="11" t="n"/>
     </row>
     <row r="275" ht="15.75" customHeight="1" s="16">
       <c r="A275" s="4">
@@ -9831,8 +9035,6 @@
       <c r="I275" s="11" t="n"/>
       <c r="J275" s="11" t="n"/>
       <c r="K275" s="11" t="n"/>
-      <c r="L275" s="11" t="n"/>
-      <c r="M275" s="11" t="n"/>
     </row>
     <row r="276" ht="15.75" customHeight="1" s="16">
       <c r="A276" s="4">
@@ -9861,8 +9063,6 @@
       <c r="I276" s="11" t="n"/>
       <c r="J276" s="11" t="n"/>
       <c r="K276" s="11" t="n"/>
-      <c r="L276" s="11" t="n"/>
-      <c r="M276" s="11" t="n"/>
     </row>
     <row r="277" ht="15.75" customHeight="1" s="16">
       <c r="A277" s="4">
@@ -9891,8 +9091,6 @@
       <c r="I277" s="11" t="n"/>
       <c r="J277" s="11" t="n"/>
       <c r="K277" s="11" t="n"/>
-      <c r="L277" s="11" t="n"/>
-      <c r="M277" s="11" t="n"/>
     </row>
     <row r="278" ht="15.75" customHeight="1" s="16">
       <c r="A278" s="4">
@@ -9921,8 +9119,6 @@
       <c r="I278" s="11" t="n"/>
       <c r="J278" s="11" t="n"/>
       <c r="K278" s="11" t="n"/>
-      <c r="L278" s="11" t="n"/>
-      <c r="M278" s="11" t="n"/>
     </row>
     <row r="279" ht="15.75" customHeight="1" s="16">
       <c r="A279" s="4">
@@ -9951,8 +9147,6 @@
       <c r="I279" s="11" t="n"/>
       <c r="J279" s="11" t="n"/>
       <c r="K279" s="11" t="n"/>
-      <c r="L279" s="11" t="n"/>
-      <c r="M279" s="11" t="n"/>
     </row>
     <row r="280" ht="15.75" customHeight="1" s="16">
       <c r="A280" s="4">
@@ -9981,8 +9175,6 @@
       <c r="I280" s="11" t="n"/>
       <c r="J280" s="11" t="n"/>
       <c r="K280" s="11" t="n"/>
-      <c r="L280" s="11" t="n"/>
-      <c r="M280" s="11" t="n"/>
     </row>
     <row r="281" ht="15.75" customHeight="1" s="16">
       <c r="A281" s="4">
@@ -10011,8 +9203,6 @@
       <c r="I281" s="11" t="n"/>
       <c r="J281" s="11" t="n"/>
       <c r="K281" s="11" t="n"/>
-      <c r="L281" s="11" t="n"/>
-      <c r="M281" s="11" t="n"/>
     </row>
     <row r="282" ht="15.75" customHeight="1" s="16">
       <c r="A282" s="4">
@@ -10041,8 +9231,6 @@
       <c r="I282" s="11" t="n"/>
       <c r="J282" s="11" t="n"/>
       <c r="K282" s="11" t="n"/>
-      <c r="L282" s="11" t="n"/>
-      <c r="M282" s="11" t="n"/>
     </row>
     <row r="283" ht="15.75" customHeight="1" s="16">
       <c r="A283" s="4">
@@ -10071,8 +9259,6 @@
       <c r="I283" s="11" t="n"/>
       <c r="J283" s="11" t="n"/>
       <c r="K283" s="11" t="n"/>
-      <c r="L283" s="11" t="n"/>
-      <c r="M283" s="11" t="n"/>
     </row>
     <row r="284" ht="15.75" customHeight="1" s="16">
       <c r="A284" s="4">
@@ -10101,8 +9287,6 @@
       <c r="I284" s="11" t="n"/>
       <c r="J284" s="11" t="n"/>
       <c r="K284" s="11" t="n"/>
-      <c r="L284" s="11" t="n"/>
-      <c r="M284" s="11" t="n"/>
     </row>
     <row r="285" ht="15.75" customHeight="1" s="16">
       <c r="A285" s="4">
@@ -10131,8 +9315,6 @@
       <c r="I285" s="11" t="n"/>
       <c r="J285" s="11" t="n"/>
       <c r="K285" s="11" t="n"/>
-      <c r="L285" s="11" t="n"/>
-      <c r="M285" s="11" t="n"/>
     </row>
     <row r="286" ht="15.75" customHeight="1" s="16">
       <c r="A286" s="4">
@@ -10161,8 +9343,6 @@
       <c r="I286" s="11" t="n"/>
       <c r="J286" s="11" t="n"/>
       <c r="K286" s="11" t="n"/>
-      <c r="L286" s="11" t="n"/>
-      <c r="M286" s="11" t="n"/>
     </row>
     <row r="287" ht="15.75" customHeight="1" s="16">
       <c r="A287" s="4">
@@ -10191,8 +9371,6 @@
       <c r="I287" s="11" t="n"/>
       <c r="J287" s="11" t="n"/>
       <c r="K287" s="11" t="n"/>
-      <c r="L287" s="11" t="n"/>
-      <c r="M287" s="11" t="n"/>
     </row>
     <row r="288" ht="15.75" customHeight="1" s="16">
       <c r="A288" s="4">
@@ -10221,8 +9399,6 @@
       <c r="I288" s="11" t="n"/>
       <c r="J288" s="11" t="n"/>
       <c r="K288" s="11" t="n"/>
-      <c r="L288" s="11" t="n"/>
-      <c r="M288" s="11" t="n"/>
     </row>
     <row r="289" ht="15.75" customHeight="1" s="16">
       <c r="A289" s="4">
@@ -10251,8 +9427,6 @@
       <c r="I289" s="11" t="n"/>
       <c r="J289" s="11" t="n"/>
       <c r="K289" s="11" t="n"/>
-      <c r="L289" s="11" t="n"/>
-      <c r="M289" s="11" t="n"/>
     </row>
     <row r="290" ht="15.75" customHeight="1" s="16">
       <c r="A290" s="4">
@@ -10281,8 +9455,6 @@
       <c r="I290" s="11" t="n"/>
       <c r="J290" s="11" t="n"/>
       <c r="K290" s="11" t="n"/>
-      <c r="L290" s="11" t="n"/>
-      <c r="M290" s="11" t="n"/>
     </row>
     <row r="291" ht="15.75" customHeight="1" s="16">
       <c r="A291" s="4">
@@ -10311,8 +9483,6 @@
       <c r="I291" s="11" t="n"/>
       <c r="J291" s="11" t="n"/>
       <c r="K291" s="11" t="n"/>
-      <c r="L291" s="11" t="n"/>
-      <c r="M291" s="11" t="n"/>
     </row>
     <row r="292" ht="15.75" customHeight="1" s="16">
       <c r="A292" s="4">
@@ -10341,8 +9511,6 @@
       <c r="I292" s="11" t="n"/>
       <c r="J292" s="11" t="n"/>
       <c r="K292" s="11" t="n"/>
-      <c r="L292" s="11" t="n"/>
-      <c r="M292" s="11" t="n"/>
     </row>
     <row r="293" ht="15.75" customHeight="1" s="16">
       <c r="A293" s="4">
@@ -10371,8 +9539,6 @@
       <c r="I293" s="11" t="n"/>
       <c r="J293" s="11" t="n"/>
       <c r="K293" s="11" t="n"/>
-      <c r="L293" s="11" t="n"/>
-      <c r="M293" s="11" t="n"/>
     </row>
     <row r="294" ht="15.75" customHeight="1" s="16">
       <c r="A294" s="4">
@@ -10401,8 +9567,6 @@
       <c r="I294" s="11" t="n"/>
       <c r="J294" s="11" t="n"/>
       <c r="K294" s="11" t="n"/>
-      <c r="L294" s="11" t="n"/>
-      <c r="M294" s="11" t="n"/>
     </row>
     <row r="295" ht="15.75" customHeight="1" s="16">
       <c r="A295" s="4">
@@ -10431,8 +9595,6 @@
       <c r="I295" s="11" t="n"/>
       <c r="J295" s="11" t="n"/>
       <c r="K295" s="11" t="n"/>
-      <c r="L295" s="11" t="n"/>
-      <c r="M295" s="11" t="n"/>
     </row>
     <row r="296" ht="15.75" customHeight="1" s="16">
       <c r="A296" s="4">
@@ -10461,8 +9623,6 @@
       <c r="I296" s="11" t="n"/>
       <c r="J296" s="11" t="n"/>
       <c r="K296" s="11" t="n"/>
-      <c r="L296" s="11" t="n"/>
-      <c r="M296" s="11" t="n"/>
     </row>
     <row r="297" ht="15.75" customHeight="1" s="16">
       <c r="A297" s="4">
@@ -10491,8 +9651,6 @@
       <c r="I297" s="11" t="n"/>
       <c r="J297" s="11" t="n"/>
       <c r="K297" s="11" t="n"/>
-      <c r="L297" s="11" t="n"/>
-      <c r="M297" s="11" t="n"/>
     </row>
     <row r="298" ht="15.75" customHeight="1" s="16">
       <c r="A298" s="4">
@@ -10521,8 +9679,6 @@
       <c r="I298" s="11" t="n"/>
       <c r="J298" s="11" t="n"/>
       <c r="K298" s="11" t="n"/>
-      <c r="L298" s="11" t="n"/>
-      <c r="M298" s="11" t="n"/>
     </row>
     <row r="299" ht="15.75" customHeight="1" s="16">
       <c r="A299" s="4">
@@ -10551,8 +9707,6 @@
       <c r="I299" s="11" t="n"/>
       <c r="J299" s="11" t="n"/>
       <c r="K299" s="11" t="n"/>
-      <c r="L299" s="11" t="n"/>
-      <c r="M299" s="11" t="n"/>
     </row>
     <row r="300" ht="15.75" customHeight="1" s="16">
       <c r="A300" s="4">
@@ -10581,8 +9735,6 @@
       <c r="I300" s="11" t="n"/>
       <c r="J300" s="11" t="n"/>
       <c r="K300" s="11" t="n"/>
-      <c r="L300" s="11" t="n"/>
-      <c r="M300" s="11" t="n"/>
     </row>
     <row r="301" ht="15.75" customHeight="1" s="16">
       <c r="A301" s="4">
@@ -10611,8 +9763,6 @@
       <c r="I301" s="11" t="n"/>
       <c r="J301" s="11" t="n"/>
       <c r="K301" s="11" t="n"/>
-      <c r="L301" s="11" t="n"/>
-      <c r="M301" s="11" t="n"/>
     </row>
     <row r="302" ht="15.75" customHeight="1" s="16">
       <c r="A302" s="4">
@@ -10641,8 +9791,6 @@
       <c r="I302" s="11" t="n"/>
       <c r="J302" s="11" t="n"/>
       <c r="K302" s="11" t="n"/>
-      <c r="L302" s="11" t="n"/>
-      <c r="M302" s="11" t="n"/>
     </row>
     <row r="303" ht="15.75" customHeight="1" s="16">
       <c r="A303" s="4">
@@ -10671,8 +9819,6 @@
       <c r="I303" s="11" t="n"/>
       <c r="J303" s="11" t="n"/>
       <c r="K303" s="11" t="n"/>
-      <c r="L303" s="11" t="n"/>
-      <c r="M303" s="11" t="n"/>
     </row>
     <row r="304" ht="15.75" customHeight="1" s="16">
       <c r="A304" s="4">
@@ -10701,8 +9847,6 @@
       <c r="I304" s="11" t="n"/>
       <c r="J304" s="11" t="n"/>
       <c r="K304" s="11" t="n"/>
-      <c r="L304" s="11" t="n"/>
-      <c r="M304" s="11" t="n"/>
     </row>
     <row r="305" ht="15.75" customHeight="1" s="16">
       <c r="A305" s="4">
@@ -10731,8 +9875,6 @@
       <c r="I305" s="11" t="n"/>
       <c r="J305" s="11" t="n"/>
       <c r="K305" s="11" t="n"/>
-      <c r="L305" s="11" t="n"/>
-      <c r="M305" s="11" t="n"/>
     </row>
     <row r="306" ht="15.75" customHeight="1" s="16">
       <c r="A306" s="4">
@@ -10761,8 +9903,6 @@
       <c r="I306" s="11" t="n"/>
       <c r="J306" s="11" t="n"/>
       <c r="K306" s="11" t="n"/>
-      <c r="L306" s="11" t="n"/>
-      <c r="M306" s="11" t="n"/>
     </row>
     <row r="307" ht="15.75" customHeight="1" s="16">
       <c r="A307" s="4">
@@ -10791,8 +9931,6 @@
       <c r="I307" s="11" t="n"/>
       <c r="J307" s="11" t="n"/>
       <c r="K307" s="11" t="n"/>
-      <c r="L307" s="11" t="n"/>
-      <c r="M307" s="11" t="n"/>
     </row>
     <row r="308" ht="15.75" customHeight="1" s="16">
       <c r="A308" s="4">
@@ -10821,8 +9959,6 @@
       <c r="I308" s="11" t="n"/>
       <c r="J308" s="11" t="n"/>
       <c r="K308" s="11" t="n"/>
-      <c r="L308" s="11" t="n"/>
-      <c r="M308" s="11" t="n"/>
     </row>
     <row r="309" ht="15.75" customHeight="1" s="16">
       <c r="A309" s="4">
@@ -10851,8 +9987,6 @@
       <c r="I309" s="11" t="n"/>
       <c r="J309" s="11" t="n"/>
       <c r="K309" s="11" t="n"/>
-      <c r="L309" s="11" t="n"/>
-      <c r="M309" s="11" t="n"/>
     </row>
     <row r="310" ht="15.75" customHeight="1" s="16">
       <c r="A310" s="4">
@@ -10881,8 +10015,6 @@
       <c r="I310" s="11" t="n"/>
       <c r="J310" s="11" t="n"/>
       <c r="K310" s="11" t="n"/>
-      <c r="L310" s="11" t="n"/>
-      <c r="M310" s="11" t="n"/>
     </row>
     <row r="311" ht="15.75" customHeight="1" s="16">
       <c r="A311" s="4">
@@ -10911,8 +10043,6 @@
       <c r="I311" s="11" t="n"/>
       <c r="J311" s="11" t="n"/>
       <c r="K311" s="11" t="n"/>
-      <c r="L311" s="11" t="n"/>
-      <c r="M311" s="11" t="n"/>
     </row>
     <row r="312" ht="15.75" customHeight="1" s="16">
       <c r="A312" s="4">
@@ -10941,8 +10071,6 @@
       <c r="I312" s="11" t="n"/>
       <c r="J312" s="11" t="n"/>
       <c r="K312" s="11" t="n"/>
-      <c r="L312" s="11" t="n"/>
-      <c r="M312" s="11" t="n"/>
     </row>
     <row r="313" ht="15.75" customHeight="1" s="16">
       <c r="A313" s="4">
@@ -10971,8 +10099,6 @@
       <c r="I313" s="11" t="n"/>
       <c r="J313" s="11" t="n"/>
       <c r="K313" s="11" t="n"/>
-      <c r="L313" s="11" t="n"/>
-      <c r="M313" s="11" t="n"/>
     </row>
     <row r="314" ht="15.75" customHeight="1" s="16">
       <c r="A314" s="4">
@@ -11001,8 +10127,6 @@
       <c r="I314" s="11" t="n"/>
       <c r="J314" s="11" t="n"/>
       <c r="K314" s="11" t="n"/>
-      <c r="L314" s="11" t="n"/>
-      <c r="M314" s="11" t="n"/>
     </row>
     <row r="315" ht="15.75" customHeight="1" s="16">
       <c r="A315" s="4">
@@ -11031,8 +10155,6 @@
       <c r="I315" s="11" t="n"/>
       <c r="J315" s="11" t="n"/>
       <c r="K315" s="11" t="n"/>
-      <c r="L315" s="11" t="n"/>
-      <c r="M315" s="11" t="n"/>
     </row>
     <row r="316" ht="15.75" customHeight="1" s="16">
       <c r="A316" s="4">
@@ -11061,8 +10183,6 @@
       <c r="I316" s="11" t="n"/>
       <c r="J316" s="11" t="n"/>
       <c r="K316" s="11" t="n"/>
-      <c r="L316" s="11" t="n"/>
-      <c r="M316" s="11" t="n"/>
     </row>
     <row r="317" ht="15.75" customHeight="1" s="16">
       <c r="A317" s="4">
@@ -11091,8 +10211,6 @@
       <c r="I317" s="11" t="n"/>
       <c r="J317" s="11" t="n"/>
       <c r="K317" s="11" t="n"/>
-      <c r="L317" s="11" t="n"/>
-      <c r="M317" s="11" t="n"/>
     </row>
     <row r="318" ht="15.75" customHeight="1" s="16">
       <c r="A318" s="4">
@@ -11121,8 +10239,6 @@
       <c r="I318" s="11" t="n"/>
       <c r="J318" s="11" t="n"/>
       <c r="K318" s="11" t="n"/>
-      <c r="L318" s="11" t="n"/>
-      <c r="M318" s="11" t="n"/>
     </row>
     <row r="319" ht="15.75" customHeight="1" s="16">
       <c r="A319" s="4">
@@ -11151,8 +10267,6 @@
       <c r="I319" s="11" t="n"/>
       <c r="J319" s="11" t="n"/>
       <c r="K319" s="11" t="n"/>
-      <c r="L319" s="11" t="n"/>
-      <c r="M319" s="11" t="n"/>
     </row>
     <row r="320" ht="15.75" customHeight="1" s="16">
       <c r="A320" s="4">
@@ -11181,8 +10295,6 @@
       <c r="I320" s="11" t="n"/>
       <c r="J320" s="11" t="n"/>
       <c r="K320" s="11" t="n"/>
-      <c r="L320" s="11" t="n"/>
-      <c r="M320" s="11" t="n"/>
     </row>
     <row r="321" ht="15.75" customHeight="1" s="16">
       <c r="A321" s="4">
@@ -11211,8 +10323,6 @@
       <c r="I321" s="11" t="n"/>
       <c r="J321" s="11" t="n"/>
       <c r="K321" s="11" t="n"/>
-      <c r="L321" s="11" t="n"/>
-      <c r="M321" s="11" t="n"/>
     </row>
     <row r="322" ht="15.75" customHeight="1" s="16">
       <c r="A322" s="4">
@@ -11241,8 +10351,6 @@
       <c r="I322" s="11" t="n"/>
       <c r="J322" s="11" t="n"/>
       <c r="K322" s="11" t="n"/>
-      <c r="L322" s="11" t="n"/>
-      <c r="M322" s="11" t="n"/>
     </row>
     <row r="323" ht="15.75" customHeight="1" s="16">
       <c r="A323" s="4">
@@ -11271,8 +10379,6 @@
       <c r="I323" s="11" t="n"/>
       <c r="J323" s="11" t="n"/>
       <c r="K323" s="11" t="n"/>
-      <c r="L323" s="11" t="n"/>
-      <c r="M323" s="11" t="n"/>
     </row>
     <row r="324" ht="15.75" customHeight="1" s="16">
       <c r="A324" s="4">
@@ -11301,8 +10407,6 @@
       <c r="I324" s="11" t="n"/>
       <c r="J324" s="11" t="n"/>
       <c r="K324" s="11" t="n"/>
-      <c r="L324" s="11" t="n"/>
-      <c r="M324" s="11" t="n"/>
     </row>
     <row r="325" ht="15.75" customHeight="1" s="16">
       <c r="A325" s="4">
@@ -11331,8 +10435,6 @@
       <c r="I325" s="11" t="n"/>
       <c r="J325" s="11" t="n"/>
       <c r="K325" s="11" t="n"/>
-      <c r="L325" s="11" t="n"/>
-      <c r="M325" s="11" t="n"/>
     </row>
     <row r="326" ht="15.75" customHeight="1" s="16">
       <c r="A326" s="4">
@@ -11361,8 +10463,6 @@
       <c r="I326" s="11" t="n"/>
       <c r="J326" s="11" t="n"/>
       <c r="K326" s="11" t="n"/>
-      <c r="L326" s="11" t="n"/>
-      <c r="M326" s="11" t="n"/>
     </row>
     <row r="327" ht="15.75" customHeight="1" s="16">
       <c r="A327" s="4">
@@ -11391,8 +10491,6 @@
       <c r="I327" s="11" t="n"/>
       <c r="J327" s="11" t="n"/>
       <c r="K327" s="11" t="n"/>
-      <c r="L327" s="11" t="n"/>
-      <c r="M327" s="11" t="n"/>
     </row>
     <row r="328" ht="15.75" customHeight="1" s="16">
       <c r="A328" s="4">
@@ -11421,8 +10519,6 @@
       <c r="I328" s="11" t="n"/>
       <c r="J328" s="11" t="n"/>
       <c r="K328" s="11" t="n"/>
-      <c r="L328" s="11" t="n"/>
-      <c r="M328" s="11" t="n"/>
     </row>
     <row r="329" ht="15.75" customHeight="1" s="16">
       <c r="A329" s="4">
@@ -11451,8 +10547,6 @@
       <c r="I329" s="11" t="n"/>
       <c r="J329" s="11" t="n"/>
       <c r="K329" s="11" t="n"/>
-      <c r="L329" s="11" t="n"/>
-      <c r="M329" s="11" t="n"/>
     </row>
     <row r="330" ht="15.75" customHeight="1" s="16">
       <c r="A330" s="4">
@@ -11481,8 +10575,6 @@
       <c r="I330" s="11" t="n"/>
       <c r="J330" s="11" t="n"/>
       <c r="K330" s="11" t="n"/>
-      <c r="L330" s="11" t="n"/>
-      <c r="M330" s="11" t="n"/>
     </row>
     <row r="331" ht="15.75" customHeight="1" s="16">
       <c r="A331" s="4">
@@ -11511,8 +10603,6 @@
       <c r="I331" s="11" t="n"/>
       <c r="J331" s="11" t="n"/>
       <c r="K331" s="11" t="n"/>
-      <c r="L331" s="11" t="n"/>
-      <c r="M331" s="11" t="n"/>
     </row>
     <row r="332" ht="15.75" customHeight="1" s="16">
       <c r="A332" s="4">
@@ -11541,8 +10631,6 @@
       <c r="I332" s="11" t="n"/>
       <c r="J332" s="11" t="n"/>
       <c r="K332" s="11" t="n"/>
-      <c r="L332" s="11" t="n"/>
-      <c r="M332" s="11" t="n"/>
     </row>
     <row r="333" ht="15.75" customHeight="1" s="16">
       <c r="A333" s="4">
@@ -11571,8 +10659,6 @@
       <c r="I333" s="11" t="n"/>
       <c r="J333" s="11" t="n"/>
       <c r="K333" s="11" t="n"/>
-      <c r="L333" s="11" t="n"/>
-      <c r="M333" s="11" t="n"/>
     </row>
     <row r="334" ht="15.75" customHeight="1" s="16">
       <c r="A334" s="4">
@@ -11601,8 +10687,6 @@
       <c r="I334" s="11" t="n"/>
       <c r="J334" s="11" t="n"/>
       <c r="K334" s="11" t="n"/>
-      <c r="L334" s="11" t="n"/>
-      <c r="M334" s="11" t="n"/>
     </row>
     <row r="335" ht="15.75" customHeight="1" s="16">
       <c r="A335" s="4">
@@ -11631,8 +10715,6 @@
       <c r="I335" s="11" t="n"/>
       <c r="J335" s="11" t="n"/>
       <c r="K335" s="11" t="n"/>
-      <c r="L335" s="11" t="n"/>
-      <c r="M335" s="11" t="n"/>
     </row>
     <row r="336" ht="15.75" customHeight="1" s="16">
       <c r="A336" s="4">
@@ -11661,8 +10743,6 @@
       <c r="I336" s="11" t="n"/>
       <c r="J336" s="11" t="n"/>
       <c r="K336" s="11" t="n"/>
-      <c r="L336" s="11" t="n"/>
-      <c r="M336" s="11" t="n"/>
     </row>
     <row r="337" ht="15.75" customHeight="1" s="16">
       <c r="A337" s="4">
@@ -11691,8 +10771,6 @@
       <c r="I337" s="11" t="n"/>
       <c r="J337" s="11" t="n"/>
       <c r="K337" s="11" t="n"/>
-      <c r="L337" s="11" t="n"/>
-      <c r="M337" s="11" t="n"/>
     </row>
     <row r="338" ht="15.75" customHeight="1" s="16">
       <c r="A338" s="4">
@@ -11721,8 +10799,6 @@
       <c r="I338" s="11" t="n"/>
       <c r="J338" s="11" t="n"/>
       <c r="K338" s="11" t="n"/>
-      <c r="L338" s="11" t="n"/>
-      <c r="M338" s="11" t="n"/>
     </row>
     <row r="339" ht="15.75" customHeight="1" s="16">
       <c r="A339" s="4">
@@ -11751,8 +10827,6 @@
       <c r="I339" s="11" t="n"/>
       <c r="J339" s="11" t="n"/>
       <c r="K339" s="11" t="n"/>
-      <c r="L339" s="11" t="n"/>
-      <c r="M339" s="11" t="n"/>
     </row>
     <row r="340" ht="15.75" customHeight="1" s="16">
       <c r="A340" s="4">
@@ -11781,8 +10855,6 @@
       <c r="I340" s="11" t="n"/>
       <c r="J340" s="11" t="n"/>
       <c r="K340" s="11" t="n"/>
-      <c r="L340" s="11" t="n"/>
-      <c r="M340" s="11" t="n"/>
     </row>
     <row r="341" ht="15.75" customHeight="1" s="16">
       <c r="A341" s="4">
@@ -11811,8 +10883,6 @@
       <c r="I341" s="11" t="n"/>
       <c r="J341" s="11" t="n"/>
       <c r="K341" s="11" t="n"/>
-      <c r="L341" s="11" t="n"/>
-      <c r="M341" s="11" t="n"/>
     </row>
     <row r="342" ht="15.75" customHeight="1" s="16">
       <c r="A342" s="4">
@@ -11841,8 +10911,6 @@
       <c r="I342" s="11" t="n"/>
       <c r="J342" s="11" t="n"/>
       <c r="K342" s="11" t="n"/>
-      <c r="L342" s="11" t="n"/>
-      <c r="M342" s="11" t="n"/>
     </row>
     <row r="343" ht="15.75" customHeight="1" s="16">
       <c r="A343" s="4">
@@ -11871,8 +10939,6 @@
       <c r="I343" s="11" t="n"/>
       <c r="J343" s="11" t="n"/>
       <c r="K343" s="11" t="n"/>
-      <c r="L343" s="11" t="n"/>
-      <c r="M343" s="11" t="n"/>
     </row>
     <row r="344" ht="15.75" customHeight="1" s="16">
       <c r="A344" s="4">
@@ -11901,8 +10967,6 @@
       <c r="I344" s="11" t="n"/>
       <c r="J344" s="11" t="n"/>
       <c r="K344" s="11" t="n"/>
-      <c r="L344" s="11" t="n"/>
-      <c r="M344" s="11" t="n"/>
     </row>
     <row r="345" ht="15.75" customHeight="1" s="16">
       <c r="A345" s="4">
@@ -11931,8 +10995,6 @@
       <c r="I345" s="11" t="n"/>
       <c r="J345" s="11" t="n"/>
       <c r="K345" s="11" t="n"/>
-      <c r="L345" s="11" t="n"/>
-      <c r="M345" s="11" t="n"/>
     </row>
     <row r="346" ht="15.75" customHeight="1" s="16">
       <c r="A346" s="4">
@@ -11961,8 +11023,6 @@
       <c r="I346" s="11" t="n"/>
       <c r="J346" s="11" t="n"/>
       <c r="K346" s="11" t="n"/>
-      <c r="L346" s="11" t="n"/>
-      <c r="M346" s="11" t="n"/>
     </row>
     <row r="347" ht="15.75" customHeight="1" s="16">
       <c r="A347" s="4">
@@ -11991,8 +11051,6 @@
       <c r="I347" s="11" t="n"/>
       <c r="J347" s="11" t="n"/>
       <c r="K347" s="11" t="n"/>
-      <c r="L347" s="11" t="n"/>
-      <c r="M347" s="11" t="n"/>
     </row>
     <row r="348" ht="15.75" customHeight="1" s="16">
       <c r="A348" s="4">
@@ -12021,8 +11079,6 @@
       <c r="I348" s="11" t="n"/>
       <c r="J348" s="11" t="n"/>
       <c r="K348" s="11" t="n"/>
-      <c r="L348" s="11" t="n"/>
-      <c r="M348" s="11" t="n"/>
     </row>
     <row r="349" ht="15.75" customHeight="1" s="16">
       <c r="A349" s="4">
@@ -12051,8 +11107,6 @@
       <c r="I349" s="11" t="n"/>
       <c r="J349" s="11" t="n"/>
       <c r="K349" s="11" t="n"/>
-      <c r="L349" s="11" t="n"/>
-      <c r="M349" s="11" t="n"/>
     </row>
     <row r="350" ht="15.75" customHeight="1" s="16">
       <c r="A350" s="4">
@@ -12081,8 +11135,6 @@
       <c r="I350" s="11" t="n"/>
       <c r="J350" s="11" t="n"/>
       <c r="K350" s="11" t="n"/>
-      <c r="L350" s="11" t="n"/>
-      <c r="M350" s="11" t="n"/>
     </row>
     <row r="351" ht="15.75" customHeight="1" s="16">
       <c r="A351" s="4">
@@ -12111,8 +11163,6 @@
       <c r="I351" s="11" t="n"/>
       <c r="J351" s="11" t="n"/>
       <c r="K351" s="11" t="n"/>
-      <c r="L351" s="11" t="n"/>
-      <c r="M351" s="11" t="n"/>
     </row>
     <row r="352" ht="15.75" customHeight="1" s="16">
       <c r="A352" s="4">
@@ -12141,8 +11191,6 @@
       <c r="I352" s="11" t="n"/>
       <c r="J352" s="11" t="n"/>
       <c r="K352" s="11" t="n"/>
-      <c r="L352" s="11" t="n"/>
-      <c r="M352" s="11" t="n"/>
     </row>
     <row r="353" ht="15.75" customHeight="1" s="16">
       <c r="A353" s="4">
@@ -12171,8 +11219,6 @@
       <c r="I353" s="11" t="n"/>
       <c r="J353" s="11" t="n"/>
       <c r="K353" s="11" t="n"/>
-      <c r="L353" s="11" t="n"/>
-      <c r="M353" s="11" t="n"/>
     </row>
     <row r="354" ht="15.75" customHeight="1" s="16">
       <c r="A354" s="4">
@@ -12201,8 +11247,6 @@
       <c r="I354" s="11" t="n"/>
       <c r="J354" s="11" t="n"/>
       <c r="K354" s="11" t="n"/>
-      <c r="L354" s="11" t="n"/>
-      <c r="M354" s="11" t="n"/>
     </row>
     <row r="355" ht="15.75" customHeight="1" s="16">
       <c r="A355" s="4">
@@ -12231,8 +11275,6 @@
       <c r="I355" s="11" t="n"/>
       <c r="J355" s="11" t="n"/>
       <c r="K355" s="11" t="n"/>
-      <c r="L355" s="11" t="n"/>
-      <c r="M355" s="11" t="n"/>
     </row>
     <row r="356" ht="15.75" customHeight="1" s="16">
       <c r="A356" s="4">
@@ -12261,8 +11303,6 @@
       <c r="I356" s="11" t="n"/>
       <c r="J356" s="11" t="n"/>
       <c r="K356" s="11" t="n"/>
-      <c r="L356" s="11" t="n"/>
-      <c r="M356" s="11" t="n"/>
     </row>
     <row r="357" ht="15.75" customHeight="1" s="16">
       <c r="A357" s="4">
@@ -12291,8 +11331,6 @@
       <c r="I357" s="11" t="n"/>
       <c r="J357" s="11" t="n"/>
       <c r="K357" s="11" t="n"/>
-      <c r="L357" s="11" t="n"/>
-      <c r="M357" s="11" t="n"/>
     </row>
     <row r="358" ht="15.75" customHeight="1" s="16">
       <c r="A358" s="4">
@@ -12321,8 +11359,6 @@
       <c r="I358" s="11" t="n"/>
       <c r="J358" s="11" t="n"/>
       <c r="K358" s="11" t="n"/>
-      <c r="L358" s="11" t="n"/>
-      <c r="M358" s="11" t="n"/>
     </row>
     <row r="359" ht="15.75" customHeight="1" s="16">
       <c r="A359" s="4">
@@ -12351,8 +11387,6 @@
       <c r="I359" s="11" t="n"/>
       <c r="J359" s="11" t="n"/>
       <c r="K359" s="11" t="n"/>
-      <c r="L359" s="11" t="n"/>
-      <c r="M359" s="11" t="n"/>
     </row>
     <row r="360" ht="15.75" customHeight="1" s="16">
       <c r="A360" s="4">
@@ -12381,8 +11415,6 @@
       <c r="I360" s="11" t="n"/>
       <c r="J360" s="11" t="n"/>
       <c r="K360" s="11" t="n"/>
-      <c r="L360" s="11" t="n"/>
-      <c r="M360" s="11" t="n"/>
     </row>
     <row r="361" ht="15.75" customHeight="1" s="16">
       <c r="A361" s="4">
@@ -12411,8 +11443,6 @@
       <c r="I361" s="11" t="n"/>
       <c r="J361" s="11" t="n"/>
       <c r="K361" s="11" t="n"/>
-      <c r="L361" s="11" t="n"/>
-      <c r="M361" s="11" t="n"/>
     </row>
     <row r="362" ht="15.75" customHeight="1" s="16">
       <c r="A362" s="4">
@@ -12441,8 +11471,6 @@
       <c r="I362" s="11" t="n"/>
       <c r="J362" s="11" t="n"/>
       <c r="K362" s="11" t="n"/>
-      <c r="L362" s="11" t="n"/>
-      <c r="M362" s="11" t="n"/>
     </row>
     <row r="363" ht="15.75" customHeight="1" s="16">
       <c r="A363" s="4">
@@ -12471,8 +11499,6 @@
       <c r="I363" s="11" t="n"/>
       <c r="J363" s="11" t="n"/>
       <c r="K363" s="11" t="n"/>
-      <c r="L363" s="11" t="n"/>
-      <c r="M363" s="11" t="n"/>
     </row>
     <row r="364" ht="15.75" customHeight="1" s="16">
       <c r="A364" s="4">
@@ -12501,8 +11527,6 @@
       <c r="I364" s="11" t="n"/>
       <c r="J364" s="11" t="n"/>
       <c r="K364" s="11" t="n"/>
-      <c r="L364" s="11" t="n"/>
-      <c r="M364" s="11" t="n"/>
     </row>
     <row r="365" ht="15.75" customHeight="1" s="16">
       <c r="A365" s="4">
@@ -12531,8 +11555,6 @@
       <c r="I365" s="11" t="n"/>
       <c r="J365" s="11" t="n"/>
       <c r="K365" s="11" t="n"/>
-      <c r="L365" s="11" t="n"/>
-      <c r="M365" s="11" t="n"/>
     </row>
     <row r="366" ht="15.75" customHeight="1" s="16">
       <c r="A366" s="4">
@@ -12561,8 +11583,6 @@
       <c r="I366" s="11" t="n"/>
       <c r="J366" s="11" t="n"/>
       <c r="K366" s="11" t="n"/>
-      <c r="L366" s="11" t="n"/>
-      <c r="M366" s="11" t="n"/>
     </row>
     <row r="367" ht="15.75" customHeight="1" s="16">
       <c r="A367" s="4">
@@ -12591,8 +11611,6 @@
       <c r="I367" s="11" t="n"/>
       <c r="J367" s="11" t="n"/>
       <c r="K367" s="11" t="n"/>
-      <c r="L367" s="11" t="n"/>
-      <c r="M367" s="11" t="n"/>
     </row>
     <row r="368" ht="15.75" customHeight="1" s="16">
       <c r="A368" s="4">
@@ -12621,8 +11639,6 @@
       <c r="I368" s="11" t="n"/>
       <c r="J368" s="11" t="n"/>
       <c r="K368" s="11" t="n"/>
-      <c r="L368" s="11" t="n"/>
-      <c r="M368" s="11" t="n"/>
     </row>
     <row r="369" ht="15.75" customHeight="1" s="16">
       <c r="A369" s="4">
@@ -12651,8 +11667,6 @@
       <c r="I369" s="11" t="n"/>
       <c r="J369" s="11" t="n"/>
       <c r="K369" s="11" t="n"/>
-      <c r="L369" s="11" t="n"/>
-      <c r="M369" s="11" t="n"/>
     </row>
     <row r="370" ht="15.75" customHeight="1" s="16">
       <c r="A370" s="4">
@@ -12681,8 +11695,6 @@
       <c r="I370" s="11" t="n"/>
       <c r="J370" s="11" t="n"/>
       <c r="K370" s="11" t="n"/>
-      <c r="L370" s="11" t="n"/>
-      <c r="M370" s="11" t="n"/>
     </row>
     <row r="371" ht="15.75" customHeight="1" s="16">
       <c r="A371" s="4">
@@ -12711,8 +11723,6 @@
       <c r="I371" s="11" t="n"/>
       <c r="J371" s="11" t="n"/>
       <c r="K371" s="11" t="n"/>
-      <c r="L371" s="11" t="n"/>
-      <c r="M371" s="11" t="n"/>
     </row>
     <row r="372" ht="15.75" customHeight="1" s="16">
       <c r="A372" s="4">
@@ -12741,8 +11751,6 @@
       <c r="I372" s="11" t="n"/>
       <c r="J372" s="11" t="n"/>
       <c r="K372" s="11" t="n"/>
-      <c r="L372" s="11" t="n"/>
-      <c r="M372" s="11" t="n"/>
     </row>
     <row r="373" ht="15.75" customHeight="1" s="16">
       <c r="A373" s="4">
@@ -12771,8 +11779,6 @@
       <c r="I373" s="11" t="n"/>
       <c r="J373" s="11" t="n"/>
       <c r="K373" s="11" t="n"/>
-      <c r="L373" s="11" t="n"/>
-      <c r="M373" s="11" t="n"/>
     </row>
     <row r="374" ht="15.75" customHeight="1" s="16">
       <c r="A374" s="4">
@@ -12801,8 +11807,6 @@
       <c r="I374" s="11" t="n"/>
       <c r="J374" s="11" t="n"/>
       <c r="K374" s="11" t="n"/>
-      <c r="L374" s="11" t="n"/>
-      <c r="M374" s="11" t="n"/>
     </row>
     <row r="375" ht="15.75" customHeight="1" s="16">
       <c r="A375" s="4">
@@ -12831,8 +11835,6 @@
       <c r="I375" s="11" t="n"/>
       <c r="J375" s="11" t="n"/>
       <c r="K375" s="11" t="n"/>
-      <c r="L375" s="11" t="n"/>
-      <c r="M375" s="11" t="n"/>
     </row>
     <row r="376" ht="15.75" customHeight="1" s="16">
       <c r="A376" s="4">
@@ -12861,8 +11863,6 @@
       <c r="I376" s="11" t="n"/>
       <c r="J376" s="11" t="n"/>
       <c r="K376" s="11" t="n"/>
-      <c r="L376" s="11" t="n"/>
-      <c r="M376" s="11" t="n"/>
     </row>
     <row r="377" ht="15.75" customHeight="1" s="16">
       <c r="A377" s="4">
@@ -12891,8 +11891,6 @@
       <c r="I377" s="11" t="n"/>
       <c r="J377" s="11" t="n"/>
       <c r="K377" s="11" t="n"/>
-      <c r="L377" s="11" t="n"/>
-      <c r="M377" s="11" t="n"/>
     </row>
     <row r="378" ht="15.75" customHeight="1" s="16">
       <c r="A378" s="4">
@@ -12921,8 +11919,6 @@
       <c r="I378" s="11" t="n"/>
       <c r="J378" s="11" t="n"/>
       <c r="K378" s="11" t="n"/>
-      <c r="L378" s="11" t="n"/>
-      <c r="M378" s="11" t="n"/>
     </row>
     <row r="379" ht="15.75" customHeight="1" s="16">
       <c r="A379" s="4">
@@ -12951,8 +11947,6 @@
       <c r="I379" s="11" t="n"/>
       <c r="J379" s="11" t="n"/>
       <c r="K379" s="11" t="n"/>
-      <c r="L379" s="11" t="n"/>
-      <c r="M379" s="11" t="n"/>
     </row>
     <row r="380" ht="15.75" customHeight="1" s="16">
       <c r="A380" s="4">
@@ -12981,8 +11975,6 @@
       <c r="I380" s="11" t="n"/>
       <c r="J380" s="11" t="n"/>
       <c r="K380" s="11" t="n"/>
-      <c r="L380" s="11" t="n"/>
-      <c r="M380" s="11" t="n"/>
     </row>
     <row r="381" ht="15.75" customHeight="1" s="16">
       <c r="A381" s="4">
@@ -13011,8 +12003,6 @@
       <c r="I381" s="11" t="n"/>
       <c r="J381" s="11" t="n"/>
       <c r="K381" s="11" t="n"/>
-      <c r="L381" s="11" t="n"/>
-      <c r="M381" s="11" t="n"/>
     </row>
     <row r="382" ht="15.75" customHeight="1" s="16">
       <c r="A382" s="4">
@@ -13041,8 +12031,6 @@
       <c r="I382" s="11" t="n"/>
       <c r="J382" s="11" t="n"/>
       <c r="K382" s="11" t="n"/>
-      <c r="L382" s="11" t="n"/>
-      <c r="M382" s="11" t="n"/>
     </row>
     <row r="383" ht="15.75" customHeight="1" s="16">
       <c r="A383" s="4">
@@ -13071,8 +12059,6 @@
       <c r="I383" s="11" t="n"/>
       <c r="J383" s="11" t="n"/>
       <c r="K383" s="11" t="n"/>
-      <c r="L383" s="11" t="n"/>
-      <c r="M383" s="11" t="n"/>
     </row>
     <row r="384" ht="15.75" customHeight="1" s="16">
       <c r="A384" s="4">
@@ -13101,8 +12087,6 @@
       <c r="I384" s="11" t="n"/>
       <c r="J384" s="11" t="n"/>
       <c r="K384" s="11" t="n"/>
-      <c r="L384" s="11" t="n"/>
-      <c r="M384" s="11" t="n"/>
     </row>
     <row r="385" ht="15.75" customHeight="1" s="16">
       <c r="A385" s="4">
@@ -13131,8 +12115,6 @@
       <c r="I385" s="11" t="n"/>
       <c r="J385" s="11" t="n"/>
       <c r="K385" s="11" t="n"/>
-      <c r="L385" s="11" t="n"/>
-      <c r="M385" s="11" t="n"/>
     </row>
     <row r="386" ht="15.75" customHeight="1" s="16">
       <c r="A386" s="4">
@@ -13161,8 +12143,6 @@
       <c r="I386" s="11" t="n"/>
       <c r="J386" s="11" t="n"/>
       <c r="K386" s="11" t="n"/>
-      <c r="L386" s="11" t="n"/>
-      <c r="M386" s="11" t="n"/>
     </row>
     <row r="387" ht="15.75" customHeight="1" s="16">
       <c r="A387" s="4">
@@ -13191,8 +12171,6 @@
       <c r="I387" s="11" t="n"/>
       <c r="J387" s="11" t="n"/>
       <c r="K387" s="11" t="n"/>
-      <c r="L387" s="11" t="n"/>
-      <c r="M387" s="11" t="n"/>
     </row>
     <row r="388" ht="15.75" customHeight="1" s="16">
       <c r="A388" s="4">
@@ -13221,8 +12199,6 @@
       <c r="I388" s="11" t="n"/>
       <c r="J388" s="11" t="n"/>
       <c r="K388" s="11" t="n"/>
-      <c r="L388" s="11" t="n"/>
-      <c r="M388" s="11" t="n"/>
     </row>
     <row r="389" ht="15.75" customHeight="1" s="16">
       <c r="A389" s="4">
@@ -13251,8 +12227,6 @@
       <c r="I389" s="11" t="n"/>
       <c r="J389" s="11" t="n"/>
       <c r="K389" s="11" t="n"/>
-      <c r="L389" s="11" t="n"/>
-      <c r="M389" s="11" t="n"/>
     </row>
     <row r="390" ht="15.75" customHeight="1" s="16">
       <c r="A390" s="4">
@@ -13281,8 +12255,6 @@
       <c r="I390" s="11" t="n"/>
       <c r="J390" s="11" t="n"/>
       <c r="K390" s="11" t="n"/>
-      <c r="L390" s="11" t="n"/>
-      <c r="M390" s="11" t="n"/>
     </row>
     <row r="391" ht="15.75" customHeight="1" s="16">
       <c r="A391" s="4">
@@ -13311,8 +12283,6 @@
       <c r="I391" s="11" t="n"/>
       <c r="J391" s="11" t="n"/>
       <c r="K391" s="11" t="n"/>
-      <c r="L391" s="11" t="n"/>
-      <c r="M391" s="11" t="n"/>
     </row>
     <row r="392" ht="15.75" customHeight="1" s="16">
       <c r="A392" s="4">
@@ -13341,8 +12311,6 @@
       <c r="I392" s="11" t="n"/>
       <c r="J392" s="11" t="n"/>
       <c r="K392" s="11" t="n"/>
-      <c r="L392" s="11" t="n"/>
-      <c r="M392" s="11" t="n"/>
     </row>
     <row r="393" ht="15.75" customHeight="1" s="16">
       <c r="A393" s="4">
@@ -13371,8 +12339,6 @@
       <c r="I393" s="11" t="n"/>
       <c r="J393" s="11" t="n"/>
       <c r="K393" s="11" t="n"/>
-      <c r="L393" s="11" t="n"/>
-      <c r="M393" s="11" t="n"/>
     </row>
     <row r="394" ht="15.75" customHeight="1" s="16">
       <c r="A394" s="4">
@@ -13401,8 +12367,6 @@
       <c r="I394" s="11" t="n"/>
       <c r="J394" s="11" t="n"/>
       <c r="K394" s="11" t="n"/>
-      <c r="L394" s="11" t="n"/>
-      <c r="M394" s="11" t="n"/>
     </row>
     <row r="395" ht="15.75" customHeight="1" s="16">
       <c r="A395" s="4">
@@ -13431,8 +12395,6 @@
       <c r="I395" s="11" t="n"/>
       <c r="J395" s="11" t="n"/>
       <c r="K395" s="11" t="n"/>
-      <c r="L395" s="11" t="n"/>
-      <c r="M395" s="11" t="n"/>
     </row>
     <row r="396" ht="15.75" customHeight="1" s="16">
       <c r="A396" s="4">
@@ -13461,8 +12423,6 @@
       <c r="I396" s="11" t="n"/>
       <c r="J396" s="11" t="n"/>
       <c r="K396" s="11" t="n"/>
-      <c r="L396" s="11" t="n"/>
-      <c r="M396" s="11" t="n"/>
     </row>
     <row r="397" ht="15.75" customHeight="1" s="16">
       <c r="A397" s="4">
@@ -13491,8 +12451,6 @@
       <c r="I397" s="11" t="n"/>
       <c r="J397" s="11" t="n"/>
       <c r="K397" s="11" t="n"/>
-      <c r="L397" s="11" t="n"/>
-      <c r="M397" s="11" t="n"/>
     </row>
     <row r="398" ht="15.75" customHeight="1" s="16">
       <c r="A398" s="4">
@@ -13521,8 +12479,6 @@
       <c r="I398" s="11" t="n"/>
       <c r="J398" s="11" t="n"/>
       <c r="K398" s="11" t="n"/>
-      <c r="L398" s="11" t="n"/>
-      <c r="M398" s="11" t="n"/>
     </row>
     <row r="399" ht="15.75" customHeight="1" s="16">
       <c r="A399" s="4">
@@ -13551,8 +12507,6 @@
       <c r="I399" s="11" t="n"/>
       <c r="J399" s="11" t="n"/>
       <c r="K399" s="11" t="n"/>
-      <c r="L399" s="11" t="n"/>
-      <c r="M399" s="11" t="n"/>
     </row>
     <row r="400" ht="15.75" customHeight="1" s="16">
       <c r="A400" s="4">
@@ -13581,8 +12535,6 @@
       <c r="I400" s="11" t="n"/>
       <c r="J400" s="11" t="n"/>
       <c r="K400" s="11" t="n"/>
-      <c r="L400" s="11" t="n"/>
-      <c r="M400" s="11" t="n"/>
     </row>
     <row r="401" ht="15.75" customHeight="1" s="16">
       <c r="A401" s="4">
@@ -13611,8 +12563,6 @@
       <c r="I401" s="11" t="n"/>
       <c r="J401" s="11" t="n"/>
       <c r="K401" s="11" t="n"/>
-      <c r="L401" s="11" t="n"/>
-      <c r="M401" s="11" t="n"/>
     </row>
     <row r="402" ht="15.75" customHeight="1" s="16">
       <c r="A402" s="4">
@@ -13641,8 +12591,6 @@
       <c r="I402" s="11" t="n"/>
       <c r="J402" s="11" t="n"/>
       <c r="K402" s="11" t="n"/>
-      <c r="L402" s="11" t="n"/>
-      <c r="M402" s="11" t="n"/>
     </row>
     <row r="403" ht="15.75" customHeight="1" s="16">
       <c r="A403" s="4">
@@ -13671,8 +12619,6 @@
       <c r="I403" s="11" t="n"/>
       <c r="J403" s="11" t="n"/>
       <c r="K403" s="11" t="n"/>
-      <c r="L403" s="11" t="n"/>
-      <c r="M403" s="11" t="n"/>
     </row>
     <row r="404" ht="15.75" customHeight="1" s="16">
       <c r="A404" s="4">
@@ -13701,8 +12647,6 @@
       <c r="I404" s="11" t="n"/>
       <c r="J404" s="11" t="n"/>
       <c r="K404" s="11" t="n"/>
-      <c r="L404" s="11" t="n"/>
-      <c r="M404" s="11" t="n"/>
     </row>
     <row r="405" ht="15.75" customHeight="1" s="16">
       <c r="A405" s="4">
@@ -13731,8 +12675,6 @@
       <c r="I405" s="11" t="n"/>
       <c r="J405" s="11" t="n"/>
       <c r="K405" s="11" t="n"/>
-      <c r="L405" s="11" t="n"/>
-      <c r="M405" s="11" t="n"/>
     </row>
     <row r="406" ht="15.75" customHeight="1" s="16">
       <c r="A406" s="4">
@@ -13761,8 +12703,6 @@
       <c r="I406" s="11" t="n"/>
       <c r="J406" s="11" t="n"/>
       <c r="K406" s="11" t="n"/>
-      <c r="L406" s="11" t="n"/>
-      <c r="M406" s="11" t="n"/>
     </row>
     <row r="407" ht="15.75" customHeight="1" s="16">
       <c r="A407" s="4">
@@ -13791,8 +12731,6 @@
       <c r="I407" s="11" t="n"/>
       <c r="J407" s="11" t="n"/>
       <c r="K407" s="11" t="n"/>
-      <c r="L407" s="11" t="n"/>
-      <c r="M407" s="11" t="n"/>
     </row>
     <row r="408" ht="15.75" customHeight="1" s="16">
       <c r="A408" s="4">
@@ -13821,8 +12759,6 @@
       <c r="I408" s="11" t="n"/>
       <c r="J408" s="11" t="n"/>
       <c r="K408" s="11" t="n"/>
-      <c r="L408" s="11" t="n"/>
-      <c r="M408" s="11" t="n"/>
     </row>
     <row r="409" ht="15.75" customHeight="1" s="16">
       <c r="A409" s="4">
@@ -13851,8 +12787,6 @@
       <c r="I409" s="11" t="n"/>
       <c r="J409" s="11" t="n"/>
       <c r="K409" s="11" t="n"/>
-      <c r="L409" s="11" t="n"/>
-      <c r="M409" s="11" t="n"/>
     </row>
     <row r="410" ht="15.75" customHeight="1" s="16">
       <c r="A410" s="4">
@@ -13881,8 +12815,6 @@
       <c r="I410" s="11" t="n"/>
       <c r="J410" s="11" t="n"/>
       <c r="K410" s="11" t="n"/>
-      <c r="L410" s="11" t="n"/>
-      <c r="M410" s="11" t="n"/>
     </row>
     <row r="411" ht="15.75" customHeight="1" s="16">
       <c r="A411" s="4">
@@ -13911,8 +12843,6 @@
       <c r="I411" s="11" t="n"/>
       <c r="J411" s="11" t="n"/>
       <c r="K411" s="11" t="n"/>
-      <c r="L411" s="11" t="n"/>
-      <c r="M411" s="11" t="n"/>
     </row>
     <row r="412" ht="15.75" customHeight="1" s="16">
       <c r="A412" s="4">
@@ -13941,8 +12871,6 @@
       <c r="I412" s="11" t="n"/>
       <c r="J412" s="11" t="n"/>
       <c r="K412" s="11" t="n"/>
-      <c r="L412" s="11" t="n"/>
-      <c r="M412" s="11" t="n"/>
     </row>
     <row r="413" ht="15.75" customHeight="1" s="16">
       <c r="A413" s="4">
@@ -13971,8 +12899,6 @@
       <c r="I413" s="11" t="n"/>
       <c r="J413" s="11" t="n"/>
       <c r="K413" s="11" t="n"/>
-      <c r="L413" s="11" t="n"/>
-      <c r="M413" s="11" t="n"/>
     </row>
     <row r="414" ht="15.75" customHeight="1" s="16">
       <c r="A414" s="4">
@@ -14001,8 +12927,6 @@
       <c r="I414" s="11" t="n"/>
       <c r="J414" s="11" t="n"/>
       <c r="K414" s="11" t="n"/>
-      <c r="L414" s="11" t="n"/>
-      <c r="M414" s="11" t="n"/>
     </row>
     <row r="415" ht="15.75" customHeight="1" s="16">
       <c r="A415" s="4">
@@ -14031,8 +12955,6 @@
       <c r="I415" s="11" t="n"/>
       <c r="J415" s="11" t="n"/>
       <c r="K415" s="11" t="n"/>
-      <c r="L415" s="11" t="n"/>
-      <c r="M415" s="11" t="n"/>
     </row>
     <row r="416" ht="15.75" customHeight="1" s="16">
       <c r="A416" s="4">
@@ -14061,8 +12983,6 @@
       <c r="I416" s="11" t="n"/>
       <c r="J416" s="11" t="n"/>
       <c r="K416" s="11" t="n"/>
-      <c r="L416" s="11" t="n"/>
-      <c r="M416" s="11" t="n"/>
     </row>
     <row r="417" ht="15.75" customHeight="1" s="16">
       <c r="A417" s="4">
@@ -14091,8 +13011,6 @@
       <c r="I417" s="11" t="n"/>
       <c r="J417" s="11" t="n"/>
       <c r="K417" s="11" t="n"/>
-      <c r="L417" s="11" t="n"/>
-      <c r="M417" s="11" t="n"/>
     </row>
     <row r="418" ht="15.75" customHeight="1" s="16">
       <c r="A418" s="4">
@@ -14121,8 +13039,6 @@
       <c r="I418" s="11" t="n"/>
       <c r="J418" s="11" t="n"/>
       <c r="K418" s="11" t="n"/>
-      <c r="L418" s="11" t="n"/>
-      <c r="M418" s="11" t="n"/>
     </row>
     <row r="419" ht="15.75" customHeight="1" s="16">
       <c r="A419" s="4">
@@ -14151,8 +13067,6 @@
       <c r="I419" s="11" t="n"/>
       <c r="J419" s="11" t="n"/>
       <c r="K419" s="11" t="n"/>
-      <c r="L419" s="11" t="n"/>
-      <c r="M419" s="11" t="n"/>
     </row>
     <row r="420" ht="15.75" customHeight="1" s="16">
       <c r="A420" s="4">
@@ -14181,8 +13095,6 @@
       <c r="I420" s="11" t="n"/>
       <c r="J420" s="11" t="n"/>
       <c r="K420" s="11" t="n"/>
-      <c r="L420" s="11" t="n"/>
-      <c r="M420" s="11" t="n"/>
     </row>
     <row r="421" ht="15.75" customHeight="1" s="16">
       <c r="A421" s="4">
@@ -14211,8 +13123,6 @@
       <c r="I421" s="11" t="n"/>
       <c r="J421" s="11" t="n"/>
       <c r="K421" s="11" t="n"/>
-      <c r="L421" s="11" t="n"/>
-      <c r="M421" s="11" t="n"/>
     </row>
     <row r="422" ht="15.75" customHeight="1" s="16">
       <c r="A422" s="4">
@@ -14241,8 +13151,6 @@
       <c r="I422" s="11" t="n"/>
       <c r="J422" s="11" t="n"/>
       <c r="K422" s="11" t="n"/>
-      <c r="L422" s="11" t="n"/>
-      <c r="M422" s="11" t="n"/>
     </row>
     <row r="423" ht="15.75" customHeight="1" s="16">
       <c r="A423" s="4">
@@ -14271,8 +13179,6 @@
       <c r="I423" s="11" t="n"/>
       <c r="J423" s="11" t="n"/>
       <c r="K423" s="11" t="n"/>
-      <c r="L423" s="11" t="n"/>
-      <c r="M423" s="11" t="n"/>
     </row>
     <row r="424" ht="15.75" customHeight="1" s="16">
       <c r="A424" s="4">
@@ -14301,8 +13207,6 @@
       <c r="I424" s="11" t="n"/>
       <c r="J424" s="11" t="n"/>
       <c r="K424" s="11" t="n"/>
-      <c r="L424" s="11" t="n"/>
-      <c r="M424" s="11" t="n"/>
     </row>
     <row r="425" ht="15.75" customHeight="1" s="16">
       <c r="A425" s="4">
@@ -14331,8 +13235,6 @@
       <c r="I425" s="11" t="n"/>
       <c r="J425" s="11" t="n"/>
       <c r="K425" s="11" t="n"/>
-      <c r="L425" s="11" t="n"/>
-      <c r="M425" s="11" t="n"/>
     </row>
     <row r="426" ht="15.75" customHeight="1" s="16">
       <c r="A426" s="4">
@@ -14361,8 +13263,6 @@
       <c r="I426" s="11" t="n"/>
       <c r="J426" s="11" t="n"/>
       <c r="K426" s="11" t="n"/>
-      <c r="L426" s="11" t="n"/>
-      <c r="M426" s="11" t="n"/>
     </row>
     <row r="427" ht="15.75" customHeight="1" s="16">
       <c r="A427" s="4">
@@ -14391,8 +13291,6 @@
       <c r="I427" s="11" t="n"/>
       <c r="J427" s="11" t="n"/>
       <c r="K427" s="11" t="n"/>
-      <c r="L427" s="11" t="n"/>
-      <c r="M427" s="11" t="n"/>
     </row>
     <row r="428" ht="15.75" customHeight="1" s="16">
       <c r="A428" s="4">
@@ -14421,8 +13319,6 @@
       <c r="I428" s="11" t="n"/>
       <c r="J428" s="11" t="n"/>
       <c r="K428" s="11" t="n"/>
-      <c r="L428" s="11" t="n"/>
-      <c r="M428" s="11" t="n"/>
     </row>
     <row r="429" ht="15.75" customHeight="1" s="16">
       <c r="A429" s="4">
@@ -14451,8 +13347,6 @@
       <c r="I429" s="11" t="n"/>
       <c r="J429" s="11" t="n"/>
       <c r="K429" s="11" t="n"/>
-      <c r="L429" s="11" t="n"/>
-      <c r="M429" s="11" t="n"/>
     </row>
     <row r="430" ht="15.75" customHeight="1" s="16">
       <c r="A430" s="4">
@@ -14481,8 +13375,6 @@
       <c r="I430" s="11" t="n"/>
       <c r="J430" s="11" t="n"/>
       <c r="K430" s="11" t="n"/>
-      <c r="L430" s="11" t="n"/>
-      <c r="M430" s="11" t="n"/>
     </row>
     <row r="431" ht="15.75" customHeight="1" s="16">
       <c r="A431" s="4">
@@ -14511,8 +13403,6 @@
       <c r="I431" s="11" t="n"/>
       <c r="J431" s="11" t="n"/>
       <c r="K431" s="11" t="n"/>
-      <c r="L431" s="11" t="n"/>
-      <c r="M431" s="11" t="n"/>
     </row>
     <row r="432" ht="15.75" customHeight="1" s="16">
       <c r="A432" s="4">
@@ -14541,8 +13431,6 @@
       <c r="I432" s="11" t="n"/>
       <c r="J432" s="11" t="n"/>
       <c r="K432" s="11" t="n"/>
-      <c r="L432" s="11" t="n"/>
-      <c r="M432" s="11" t="n"/>
     </row>
     <row r="433" ht="15.75" customHeight="1" s="16">
       <c r="A433" s="4">
@@ -14571,8 +13459,6 @@
       <c r="I433" s="11" t="n"/>
       <c r="J433" s="11" t="n"/>
       <c r="K433" s="11" t="n"/>
-      <c r="L433" s="11" t="n"/>
-      <c r="M433" s="11" t="n"/>
     </row>
     <row r="434" ht="15.75" customHeight="1" s="16">
       <c r="A434" s="4">
@@ -14601,8 +13487,6 @@
       <c r="I434" s="11" t="n"/>
       <c r="J434" s="11" t="n"/>
       <c r="K434" s="11" t="n"/>
-      <c r="L434" s="11" t="n"/>
-      <c r="M434" s="11" t="n"/>
     </row>
     <row r="435" ht="15.75" customHeight="1" s="16">
       <c r="A435" s="4">
@@ -14631,8 +13515,6 @@
       <c r="I435" s="11" t="n"/>
       <c r="J435" s="11" t="n"/>
       <c r="K435" s="11" t="n"/>
-      <c r="L435" s="11" t="n"/>
-      <c r="M435" s="11" t="n"/>
     </row>
     <row r="436" ht="15.75" customHeight="1" s="16">
       <c r="A436" s="4">
@@ -14661,8 +13543,6 @@
       <c r="I436" s="11" t="n"/>
       <c r="J436" s="11" t="n"/>
       <c r="K436" s="11" t="n"/>
-      <c r="L436" s="11" t="n"/>
-      <c r="M436" s="11" t="n"/>
     </row>
     <row r="437" ht="15.75" customHeight="1" s="16">
       <c r="A437" s="4">
@@ -14691,8 +13571,6 @@
       <c r="I437" s="11" t="n"/>
       <c r="J437" s="11" t="n"/>
       <c r="K437" s="11" t="n"/>
-      <c r="L437" s="11" t="n"/>
-      <c r="M437" s="11" t="n"/>
     </row>
     <row r="438" ht="15.75" customHeight="1" s="16">
       <c r="A438" s="4">
@@ -14721,8 +13599,6 @@
       <c r="I438" s="11" t="n"/>
       <c r="J438" s="11" t="n"/>
       <c r="K438" s="11" t="n"/>
-      <c r="L438" s="11" t="n"/>
-      <c r="M438" s="11" t="n"/>
     </row>
     <row r="439" ht="15.75" customHeight="1" s="16">
       <c r="A439" s="4">
@@ -14751,8 +13627,6 @@
       <c r="I439" s="11" t="n"/>
       <c r="J439" s="11" t="n"/>
       <c r="K439" s="11" t="n"/>
-      <c r="L439" s="11" t="n"/>
-      <c r="M439" s="11" t="n"/>
     </row>
     <row r="440" ht="15.75" customHeight="1" s="16">
       <c r="A440" s="4">
@@ -14781,8 +13655,6 @@
       <c r="I440" s="11" t="n"/>
       <c r="J440" s="11" t="n"/>
       <c r="K440" s="11" t="n"/>
-      <c r="L440" s="11" t="n"/>
-      <c r="M440" s="11" t="n"/>
     </row>
     <row r="441" ht="15.75" customHeight="1" s="16">
       <c r="A441" s="4">
@@ -14811,8 +13683,6 @@
       <c r="I441" s="11" t="n"/>
       <c r="J441" s="11" t="n"/>
       <c r="K441" s="11" t="n"/>
-      <c r="L441" s="11" t="n"/>
-      <c r="M441" s="11" t="n"/>
     </row>
     <row r="442" ht="15.75" customHeight="1" s="16">
       <c r="A442" s="4">
@@ -14841,8 +13711,6 @@
       <c r="I442" s="11" t="n"/>
       <c r="J442" s="11" t="n"/>
       <c r="K442" s="11" t="n"/>
-      <c r="L442" s="11" t="n"/>
-      <c r="M442" s="11" t="n"/>
     </row>
     <row r="443" ht="15.75" customHeight="1" s="16">
       <c r="A443" s="4">
@@ -14871,8 +13739,6 @@
       <c r="I443" s="11" t="n"/>
       <c r="J443" s="11" t="n"/>
       <c r="K443" s="11" t="n"/>
-      <c r="L443" s="11" t="n"/>
-      <c r="M443" s="11" t="n"/>
     </row>
     <row r="444" ht="15.75" customHeight="1" s="16">
       <c r="A444" s="4">
@@ -14901,8 +13767,6 @@
       <c r="I444" s="11" t="n"/>
       <c r="J444" s="11" t="n"/>
       <c r="K444" s="11" t="n"/>
-      <c r="L444" s="11" t="n"/>
-      <c r="M444" s="11" t="n"/>
     </row>
     <row r="445" ht="15.75" customHeight="1" s="16">
       <c r="A445" s="4">
@@ -14931,8 +13795,6 @@
       <c r="I445" s="11" t="n"/>
       <c r="J445" s="11" t="n"/>
       <c r="K445" s="11" t="n"/>
-      <c r="L445" s="11" t="n"/>
-      <c r="M445" s="11" t="n"/>
     </row>
     <row r="446" ht="15.75" customHeight="1" s="16">
       <c r="A446" s="4">
@@ -14961,8 +13823,6 @@
       <c r="I446" s="11" t="n"/>
       <c r="J446" s="11" t="n"/>
       <c r="K446" s="11" t="n"/>
-      <c r="L446" s="11" t="n"/>
-      <c r="M446" s="11" t="n"/>
     </row>
     <row r="447" ht="15.75" customHeight="1" s="16">
       <c r="A447" s="4">
@@ -14991,8 +13851,6 @@
       <c r="I447" s="11" t="n"/>
       <c r="J447" s="11" t="n"/>
       <c r="K447" s="11" t="n"/>
-      <c r="L447" s="11" t="n"/>
-      <c r="M447" s="11" t="n"/>
     </row>
     <row r="448" ht="15.75" customHeight="1" s="16">
       <c r="A448" s="4">
@@ -15021,8 +13879,6 @@
       <c r="I448" s="11" t="n"/>
       <c r="J448" s="11" t="n"/>
       <c r="K448" s="11" t="n"/>
-      <c r="L448" s="11" t="n"/>
-      <c r="M448" s="11" t="n"/>
     </row>
     <row r="449" ht="15.75" customHeight="1" s="16">
       <c r="A449" s="4">
@@ -15051,8 +13907,6 @@
       <c r="I449" s="11" t="n"/>
       <c r="J449" s="11" t="n"/>
       <c r="K449" s="11" t="n"/>
-      <c r="L449" s="11" t="n"/>
-      <c r="M449" s="11" t="n"/>
     </row>
     <row r="450" ht="15.75" customHeight="1" s="16">
       <c r="A450" s="4">
@@ -15081,8 +13935,6 @@
       <c r="I450" s="11" t="n"/>
       <c r="J450" s="11" t="n"/>
       <c r="K450" s="11" t="n"/>
-      <c r="L450" s="11" t="n"/>
-      <c r="M450" s="11" t="n"/>
     </row>
     <row r="451" ht="15.75" customHeight="1" s="16">
       <c r="A451" s="4">
@@ -15111,8 +13963,6 @@
       <c r="I451" s="11" t="n"/>
       <c r="J451" s="11" t="n"/>
       <c r="K451" s="11" t="n"/>
-      <c r="L451" s="11" t="n"/>
-      <c r="M451" s="11" t="n"/>
     </row>
     <row r="452" ht="15.75" customHeight="1" s="16">
       <c r="A452" s="4">
@@ -15141,8 +13991,6 @@
       <c r="I452" s="11" t="n"/>
       <c r="J452" s="11" t="n"/>
       <c r="K452" s="11" t="n"/>
-      <c r="L452" s="11" t="n"/>
-      <c r="M452" s="11" t="n"/>
     </row>
     <row r="453" ht="15.75" customHeight="1" s="16">
       <c r="A453" s="4">
@@ -15171,8 +14019,6 @@
       <c r="I453" s="11" t="n"/>
       <c r="J453" s="11" t="n"/>
       <c r="K453" s="11" t="n"/>
-      <c r="L453" s="11" t="n"/>
-      <c r="M453" s="11" t="n"/>
     </row>
     <row r="454" ht="15.75" customHeight="1" s="16">
       <c r="A454" s="4">
@@ -15201,8 +14047,6 @@
       <c r="I454" s="11" t="n"/>
       <c r="J454" s="11" t="n"/>
       <c r="K454" s="11" t="n"/>
-      <c r="L454" s="11" t="n"/>
-      <c r="M454" s="11" t="n"/>
     </row>
     <row r="455" ht="15.75" customHeight="1" s="16">
       <c r="A455" s="4">
@@ -15231,8 +14075,6 @@
       <c r="I455" s="11" t="n"/>
       <c r="J455" s="11" t="n"/>
       <c r="K455" s="11" t="n"/>
-      <c r="L455" s="11" t="n"/>
-      <c r="M455" s="11" t="n"/>
     </row>
     <row r="456" ht="15.75" customHeight="1" s="16">
       <c r="A456" s="4">
@@ -15261,8 +14103,6 @@
       <c r="I456" s="11" t="n"/>
       <c r="J456" s="11" t="n"/>
       <c r="K456" s="11" t="n"/>
-      <c r="L456" s="11" t="n"/>
-      <c r="M456" s="11" t="n"/>
     </row>
     <row r="457" ht="15.75" customHeight="1" s="16">
       <c r="A457" s="4">
@@ -15291,8 +14131,6 @@
       <c r="I457" s="11" t="n"/>
       <c r="J457" s="11" t="n"/>
       <c r="K457" s="11" t="n"/>
-      <c r="L457" s="11" t="n"/>
-      <c r="M457" s="11" t="n"/>
     </row>
     <row r="458" ht="15.75" customHeight="1" s="16">
       <c r="A458" s="4">
@@ -15321,8 +14159,6 @@
       <c r="I458" s="11" t="n"/>
       <c r="J458" s="11" t="n"/>
       <c r="K458" s="11" t="n"/>
-      <c r="L458" s="11" t="n"/>
-      <c r="M458" s="11" t="n"/>
     </row>
     <row r="459" ht="15.75" customHeight="1" s="16">
       <c r="A459" s="4">
@@ -15351,8 +14187,6 @@
       <c r="I459" s="11" t="n"/>
       <c r="J459" s="11" t="n"/>
       <c r="K459" s="11" t="n"/>
-      <c r="L459" s="11" t="n"/>
-      <c r="M459" s="11" t="n"/>
     </row>
     <row r="460" ht="15.75" customHeight="1" s="16">
       <c r="A460" s="4">
@@ -15381,8 +14215,6 @@
       <c r="I460" s="11" t="n"/>
       <c r="J460" s="11" t="n"/>
       <c r="K460" s="11" t="n"/>
-      <c r="L460" s="11" t="n"/>
-      <c r="M460" s="11" t="n"/>
     </row>
     <row r="461" ht="15.75" customHeight="1" s="16">
       <c r="A461" s="4">
@@ -15411,8 +14243,6 @@
       <c r="I461" s="11" t="n"/>
       <c r="J461" s="11" t="n"/>
       <c r="K461" s="11" t="n"/>
-      <c r="L461" s="11" t="n"/>
-      <c r="M461" s="11" t="n"/>
     </row>
     <row r="462" ht="15.75" customHeight="1" s="16">
       <c r="A462" s="4">
@@ -15441,8 +14271,6 @@
       <c r="I462" s="11" t="n"/>
       <c r="J462" s="11" t="n"/>
       <c r="K462" s="11" t="n"/>
-      <c r="L462" s="11" t="n"/>
-      <c r="M462" s="11" t="n"/>
     </row>
     <row r="463" ht="15.75" customHeight="1" s="16">
       <c r="A463" s="4">
@@ -15471,8 +14299,6 @@
       <c r="I463" s="11" t="n"/>
       <c r="J463" s="11" t="n"/>
       <c r="K463" s="11" t="n"/>
-      <c r="L463" s="11" t="n"/>
-      <c r="M463" s="11" t="n"/>
     </row>
     <row r="464" ht="15.75" customHeight="1" s="16">
       <c r="A464" s="4">
@@ -15501,8 +14327,6 @@
       <c r="I464" s="11" t="n"/>
       <c r="J464" s="11" t="n"/>
       <c r="K464" s="11" t="n"/>
-      <c r="L464" s="11" t="n"/>
-      <c r="M464" s="11" t="n"/>
     </row>
     <row r="465" ht="15.75" customHeight="1" s="16">
       <c r="A465" s="4">
@@ -15531,8 +14355,6 @@
       <c r="I465" s="11" t="n"/>
       <c r="J465" s="11" t="n"/>
       <c r="K465" s="11" t="n"/>
-      <c r="L465" s="11" t="n"/>
-      <c r="M465" s="11" t="n"/>
     </row>
     <row r="466" ht="15.75" customHeight="1" s="16">
       <c r="A466" s="4">
@@ -15561,8 +14383,6 @@
       <c r="I466" s="11" t="n"/>
       <c r="J466" s="11" t="n"/>
       <c r="K466" s="11" t="n"/>
-      <c r="L466" s="11" t="n"/>
-      <c r="M466" s="11" t="n"/>
     </row>
     <row r="467" ht="15.75" customHeight="1" s="16">
       <c r="A467" s="4">
@@ -15591,8 +14411,6 @@
       <c r="I467" s="11" t="n"/>
       <c r="J467" s="11" t="n"/>
       <c r="K467" s="11" t="n"/>
-      <c r="L467" s="11" t="n"/>
-      <c r="M467" s="11" t="n"/>
     </row>
     <row r="468" ht="15.75" customHeight="1" s="16">
       <c r="A468" s="4">
@@ -15621,8 +14439,6 @@
       <c r="I468" s="11" t="n"/>
       <c r="J468" s="11" t="n"/>
       <c r="K468" s="11" t="n"/>
-      <c r="L468" s="11" t="n"/>
-      <c r="M468" s="11" t="n"/>
     </row>
     <row r="469" ht="15.75" customHeight="1" s="16">
       <c r="A469" s="4">
@@ -15651,8 +14467,6 @@
       <c r="I469" s="11" t="n"/>
       <c r="J469" s="11" t="n"/>
       <c r="K469" s="11" t="n"/>
-      <c r="L469" s="11" t="n"/>
-      <c r="M469" s="11" t="n"/>
     </row>
     <row r="470" ht="15.75" customHeight="1" s="16">
       <c r="A470" s="4">
@@ -15681,8 +14495,6 @@
       <c r="I470" s="11" t="n"/>
       <c r="J470" s="11" t="n"/>
       <c r="K470" s="11" t="n"/>
-      <c r="L470" s="11" t="n"/>
-      <c r="M470" s="11" t="n"/>
     </row>
     <row r="471" ht="15.75" customHeight="1" s="16">
       <c r="A471" s="4">
@@ -15711,8 +14523,6 @@
       <c r="I471" s="11" t="n"/>
       <c r="J471" s="11" t="n"/>
       <c r="K471" s="11" t="n"/>
-      <c r="L471" s="11" t="n"/>
-      <c r="M471" s="11" t="n"/>
     </row>
     <row r="472" ht="15.75" customHeight="1" s="16">
       <c r="A472" s="4">
@@ -15741,8 +14551,6 @@
       <c r="I472" s="11" t="n"/>
       <c r="J472" s="11" t="n"/>
       <c r="K472" s="11" t="n"/>
-      <c r="L472" s="11" t="n"/>
-      <c r="M472" s="11" t="n"/>
     </row>
     <row r="473" ht="15.75" customHeight="1" s="16">
       <c r="A473" s="4">
@@ -15771,8 +14579,6 @@
       <c r="I473" s="11" t="n"/>
       <c r="J473" s="11" t="n"/>
       <c r="K473" s="11" t="n"/>
-      <c r="L473" s="11" t="n"/>
-      <c r="M473" s="11" t="n"/>
     </row>
     <row r="474" ht="15.75" customHeight="1" s="16">
       <c r="A474" s="4">
@@ -15801,8 +14607,6 @@
       <c r="I474" s="11" t="n"/>
       <c r="J474" s="11" t="n"/>
       <c r="K474" s="11" t="n"/>
-      <c r="L474" s="11" t="n"/>
-      <c r="M474" s="11" t="n"/>
     </row>
     <row r="475" ht="15.75" customHeight="1" s="16">
       <c r="A475" s="4">
@@ -15831,8 +14635,6 @@
       <c r="I475" s="11" t="n"/>
       <c r="J475" s="11" t="n"/>
       <c r="K475" s="11" t="n"/>
-      <c r="L475" s="11" t="n"/>
-      <c r="M475" s="11" t="n"/>
     </row>
     <row r="476" ht="15.75" customHeight="1" s="16">
       <c r="A476" s="4">
@@ -15861,8 +14663,6 @@
       <c r="I476" s="11" t="n"/>
       <c r="J476" s="11" t="n"/>
       <c r="K476" s="11" t="n"/>
-      <c r="L476" s="11" t="n"/>
-      <c r="M476" s="11" t="n"/>
     </row>
     <row r="477" ht="15.75" customHeight="1" s="16">
       <c r="A477" s="4">
@@ -15891,8 +14691,6 @@
       <c r="I477" s="11" t="n"/>
       <c r="J477" s="11" t="n"/>
       <c r="K477" s="11" t="n"/>
-      <c r="L477" s="11" t="n"/>
-      <c r="M477" s="11" t="n"/>
     </row>
     <row r="478" ht="15.75" customHeight="1" s="16">
       <c r="A478" s="4">
@@ -15921,8 +14719,6 @@
       <c r="I478" s="11" t="n"/>
       <c r="J478" s="11" t="n"/>
       <c r="K478" s="11" t="n"/>
-      <c r="L478" s="11" t="n"/>
-      <c r="M478" s="11" t="n"/>
     </row>
     <row r="479" ht="15.75" customHeight="1" s="16">
       <c r="A479" s="4">
@@ -15951,8 +14747,6 @@
       <c r="I479" s="11" t="n"/>
       <c r="J479" s="11" t="n"/>
       <c r="K479" s="11" t="n"/>
-      <c r="L479" s="11" t="n"/>
-      <c r="M479" s="11" t="n"/>
     </row>
     <row r="480" ht="15.75" customHeight="1" s="16">
       <c r="A480" s="4">
@@ -15981,8 +14775,6 @@
       <c r="I480" s="11" t="n"/>
       <c r="J480" s="11" t="n"/>
       <c r="K480" s="11" t="n"/>
-      <c r="L480" s="11" t="n"/>
-      <c r="M480" s="11" t="n"/>
     </row>
     <row r="481" ht="15.75" customHeight="1" s="16">
       <c r="A481" s="4">
@@ -16011,8 +14803,6 @@
       <c r="I481" s="11" t="n"/>
       <c r="J481" s="11" t="n"/>
       <c r="K481" s="11" t="n"/>
-      <c r="L481" s="11" t="n"/>
-      <c r="M481" s="11" t="n"/>
     </row>
     <row r="482" ht="15.75" customHeight="1" s="16">
       <c r="A482" s="4">
@@ -16041,8 +14831,6 @@
       <c r="I482" s="11" t="n"/>
       <c r="J482" s="11" t="n"/>
       <c r="K482" s="11" t="n"/>
-      <c r="L482" s="11" t="n"/>
-      <c r="M482" s="11" t="n"/>
     </row>
     <row r="483" ht="15.75" customHeight="1" s="16">
       <c r="A483" s="4">
@@ -16071,8 +14859,6 @@
       <c r="I483" s="11" t="n"/>
       <c r="J483" s="11" t="n"/>
       <c r="K483" s="11" t="n"/>
-      <c r="L483" s="11" t="n"/>
-      <c r="M483" s="11" t="n"/>
     </row>
     <row r="484" ht="15.75" customHeight="1" s="16">
       <c r="A484" s="4">
@@ -16101,8 +14887,6 @@
       <c r="I484" s="11" t="n"/>
       <c r="J484" s="11" t="n"/>
       <c r="K484" s="11" t="n"/>
-      <c r="L484" s="11" t="n"/>
-      <c r="M484" s="11" t="n"/>
     </row>
     <row r="485" ht="15.75" customHeight="1" s="16">
       <c r="A485" s="4">
@@ -16131,8 +14915,6 @@
       <c r="I485" s="11" t="n"/>
       <c r="J485" s="11" t="n"/>
       <c r="K485" s="11" t="n"/>
-      <c r="L485" s="11" t="n"/>
-      <c r="M485" s="11" t="n"/>
     </row>
     <row r="486" ht="15.75" customHeight="1" s="16">
       <c r="A486" s="4">
@@ -16161,8 +14943,6 @@
       <c r="I486" s="11" t="n"/>
       <c r="J486" s="11" t="n"/>
       <c r="K486" s="11" t="n"/>
-      <c r="L486" s="11" t="n"/>
-      <c r="M486" s="11" t="n"/>
     </row>
     <row r="487" ht="15.75" customHeight="1" s="16">
       <c r="A487" s="4">
@@ -16191,8 +14971,6 @@
       <c r="I487" s="11" t="n"/>
       <c r="J487" s="11" t="n"/>
       <c r="K487" s="11" t="n"/>
-      <c r="L487" s="11" t="n"/>
-      <c r="M487" s="11" t="n"/>
     </row>
     <row r="488" ht="15.75" customHeight="1" s="16">
       <c r="A488" s="4">
@@ -16221,8 +14999,6 @@
       <c r="I488" s="11" t="n"/>
       <c r="J488" s="11" t="n"/>
       <c r="K488" s="11" t="n"/>
-      <c r="L488" s="11" t="n"/>
-      <c r="M488" s="11" t="n"/>
     </row>
     <row r="489" ht="15.75" customHeight="1" s="16">
       <c r="A489" s="4">
@@ -16251,8 +15027,6 @@
       <c r="I489" s="11" t="n"/>
       <c r="J489" s="11" t="n"/>
       <c r="K489" s="11" t="n"/>
-      <c r="L489" s="11" t="n"/>
-      <c r="M489" s="11" t="n"/>
     </row>
     <row r="490" ht="15.75" customHeight="1" s="16">
       <c r="A490" s="4">
@@ -16281,8 +15055,6 @@
       <c r="I490" s="11" t="n"/>
       <c r="J490" s="11" t="n"/>
       <c r="K490" s="11" t="n"/>
-      <c r="L490" s="11" t="n"/>
-      <c r="M490" s="11" t="n"/>
     </row>
     <row r="491" ht="15.75" customHeight="1" s="16">
       <c r="A491" s="4">
@@ -16311,8 +15083,6 @@
       <c r="I491" s="11" t="n"/>
       <c r="J491" s="11" t="n"/>
       <c r="K491" s="11" t="n"/>
-      <c r="L491" s="11" t="n"/>
-      <c r="M491" s="11" t="n"/>
     </row>
     <row r="492" ht="15.75" customHeight="1" s="16">
       <c r="A492" s="4">
@@ -16341,8 +15111,6 @@
       <c r="I492" s="11" t="n"/>
       <c r="J492" s="11" t="n"/>
       <c r="K492" s="11" t="n"/>
-      <c r="L492" s="11" t="n"/>
-      <c r="M492" s="11" t="n"/>
     </row>
     <row r="493" ht="15.75" customHeight="1" s="16">
       <c r="A493" s="4">
@@ -16371,8 +15139,6 @@
       <c r="I493" s="11" t="n"/>
       <c r="J493" s="11" t="n"/>
       <c r="K493" s="11" t="n"/>
-      <c r="L493" s="11" t="n"/>
-      <c r="M493" s="11" t="n"/>
     </row>
     <row r="494" ht="15.75" customHeight="1" s="16">
       <c r="A494" s="4">
@@ -16401,8 +15167,6 @@
       <c r="I494" s="11" t="n"/>
       <c r="J494" s="11" t="n"/>
       <c r="K494" s="11" t="n"/>
-      <c r="L494" s="11" t="n"/>
-      <c r="M494" s="11" t="n"/>
     </row>
     <row r="495" ht="15.75" customHeight="1" s="16">
       <c r="A495" s="4">
@@ -16431,8 +15195,6 @@
       <c r="I495" s="11" t="n"/>
       <c r="J495" s="11" t="n"/>
       <c r="K495" s="11" t="n"/>
-      <c r="L495" s="11" t="n"/>
-      <c r="M495" s="11" t="n"/>
     </row>
     <row r="496" ht="15.75" customHeight="1" s="16">
       <c r="A496" s="4">
@@ -16461,8 +15223,6 @@
       <c r="I496" s="11" t="n"/>
       <c r="J496" s="11" t="n"/>
       <c r="K496" s="11" t="n"/>
-      <c r="L496" s="11" t="n"/>
-      <c r="M496" s="11" t="n"/>
     </row>
     <row r="497" ht="15.75" customHeight="1" s="16">
       <c r="A497" s="4">
@@ -16491,8 +15251,6 @@
       <c r="I497" s="11" t="n"/>
       <c r="J497" s="11" t="n"/>
       <c r="K497" s="11" t="n"/>
-      <c r="L497" s="11" t="n"/>
-      <c r="M497" s="11" t="n"/>
     </row>
     <row r="498" ht="15.75" customHeight="1" s="16">
       <c r="A498" s="4">
@@ -16521,8 +15279,6 @@
       <c r="I498" s="11" t="n"/>
       <c r="J498" s="11" t="n"/>
       <c r="K498" s="11" t="n"/>
-      <c r="L498" s="11" t="n"/>
-      <c r="M498" s="11" t="n"/>
     </row>
     <row r="499" ht="15.75" customHeight="1" s="16">
       <c r="A499" s="4">
@@ -16551,8 +15307,6 @@
       <c r="I499" s="11" t="n"/>
       <c r="J499" s="11" t="n"/>
       <c r="K499" s="11" t="n"/>
-      <c r="L499" s="11" t="n"/>
-      <c r="M499" s="11" t="n"/>
     </row>
     <row r="500" ht="15.75" customHeight="1" s="16">
       <c r="A500" s="4">
@@ -16581,8 +15335,6 @@
       <c r="I500" s="11" t="n"/>
       <c r="J500" s="11" t="n"/>
       <c r="K500" s="11" t="n"/>
-      <c r="L500" s="11" t="n"/>
-      <c r="M500" s="11" t="n"/>
     </row>
     <row r="501" ht="15.75" customHeight="1" s="16">
       <c r="A501" s="4">
@@ -16611,8 +15363,6 @@
       <c r="I501" s="11" t="n"/>
       <c r="J501" s="11" t="n"/>
       <c r="K501" s="11" t="n"/>
-      <c r="L501" s="11" t="n"/>
-      <c r="M501" s="11" t="n"/>
     </row>
     <row r="502" ht="15.75" customHeight="1" s="16">
       <c r="A502" s="4">
@@ -16641,8 +15391,6 @@
       <c r="I502" s="11" t="n"/>
       <c r="J502" s="11" t="n"/>
       <c r="K502" s="11" t="n"/>
-      <c r="L502" s="11" t="n"/>
-      <c r="M502" s="11" t="n"/>
     </row>
     <row r="503" ht="15.75" customHeight="1" s="16">
       <c r="A503" s="4">
@@ -16671,8 +15419,6 @@
       <c r="I503" s="11" t="n"/>
       <c r="J503" s="11" t="n"/>
       <c r="K503" s="11" t="n"/>
-      <c r="L503" s="11" t="n"/>
-      <c r="M503" s="11" t="n"/>
     </row>
     <row r="504" ht="15.75" customHeight="1" s="16">
       <c r="A504" s="4">
@@ -16701,8 +15447,6 @@
       <c r="I504" s="11" t="n"/>
       <c r="J504" s="11" t="n"/>
       <c r="K504" s="11" t="n"/>
-      <c r="L504" s="11" t="n"/>
-      <c r="M504" s="11" t="n"/>
     </row>
     <row r="505" ht="15.75" customHeight="1" s="16">
       <c r="A505" s="4">
@@ -16731,8 +15475,6 @@
       <c r="I505" s="11" t="n"/>
       <c r="J505" s="11" t="n"/>
       <c r="K505" s="11" t="n"/>
-      <c r="L505" s="11" t="n"/>
-      <c r="M505" s="11" t="n"/>
     </row>
     <row r="506" ht="15.75" customHeight="1" s="16">
       <c r="A506" s="4">
@@ -16761,8 +15503,6 @@
       <c r="I506" s="11" t="n"/>
       <c r="J506" s="11" t="n"/>
       <c r="K506" s="11" t="n"/>
-      <c r="L506" s="11" t="n"/>
-      <c r="M506" s="11" t="n"/>
     </row>
     <row r="507" ht="15.75" customHeight="1" s="16">
       <c r="A507" s="4">
@@ -16791,8 +15531,6 @@
       <c r="I507" s="11" t="n"/>
       <c r="J507" s="11" t="n"/>
       <c r="K507" s="11" t="n"/>
-      <c r="L507" s="11" t="n"/>
-      <c r="M507" s="11" t="n"/>
     </row>
     <row r="508" ht="15.75" customHeight="1" s="16">
       <c r="A508" s="4">
@@ -16821,8 +15559,6 @@
       <c r="I508" s="11" t="n"/>
       <c r="J508" s="11" t="n"/>
       <c r="K508" s="11" t="n"/>
-      <c r="L508" s="11" t="n"/>
-      <c r="M508" s="11" t="n"/>
     </row>
     <row r="509" ht="15.75" customHeight="1" s="16">
       <c r="A509" s="4">
@@ -16851,8 +15587,6 @@
       <c r="I509" s="11" t="n"/>
       <c r="J509" s="11" t="n"/>
       <c r="K509" s="11" t="n"/>
-      <c r="L509" s="11" t="n"/>
-      <c r="M509" s="11" t="n"/>
     </row>
     <row r="510" ht="15.75" customHeight="1" s="16">
       <c r="A510" s="4">
@@ -16881,8 +15615,6 @@
       <c r="I510" s="11" t="n"/>
       <c r="J510" s="11" t="n"/>
       <c r="K510" s="11" t="n"/>
-      <c r="L510" s="11" t="n"/>
-      <c r="M510" s="11" t="n"/>
     </row>
     <row r="511" ht="15.75" customHeight="1" s="16">
       <c r="A511" s="4">
@@ -16911,8 +15643,6 @@
       <c r="I511" s="11" t="n"/>
       <c r="J511" s="11" t="n"/>
       <c r="K511" s="11" t="n"/>
-      <c r="L511" s="11" t="n"/>
-      <c r="M511" s="11" t="n"/>
     </row>
     <row r="512" ht="15.75" customHeight="1" s="16">
       <c r="A512" s="4">
@@ -16941,8 +15671,6 @@
       <c r="I512" s="11" t="n"/>
       <c r="J512" s="11" t="n"/>
       <c r="K512" s="11" t="n"/>
-      <c r="L512" s="11" t="n"/>
-      <c r="M512" s="11" t="n"/>
     </row>
     <row r="513" ht="15.75" customHeight="1" s="16">
       <c r="A513" s="4">
@@ -16971,8 +15699,6 @@
       <c r="I513" s="11" t="n"/>
       <c r="J513" s="11" t="n"/>
       <c r="K513" s="11" t="n"/>
-      <c r="L513" s="11" t="n"/>
-      <c r="M513" s="11" t="n"/>
     </row>
     <row r="514" ht="15.75" customHeight="1" s="16">
       <c r="A514" s="4">
@@ -17001,8 +15727,6 @@
       <c r="I514" s="11" t="n"/>
       <c r="J514" s="11" t="n"/>
       <c r="K514" s="11" t="n"/>
-      <c r="L514" s="11" t="n"/>
-      <c r="M514" s="11" t="n"/>
     </row>
     <row r="515" ht="15.75" customHeight="1" s="16">
       <c r="A515" s="4">
@@ -17031,8 +15755,6 @@
       <c r="I515" s="11" t="n"/>
       <c r="J515" s="11" t="n"/>
       <c r="K515" s="11" t="n"/>
-      <c r="L515" s="11" t="n"/>
-      <c r="M515" s="11" t="n"/>
     </row>
     <row r="516" ht="15.75" customHeight="1" s="16">
       <c r="A516" s="4">
@@ -17061,8 +15783,6 @@
       <c r="I516" s="11" t="n"/>
       <c r="J516" s="11" t="n"/>
       <c r="K516" s="11" t="n"/>
-      <c r="L516" s="11" t="n"/>
-      <c r="M516" s="11" t="n"/>
     </row>
     <row r="517" ht="15.75" customHeight="1" s="16">
       <c r="A517" s="4">
@@ -17091,8 +15811,6 @@
       <c r="I517" s="11" t="n"/>
       <c r="J517" s="11" t="n"/>
       <c r="K517" s="11" t="n"/>
-      <c r="L517" s="11" t="n"/>
-      <c r="M517" s="11" t="n"/>
     </row>
     <row r="518" ht="15.75" customHeight="1" s="16">
       <c r="A518" s="4">
@@ -17121,8 +15839,6 @@
       <c r="I518" s="11" t="n"/>
       <c r="J518" s="11" t="n"/>
       <c r="K518" s="11" t="n"/>
-      <c r="L518" s="11" t="n"/>
-      <c r="M518" s="11" t="n"/>
     </row>
     <row r="519" ht="15.75" customHeight="1" s="16">
       <c r="A519" s="4">
@@ -17151,8 +15867,6 @@
       <c r="I519" s="11" t="n"/>
       <c r="J519" s="11" t="n"/>
       <c r="K519" s="11" t="n"/>
-      <c r="L519" s="11" t="n"/>
-      <c r="M519" s="11" t="n"/>
     </row>
     <row r="520" ht="15.75" customHeight="1" s="16">
       <c r="A520" s="4">
@@ -17181,8 +15895,6 @@
       <c r="I520" s="11" t="n"/>
       <c r="J520" s="11" t="n"/>
       <c r="K520" s="11" t="n"/>
-      <c r="L520" s="11" t="n"/>
-      <c r="M520" s="11" t="n"/>
     </row>
     <row r="521" ht="15.75" customHeight="1" s="16">
       <c r="A521" s="4">
@@ -17211,8 +15923,6 @@
       <c r="I521" s="11" t="n"/>
       <c r="J521" s="11" t="n"/>
       <c r="K521" s="11" t="n"/>
-      <c r="L521" s="11" t="n"/>
-      <c r="M521" s="11" t="n"/>
     </row>
     <row r="522" ht="15.75" customHeight="1" s="16">
       <c r="A522" s="4">
@@ -17241,8 +15951,6 @@
       <c r="I522" s="11" t="n"/>
       <c r="J522" s="11" t="n"/>
       <c r="K522" s="11" t="n"/>
-      <c r="L522" s="11" t="n"/>
-      <c r="M522" s="11" t="n"/>
     </row>
     <row r="523" ht="15.75" customHeight="1" s="16">
       <c r="A523" s="4">
@@ -17271,8 +15979,6 @@
       <c r="I523" s="11" t="n"/>
       <c r="J523" s="11" t="n"/>
       <c r="K523" s="11" t="n"/>
-      <c r="L523" s="11" t="n"/>
-      <c r="M523" s="11" t="n"/>
     </row>
     <row r="524" ht="15.75" customHeight="1" s="16">
       <c r="A524" s="4">
@@ -17301,8 +16007,6 @@
       <c r="I524" s="11" t="n"/>
       <c r="J524" s="11" t="n"/>
       <c r="K524" s="11" t="n"/>
-      <c r="L524" s="11" t="n"/>
-      <c r="M524" s="11" t="n"/>
     </row>
     <row r="525" ht="15.75" customHeight="1" s="16">
       <c r="A525" s="4">
@@ -17331,8 +16035,6 @@
       <c r="I525" s="11" t="n"/>
       <c r="J525" s="11" t="n"/>
       <c r="K525" s="11" t="n"/>
-      <c r="L525" s="11" t="n"/>
-      <c r="M525" s="11" t="n"/>
     </row>
     <row r="526" ht="15.75" customHeight="1" s="16">
       <c r="A526" s="4">
@@ -17361,8 +16063,6 @@
       <c r="I526" s="11" t="n"/>
       <c r="J526" s="11" t="n"/>
       <c r="K526" s="11" t="n"/>
-      <c r="L526" s="11" t="n"/>
-      <c r="M526" s="11" t="n"/>
     </row>
     <row r="527" ht="15.75" customHeight="1" s="16">
       <c r="A527" s="4">
@@ -17391,8 +16091,6 @@
       <c r="I527" s="11" t="n"/>
       <c r="J527" s="11" t="n"/>
       <c r="K527" s="11" t="n"/>
-      <c r="L527" s="11" t="n"/>
-      <c r="M527" s="11" t="n"/>
     </row>
     <row r="528" ht="15.75" customHeight="1" s="16">
       <c r="A528" s="4">
@@ -17421,8 +16119,6 @@
       <c r="I528" s="11" t="n"/>
       <c r="J528" s="11" t="n"/>
       <c r="K528" s="11" t="n"/>
-      <c r="L528" s="11" t="n"/>
-      <c r="M528" s="11" t="n"/>
     </row>
     <row r="529" ht="15.75" customHeight="1" s="16">
       <c r="A529" s="4">
@@ -17451,8 +16147,6 @@
       <c r="I529" s="11" t="n"/>
       <c r="J529" s="11" t="n"/>
       <c r="K529" s="11" t="n"/>
-      <c r="L529" s="11" t="n"/>
-      <c r="M529" s="11" t="n"/>
     </row>
     <row r="530" ht="15.75" customHeight="1" s="16">
       <c r="A530" s="4">
@@ -17481,8 +16175,6 @@
       <c r="I530" s="11" t="n"/>
       <c r="J530" s="11" t="n"/>
       <c r="K530" s="11" t="n"/>
-      <c r="L530" s="11" t="n"/>
-      <c r="M530" s="11" t="n"/>
     </row>
     <row r="531" ht="15.75" customHeight="1" s="16">
       <c r="A531" s="4">
@@ -17511,8 +16203,6 @@
       <c r="I531" s="11" t="n"/>
       <c r="J531" s="11" t="n"/>
       <c r="K531" s="11" t="n"/>
-      <c r="L531" s="11" t="n"/>
-      <c r="M531" s="11" t="n"/>
     </row>
     <row r="532" ht="15.75" customHeight="1" s="16">
       <c r="A532" s="4">
@@ -17541,8 +16231,6 @@
       <c r="I532" s="11" t="n"/>
       <c r="J532" s="11" t="n"/>
       <c r="K532" s="11" t="n"/>
-      <c r="L532" s="11" t="n"/>
-      <c r="M532" s="11" t="n"/>
     </row>
     <row r="533" ht="15.75" customHeight="1" s="16">
       <c r="A533" s="4">
@@ -17571,8 +16259,6 @@
       <c r="I533" s="11" t="n"/>
       <c r="J533" s="11" t="n"/>
       <c r="K533" s="11" t="n"/>
-      <c r="L533" s="11" t="n"/>
-      <c r="M533" s="11" t="n"/>
     </row>
     <row r="534" ht="15.75" customHeight="1" s="16">
       <c r="A534" s="4">
@@ -17601,8 +16287,6 @@
       <c r="I534" s="11" t="n"/>
       <c r="J534" s="11" t="n"/>
       <c r="K534" s="11" t="n"/>
-      <c r="L534" s="11" t="n"/>
-      <c r="M534" s="11" t="n"/>
     </row>
     <row r="535" ht="15.75" customHeight="1" s="16">
       <c r="A535" s="4">
@@ -17631,8 +16315,6 @@
       <c r="I535" s="11" t="n"/>
       <c r="J535" s="11" t="n"/>
       <c r="K535" s="11" t="n"/>
-      <c r="L535" s="11" t="n"/>
-      <c r="M535" s="11" t="n"/>
     </row>
     <row r="536" ht="15.75" customHeight="1" s="16">
       <c r="A536" s="4">
@@ -17661,8 +16343,6 @@
       <c r="I536" s="11" t="n"/>
       <c r="J536" s="11" t="n"/>
       <c r="K536" s="11" t="n"/>
-      <c r="L536" s="11" t="n"/>
-      <c r="M536" s="11" t="n"/>
     </row>
     <row r="537" ht="15.75" customHeight="1" s="16">
       <c r="A537" s="4">
@@ -17691,8 +16371,6 @@
       <c r="I537" s="11" t="n"/>
       <c r="J537" s="11" t="n"/>
       <c r="K537" s="11" t="n"/>
-      <c r="L537" s="11" t="n"/>
-      <c r="M537" s="11" t="n"/>
     </row>
     <row r="538" ht="15.75" customHeight="1" s="16">
       <c r="A538" s="4">
@@ -17721,8 +16399,6 @@
       <c r="I538" s="11" t="n"/>
       <c r="J538" s="11" t="n"/>
       <c r="K538" s="11" t="n"/>
-      <c r="L538" s="11" t="n"/>
-      <c r="M538" s="11" t="n"/>
     </row>
     <row r="539" ht="15.75" customHeight="1" s="16">
       <c r="A539" s="4">
@@ -17751,8 +16427,6 @@
       <c r="I539" s="11" t="n"/>
       <c r="J539" s="11" t="n"/>
       <c r="K539" s="11" t="n"/>
-      <c r="L539" s="11" t="n"/>
-      <c r="M539" s="11" t="n"/>
     </row>
     <row r="540" ht="15.75" customHeight="1" s="16">
       <c r="A540" s="4">
@@ -17781,8 +16455,6 @@
       <c r="I540" s="11" t="n"/>
       <c r="J540" s="11" t="n"/>
       <c r="K540" s="11" t="n"/>
-      <c r="L540" s="11" t="n"/>
-      <c r="M540" s="11" t="n"/>
     </row>
     <row r="541" ht="15.75" customHeight="1" s="16">
       <c r="A541" s="4">
@@ -17811,8 +16483,6 @@
       <c r="I541" s="11" t="n"/>
       <c r="J541" s="11" t="n"/>
       <c r="K541" s="11" t="n"/>
-      <c r="L541" s="11" t="n"/>
-      <c r="M541" s="11" t="n"/>
     </row>
     <row r="542" ht="15.75" customHeight="1" s="16">
       <c r="A542" s="4">
@@ -17841,8 +16511,6 @@
       <c r="I542" s="11" t="n"/>
       <c r="J542" s="11" t="n"/>
       <c r="K542" s="11" t="n"/>
-      <c r="L542" s="11" t="n"/>
-      <c r="M542" s="11" t="n"/>
     </row>
     <row r="543" ht="15.75" customHeight="1" s="16">
       <c r="A543" s="4">
@@ -17871,8 +16539,6 @@
       <c r="I543" s="11" t="n"/>
       <c r="J543" s="11" t="n"/>
       <c r="K543" s="11" t="n"/>
-      <c r="L543" s="11" t="n"/>
-      <c r="M543" s="11" t="n"/>
     </row>
     <row r="544" ht="15.75" customHeight="1" s="16">
       <c r="A544" s="4">
@@ -17901,8 +16567,6 @@
       <c r="I544" s="11" t="n"/>
       <c r="J544" s="11" t="n"/>
       <c r="K544" s="11" t="n"/>
-      <c r="L544" s="11" t="n"/>
-      <c r="M544" s="11" t="n"/>
     </row>
     <row r="545" ht="15.75" customHeight="1" s="16">
       <c r="A545" s="4">
@@ -17931,8 +16595,6 @@
       <c r="I545" s="11" t="n"/>
       <c r="J545" s="11" t="n"/>
       <c r="K545" s="11" t="n"/>
-      <c r="L545" s="11" t="n"/>
-      <c r="M545" s="11" t="n"/>
     </row>
     <row r="546" ht="15.75" customHeight="1" s="16">
       <c r="A546" s="4">
@@ -17961,8 +16623,6 @@
       <c r="I546" s="11" t="n"/>
       <c r="J546" s="11" t="n"/>
       <c r="K546" s="11" t="n"/>
-      <c r="L546" s="11" t="n"/>
-      <c r="M546" s="11" t="n"/>
     </row>
     <row r="547" ht="15.75" customHeight="1" s="16">
       <c r="A547" s="4">
@@ -17991,8 +16651,6 @@
       <c r="I547" s="11" t="n"/>
       <c r="J547" s="11" t="n"/>
       <c r="K547" s="11" t="n"/>
-      <c r="L547" s="11" t="n"/>
-      <c r="M547" s="11" t="n"/>
     </row>
     <row r="548" ht="15.75" customHeight="1" s="16">
       <c r="A548" s="4">
@@ -18021,8 +16679,6 @@
       <c r="I548" s="11" t="n"/>
       <c r="J548" s="11" t="n"/>
       <c r="K548" s="11" t="n"/>
-      <c r="L548" s="11" t="n"/>
-      <c r="M548" s="11" t="n"/>
     </row>
     <row r="549" ht="15.75" customHeight="1" s="16">
       <c r="A549" s="4">
@@ -18051,8 +16707,6 @@
       <c r="I549" s="11" t="n"/>
       <c r="J549" s="11" t="n"/>
       <c r="K549" s="11" t="n"/>
-      <c r="L549" s="11" t="n"/>
-      <c r="M549" s="11" t="n"/>
     </row>
     <row r="550" ht="15.75" customHeight="1" s="16">
       <c r="A550" s="4">
@@ -18081,8 +16735,6 @@
       <c r="I550" s="11" t="n"/>
       <c r="J550" s="11" t="n"/>
       <c r="K550" s="11" t="n"/>
-      <c r="L550" s="11" t="n"/>
-      <c r="M550" s="11" t="n"/>
     </row>
     <row r="551" ht="15.75" customHeight="1" s="16">
       <c r="A551" s="4">
@@ -18111,8 +16763,6 @@
       <c r="I551" s="11" t="n"/>
       <c r="J551" s="11" t="n"/>
       <c r="K551" s="11" t="n"/>
-      <c r="L551" s="11" t="n"/>
-      <c r="M551" s="11" t="n"/>
     </row>
     <row r="552" ht="15.75" customHeight="1" s="16">
       <c r="A552" s="4">
@@ -18141,8 +16791,6 @@
       <c r="I552" s="11" t="n"/>
       <c r="J552" s="11" t="n"/>
       <c r="K552" s="11" t="n"/>
-      <c r="L552" s="11" t="n"/>
-      <c r="M552" s="11" t="n"/>
     </row>
     <row r="553" ht="15.75" customHeight="1" s="16">
       <c r="A553" s="4">
@@ -18181,28 +16829,18 @@
       </c>
       <c r="H553" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I553" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J553" s="11" t="inlineStr">
-        <is>
           <t>Ministry posts recruitment/vacancy circulars under 'Tenders &amp; Advertisement'.</t>
         </is>
       </c>
-      <c r="K553" s="17" t="n">
+      <c r="J553" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L553" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M553" s="11" t="inlineStr">
+      <c r="K553" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -18245,28 +16883,18 @@
       </c>
       <c r="H554" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I554" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J554" s="11" t="inlineStr">
-        <is>
           <t>Division staffed via Ministry; vacancies under Ministry's Tenders &amp; Advertisement.</t>
         </is>
       </c>
-      <c r="K554" s="17" t="n">
+      <c r="J554" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L554" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M554" s="11" t="inlineStr">
+      <c r="K554" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -18309,28 +16937,18 @@
       </c>
       <c r="H555" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I555" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J555" s="11" t="inlineStr">
-        <is>
           <t>Division staffed via Ministry; vacancies under Ministry's Tenders &amp; Advertisement.</t>
         </is>
       </c>
-      <c r="K555" s="17" t="n">
+      <c r="J555" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L555" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M555" s="11" t="inlineStr">
+      <c r="K555" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -18373,28 +16991,18 @@
       </c>
       <c r="H556" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I556" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J556" s="11" t="inlineStr">
-        <is>
           <t>EMRS recruitment is conducted by NESTS (own portal), not the Ministry homepage.</t>
         </is>
       </c>
-      <c r="K556" s="17" t="n">
+      <c r="J556" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L556" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M556" s="11" t="inlineStr">
+      <c r="K556" s="11" t="inlineStr">
         <is>
           <t>Portal</t>
         </is>
@@ -18437,28 +17045,18 @@
       </c>
       <c r="H557" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I557" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J557" s="11" t="inlineStr">
-        <is>
           <t>NCST publishes vacancies on its own official site.</t>
         </is>
       </c>
-      <c r="K557" s="17" t="n">
+      <c r="J557" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L557" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M557" s="11" t="inlineStr">
+      <c r="K557" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -18501,28 +17099,18 @@
       </c>
       <c r="H558" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I558" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J558" s="11" t="inlineStr">
-        <is>
           <t>NSTFDC official site; not reachable for deep-link confirmation from here.</t>
         </is>
       </c>
-      <c r="K558" s="17" t="n">
+      <c r="J558" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L558" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M558" s="11" t="inlineStr">
+      <c r="K558" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -18565,28 +17153,18 @@
       </c>
       <c r="H559" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I559" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J559" s="11" t="inlineStr">
-        <is>
           <t>TRIFED publishes its own recruitment (Careers) on its portal.</t>
         </is>
       </c>
-      <c r="K559" s="17" t="n">
+      <c r="J559" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L559" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M559" s="11" t="inlineStr">
+      <c r="K559" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -18629,28 +17207,18 @@
       </c>
       <c r="H560" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I560" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J560" s="11" t="inlineStr">
-        <is>
           <t>NITRT has no separately confirmed recruitment portal; Ministry advertisements used as coordination point.</t>
         </is>
       </c>
-      <c r="K560" s="17" t="n">
+      <c r="J560" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L560" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M560" s="11" t="inlineStr">
+      <c r="K560" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -18693,28 +17261,18 @@
       </c>
       <c r="H561" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I561" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J561" s="11" t="inlineStr">
-        <is>
           <t>EMRS regional/field-unit recruitment via NESTS portal.</t>
         </is>
       </c>
-      <c r="K561" s="17" t="n">
+      <c r="J561" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L561" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M561" s="11" t="inlineStr">
+      <c r="K561" s="11" t="inlineStr">
         <is>
           <t>Portal</t>
         </is>
@@ -18757,28 +17315,18 @@
       </c>
       <c r="H562" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I562" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J562" s="11" t="inlineStr">
-        <is>
           <t>Regional offices staffed via Ministry; vacancies under Ministry advertisements.</t>
         </is>
       </c>
-      <c r="K562" s="17" t="n">
+      <c r="J562" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L562" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M562" s="11" t="inlineStr">
+      <c r="K562" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -18811,8 +17359,6 @@
       <c r="I563" s="11" t="n"/>
       <c r="J563" s="11" t="n"/>
       <c r="K563" s="11" t="n"/>
-      <c r="L563" s="11" t="n"/>
-      <c r="M563" s="11" t="n"/>
     </row>
     <row r="564" ht="15.75" customHeight="1" s="16">
       <c r="A564" s="4">
@@ -18851,28 +17397,18 @@
       </c>
       <c r="H564" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I564" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J564" s="11" t="inlineStr">
-        <is>
           <t>MWCD careers page (not the homepage).</t>
         </is>
       </c>
-      <c r="K564" s="17" t="n">
+      <c r="J564" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L564" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M564" s="11" t="inlineStr">
+      <c r="K564" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -18915,28 +17451,18 @@
       </c>
       <c r="H565" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I565" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J565" s="11" t="inlineStr">
-        <is>
           <t>Division staffed via Ministry; MWCD careers page.</t>
         </is>
       </c>
-      <c r="K565" s="17" t="n">
+      <c r="J565" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L565" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M565" s="11" t="inlineStr">
+      <c r="K565" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -18979,28 +17505,18 @@
       </c>
       <c r="H566" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I566" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J566" s="11" t="inlineStr">
-        <is>
           <t>Division staffed via Ministry; MWCD careers page.</t>
         </is>
       </c>
-      <c r="K566" s="17" t="n">
+      <c r="J566" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L566" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M566" s="11" t="inlineStr">
+      <c r="K566" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -19043,28 +17559,18 @@
       </c>
       <c r="H567" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I567" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J567" s="11" t="inlineStr">
-        <is>
           <t>Division staffed via Ministry; MWCD careers page.</t>
         </is>
       </c>
-      <c r="K567" s="17" t="n">
+      <c r="J567" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L567" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M567" s="11" t="inlineStr">
+      <c r="K567" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -19107,28 +17613,18 @@
       </c>
       <c r="H568" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I568" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J568" s="11" t="inlineStr">
-        <is>
           <t>Division staffed via Ministry; MWCD careers page.</t>
         </is>
       </c>
-      <c r="K568" s="17" t="n">
+      <c r="J568" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L568" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M568" s="11" t="inlineStr">
+      <c r="K568" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -19171,28 +17667,18 @@
       </c>
       <c r="H569" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I569" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J569" s="11" t="inlineStr">
-        <is>
           <t>Division staffed via Ministry; MWCD careers page.</t>
         </is>
       </c>
-      <c r="K569" s="17" t="n">
+      <c r="J569" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L569" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M569" s="11" t="inlineStr">
+      <c r="K569" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -19235,28 +17721,18 @@
       </c>
       <c r="H570" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I570" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J570" s="11" t="inlineStr">
-        <is>
           <t>CARA publishes recruitment on its own site; dedicated deep page not auto-confirmed.</t>
         </is>
       </c>
-      <c r="K570" s="17" t="n">
+      <c r="J570" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L570" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M570" s="11" t="inlineStr">
+      <c r="K570" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -19299,28 +17775,18 @@
       </c>
       <c r="H571" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I571" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J571" s="11" t="inlineStr">
-        <is>
           <t>NCPCR publishes vacancies on its own official site.</t>
         </is>
       </c>
-      <c r="K571" s="17" t="n">
+      <c r="J571" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L571" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M571" s="11" t="inlineStr">
+      <c r="K571" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -19363,28 +17829,18 @@
       </c>
       <c r="H572" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I572" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J572" s="11" t="inlineStr">
-        <is>
           <t>Anganwadi/ICDS posts are recruited at State/District level; Ministry careers page for central coordination only.</t>
         </is>
       </c>
-      <c r="K572" s="17" t="n">
+      <c r="J572" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L572" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M572" s="11" t="inlineStr">
+      <c r="K572" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -19427,28 +17883,18 @@
       </c>
       <c r="H573" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I573" s="11" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J573" s="11" t="inlineStr">
-        <is>
           <t>State/District Mission Directorate posts recruited at State level; central coordination via Ministry.</t>
         </is>
       </c>
-      <c r="K573" s="17" t="n">
+      <c r="J573" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L573" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M573" s="11" t="inlineStr">
+      <c r="K573" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -19491,28 +17937,18 @@
       </c>
       <c r="H574" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I574" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J574" s="11" t="inlineStr">
-        <is>
           <t>National Commission for Women recruitment page.</t>
         </is>
       </c>
-      <c r="K574" s="17" t="n">
+      <c r="J574" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L574" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M574" s="11" t="inlineStr">
+      <c r="K574" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -19555,28 +17991,18 @@
       </c>
       <c r="H575" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I575" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J575" s="11" t="inlineStr">
-        <is>
           <t>NIPCCD is now SPNIWCD; recruitment page confirmed.</t>
         </is>
       </c>
-      <c r="K575" s="17" t="n">
+      <c r="J575" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L575" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M575" s="11" t="inlineStr">
+      <c r="K575" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -19609,8 +18035,6 @@
       <c r="I576" s="11" t="n"/>
       <c r="J576" s="11" t="n"/>
       <c r="K576" s="11" t="n"/>
-      <c r="L576" s="11" t="n"/>
-      <c r="M576" s="11" t="n"/>
     </row>
     <row r="577" ht="15.75" customHeight="1" s="16">
       <c r="A577" s="4">
@@ -19649,28 +18073,18 @@
       </c>
       <c r="H577" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I577" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J577" s="11" t="inlineStr">
-        <is>
           <t>Official Ministry vacancy page (not the homepage).</t>
         </is>
       </c>
-      <c r="K577" s="17" t="n">
+      <c r="J577" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L577" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M577" s="11" t="inlineStr">
+      <c r="K577" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -19713,28 +18127,18 @@
       </c>
       <c r="H578" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I578" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J578" s="11" t="inlineStr">
-        <is>
           <t>Dept of Sports vacancies posted on the Ministry vacancy page.</t>
         </is>
       </c>
-      <c r="K578" s="17" t="n">
+      <c r="J578" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L578" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M578" s="11" t="inlineStr">
+      <c r="K578" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -19777,28 +18181,18 @@
       </c>
       <c r="H579" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I579" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J579" s="11" t="inlineStr">
-        <is>
           <t>NSS Directorate vacancies via Ministry vacancy page.</t>
         </is>
       </c>
-      <c r="K579" s="17" t="n">
+      <c r="J579" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L579" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M579" s="11" t="inlineStr">
+      <c r="K579" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -19841,28 +18235,18 @@
       </c>
       <c r="H580" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I580" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J580" s="11" t="inlineStr">
-        <is>
           <t>Khelo India Division vacancies via Ministry vacancy page.</t>
         </is>
       </c>
-      <c r="K580" s="17" t="n">
+      <c r="J580" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L580" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M580" s="11" t="inlineStr">
+      <c r="K580" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -19905,28 +18289,18 @@
       </c>
       <c r="H581" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I581" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J581" s="11" t="inlineStr">
-        <is>
           <t>NYKS publishes recruitment on its own official site.</t>
         </is>
       </c>
-      <c r="K581" s="17" t="n">
+      <c r="J581" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L581" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M581" s="11" t="inlineStr">
+      <c r="K581" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -19969,28 +18343,18 @@
       </c>
       <c r="H582" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I582" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J582" s="11" t="inlineStr">
-        <is>
           <t>SAI regional/training-centre recruitment via SAI jobs portal.</t>
         </is>
       </c>
-      <c r="K582" s="17" t="n">
+      <c r="J582" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L582" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M582" s="11" t="inlineStr">
+      <c r="K582" s="11" t="inlineStr">
         <is>
           <t>Portal</t>
         </is>
@@ -20033,28 +18397,18 @@
       </c>
       <c r="H583" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I583" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J583" s="11" t="inlineStr">
-        <is>
           <t>Sports Authority of India jobs portal.</t>
         </is>
       </c>
-      <c r="K583" s="17" t="n">
+      <c r="J583" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L583" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M583" s="11" t="inlineStr">
+      <c r="K583" s="11" t="inlineStr">
         <is>
           <t>Portal</t>
         </is>
@@ -20097,28 +18451,18 @@
       </c>
       <c r="H584" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I584" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J584" s="11" t="inlineStr">
-        <is>
           <t>LNIPE official site; deep recruitment link not reachable for confirmation from here.</t>
         </is>
       </c>
-      <c r="K584" s="17" t="n">
+      <c r="J584" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L584" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M584" s="11" t="inlineStr">
+      <c r="K584" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -20161,28 +18505,18 @@
       </c>
       <c r="H585" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I585" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J585" s="11" t="inlineStr">
-        <is>
           <t>NSNIS Patiala is the academic wing of SAI; recruitment via SAI jobs portal.</t>
         </is>
       </c>
-      <c r="K585" s="17" t="n">
+      <c r="J585" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L585" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M585" s="11" t="inlineStr">
+      <c r="K585" s="11" t="inlineStr">
         <is>
           <t>Portal</t>
         </is>
@@ -20225,28 +18559,18 @@
       </c>
       <c r="H586" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I586" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J586" s="11" t="inlineStr">
-        <is>
           <t>NADA India official portal.</t>
         </is>
       </c>
-      <c r="K586" s="17" t="n">
+      <c r="J586" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L586" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M586" s="11" t="inlineStr">
+      <c r="K586" s="11" t="inlineStr">
         <is>
           <t>Portal</t>
         </is>
@@ -20279,8 +18603,6 @@
       <c r="I587" s="11" t="n"/>
       <c r="J587" s="11" t="n"/>
       <c r="K587" s="11" t="n"/>
-      <c r="L587" s="11" t="n"/>
-      <c r="M587" s="11" t="n"/>
     </row>
     <row r="588" ht="15.75" customHeight="1" s="16">
       <c r="A588" s="4">
@@ -20319,28 +18641,18 @@
       </c>
       <c r="H588" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I588" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J588" s="11" t="inlineStr">
-        <is>
           <t>NOTE: domain migrated from dhi.gov.in to heavyindustries.gov.in; recruitment under 'Job Opportunities'.</t>
         </is>
       </c>
-      <c r="K588" s="17" t="n">
+      <c r="J588" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L588" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M588" s="11" t="inlineStr">
+      <c r="K588" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -20383,28 +18695,18 @@
       </c>
       <c r="H589" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I589" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J589" s="11" t="inlineStr">
-        <is>
           <t>Division staffed via Ministry; recruitment on Ministry 'Job Opportunities' page (domain migrated from dhi.gov.in).</t>
         </is>
       </c>
-      <c r="K589" s="17" t="n">
+      <c r="J589" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L589" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M589" s="11" t="inlineStr">
+      <c r="K589" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -20447,28 +18749,18 @@
       </c>
       <c r="H590" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I590" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J590" s="11" t="inlineStr">
-        <is>
           <t>Division staffed via Ministry; recruitment on Ministry 'Job Opportunities' page (domain migrated from dhi.gov.in).</t>
         </is>
       </c>
-      <c r="K590" s="17" t="n">
+      <c r="J590" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L590" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M590" s="11" t="inlineStr">
+      <c r="K590" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -20511,28 +18803,18 @@
       </c>
       <c r="H591" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I591" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J591" s="11" t="inlineStr">
-        <is>
           <t>ARAI Careers page.</t>
         </is>
       </c>
-      <c r="K591" s="17" t="n">
+      <c r="J591" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L591" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M591" s="11" t="inlineStr">
+      <c r="K591" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -20575,28 +18857,18 @@
       </c>
       <c r="H592" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I592" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J592" s="11" t="inlineStr">
-        <is>
           <t>ICAT Careers page.</t>
         </is>
       </c>
-      <c r="K592" s="17" t="n">
+      <c r="J592" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L592" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M592" s="11" t="inlineStr">
+      <c r="K592" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -20639,28 +18911,18 @@
       </c>
       <c r="H593" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I593" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J593" s="11" t="inlineStr">
-        <is>
           <t>CMTI official site; careers page not reachable for confirmation from here.</t>
         </is>
       </c>
-      <c r="K593" s="17" t="n">
+      <c r="J593" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L593" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M593" s="11" t="inlineStr">
+      <c r="K593" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -20703,28 +18965,18 @@
       </c>
       <c r="H594" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I594" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J594" s="11" t="inlineStr">
-        <is>
           <t>BHEL dedicated careers portal.</t>
         </is>
       </c>
-      <c r="K594" s="17" t="n">
+      <c r="J594" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L594" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M594" s="11" t="inlineStr">
+      <c r="K594" s="11" t="inlineStr">
         <is>
           <t>Portal</t>
         </is>
@@ -20767,28 +19019,18 @@
       </c>
       <c r="H595" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I595" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J595" s="11" t="inlineStr">
-        <is>
           <t>HMT careers page (site blocks automated access but verified to exist).</t>
         </is>
       </c>
-      <c r="K595" s="17" t="n">
+      <c r="J595" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L595" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M595" s="11" t="inlineStr">
+      <c r="K595" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -20821,8 +19063,6 @@
       <c r="I596" s="11" t="n"/>
       <c r="J596" s="11" t="n"/>
       <c r="K596" s="11" t="n"/>
-      <c r="L596" s="11" t="n"/>
-      <c r="M596" s="11" t="n"/>
     </row>
     <row r="597" ht="15.75" customHeight="1" s="16">
       <c r="A597" s="4">
@@ -20861,28 +19101,18 @@
       </c>
       <c r="H597" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I597" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J597" s="11" t="inlineStr">
-        <is>
           <t>Ministry of Mines recruitment page (not the homepage).</t>
         </is>
       </c>
-      <c r="K597" s="17" t="n">
+      <c r="J597" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L597" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M597" s="11" t="inlineStr">
+      <c r="K597" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -20925,28 +19155,18 @@
       </c>
       <c r="H598" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I598" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J598" s="11" t="inlineStr">
-        <is>
           <t>Indian Bureau of Mines recruitment page.</t>
         </is>
       </c>
-      <c r="K598" s="17" t="n">
+      <c r="J598" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L598" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M598" s="11" t="inlineStr">
+      <c r="K598" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -20989,28 +19209,18 @@
       </c>
       <c r="H599" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I599" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J599" s="11" t="inlineStr">
-        <is>
           <t>GSI Group-A posts via UPSC Geo-Scientist exam; coordination/deputation via Ministry of Mines recruitment page.</t>
         </is>
       </c>
-      <c r="K599" s="17" t="n">
+      <c r="J599" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L599" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M599" s="11" t="inlineStr">
+      <c r="K599" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -21053,28 +19263,18 @@
       </c>
       <c r="H600" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I600" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J600" s="11" t="inlineStr">
-        <is>
           <t>IBM regional/field-office recruitment via IBM recruitment page.</t>
         </is>
       </c>
-      <c r="K600" s="17" t="n">
+      <c r="J600" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L600" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M600" s="11" t="inlineStr">
+      <c r="K600" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -21117,28 +19317,18 @@
       </c>
       <c r="H601" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I601" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J601" s="11" t="inlineStr">
-        <is>
           <t>NMDC careers page.</t>
         </is>
       </c>
-      <c r="K601" s="17" t="n">
+      <c r="J601" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L601" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M601" s="11" t="inlineStr">
+      <c r="K601" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -21181,28 +19371,18 @@
       </c>
       <c r="H602" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I602" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J602" s="11" t="inlineStr">
-        <is>
           <t>MOIL recruitment listing.</t>
         </is>
       </c>
-      <c r="K602" s="17" t="n">
+      <c r="J602" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L602" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M602" s="11" t="inlineStr">
+      <c r="K602" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -21235,8 +19415,6 @@
       <c r="I603" s="11" t="n"/>
       <c r="J603" s="11" t="n"/>
       <c r="K603" s="11" t="n"/>
-      <c r="L603" s="11" t="n"/>
-      <c r="M603" s="11" t="n"/>
     </row>
     <row r="604" ht="15.75" customHeight="1" s="16">
       <c r="A604" s="4">
@@ -21275,28 +19453,18 @@
       </c>
       <c r="H604" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I604" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J604" s="11" t="inlineStr">
-        <is>
           <t>Ministry of Tourism recruitment page (not the homepage) - shows live vacancy advertisements.</t>
         </is>
       </c>
-      <c r="K604" s="17" t="n">
+      <c r="J604" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L604" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M604" s="11" t="inlineStr">
+      <c r="K604" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -21339,28 +19507,18 @@
       </c>
       <c r="H605" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I605" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J605" s="11" t="inlineStr">
-        <is>
           <t>Division staffed via Ministry; Ministry of Tourism recruitment page.</t>
         </is>
       </c>
-      <c r="K605" s="17" t="n">
+      <c r="J605" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L605" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M605" s="11" t="inlineStr">
+      <c r="K605" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -21403,28 +19561,18 @@
       </c>
       <c r="H606" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I606" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J606" s="11" t="inlineStr">
-        <is>
           <t>Division staffed via Ministry; Ministry of Tourism recruitment page.</t>
         </is>
       </c>
-      <c r="K606" s="17" t="n">
+      <c r="J606" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L606" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M606" s="11" t="inlineStr">
+      <c r="K606" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -21467,28 +19615,18 @@
       </c>
       <c r="H607" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I607" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J607" s="11" t="inlineStr">
-        <is>
           <t>India Tourism Offices staffed via Ministry; Ministry of Tourism recruitment page.</t>
         </is>
       </c>
-      <c r="K607" s="17" t="n">
+      <c r="J607" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L607" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M607" s="11" t="inlineStr">
+      <c r="K607" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -21531,28 +19669,18 @@
       </c>
       <c r="H608" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I608" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J608" s="11" t="inlineStr">
-        <is>
           <t>Individual IHMs recruit separately; NCHMCT coordinates and posts many notices on its recruitments page.</t>
         </is>
       </c>
-      <c r="K608" s="17" t="n">
+      <c r="J608" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L608" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M608" s="11" t="inlineStr">
+      <c r="K608" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -21595,28 +19723,18 @@
       </c>
       <c r="H609" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I609" s="11" t="inlineStr">
         <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J609" s="11" t="inlineStr">
-        <is>
           <t>NCHMCT recruitments page.</t>
         </is>
       </c>
-      <c r="K609" s="17" t="n">
+      <c r="J609" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L609" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M609" s="11" t="inlineStr">
+      <c r="K609" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
@@ -21659,28 +19777,18 @@
       </c>
       <c r="H610" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I610" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J610" s="11" t="inlineStr">
-        <is>
           <t>IITTM posts vacancy advertisements as notifications on its site; Director-level posts also via Ministry of Tourism recruitment page.</t>
         </is>
       </c>
-      <c r="K610" s="17" t="n">
+      <c r="J610" s="17" t="n">
         <v>46183</v>
       </c>
-      <c r="L610" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="M610" s="11" t="inlineStr">
+      <c r="K610" s="11" t="inlineStr">
         <is>
           <t>Website</t>
         </is>

--- a/Master list - Ministries and Departments.xlsx
+++ b/Master list - Ministries and Departments.xlsx
@@ -1031,12 +1031,12 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>https://aiia.gov.in/</t>
+          <t>https://recruitment.ayush.gov.in/</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>https://aiia.gov.in/</t>
+          <t>https://recruitment.ayush.gov.in/</t>
         </is>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="H13" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>AIIA posts recruitment notices on its official site; stable deep recruitment URL not confirmed.</t>
+          <t>AYUSH central recruitment portal (covers AIIA); AIIA also runs aiiarecruitment.org. Replaces homepage.</t>
         </is>
       </c>
       <c r="J13" s="17" t="n">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Portal</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>https://www.nium.in/</t>
+          <t>https://recruitment.ayush.gov.in/</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>https://www.nium.in/</t>
+          <t>https://recruitment.ayush.gov.in/</t>
         </is>
       </c>
       <c r="G15" s="11" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="H15" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>NIUM recruitment notices on official site; dedicated page not auto-confirmed.</t>
+          <t>AYUSH central recruitment portal lists NIUM. Replaces homepage.</t>
         </is>
       </c>
       <c r="J15" s="17" t="n">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="K15" s="11" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Portal</t>
         </is>
       </c>
     </row>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>https://www.nih.nic.in/</t>
+          <t>https://www.nih.ayush.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>https://www.nih.nic.in/</t>
+          <t>https://www.nih.ayush.gov.in/recruitment</t>
         </is>
       </c>
       <c r="G17" s="11" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="H17" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>NIH Kolkata recruitment notices on official site; dedicated page not auto-confirmed.</t>
+          <t>NIH recruitment page; domain migrated nih.nic.in -&gt; nih.ayush.gov.in. Replaces homepage.</t>
         </is>
       </c>
       <c r="J17" s="17" t="n">
@@ -1409,12 +1409,12 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>https://ccrsindia.res.in/</t>
+          <t>https://recruitment.ayush.gov.in/</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>https://ccrsindia.res.in/</t>
+          <t>https://recruitment.ayush.gov.in/</t>
         </is>
       </c>
       <c r="G20" s="11" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
-          <t>Official CCRS domain; site not reachable for deep-link confirmation from here.</t>
+          <t>AYUSH central recruitment portal lists CCRS; walk-ins also on ccrs.ayush.gov.in. Replaces homepage.</t>
         </is>
       </c>
       <c r="J20" s="17" t="n">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="K20" s="11" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Portal</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>https://www.ccrhindia.nic.in/</t>
+          <t>https://recruitment.ayush.gov.in/</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>https://www.ccrhindia.nic.in/</t>
+          <t>https://recruitment.ayush.gov.in/</t>
         </is>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -1483,7 +1483,7 @@
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>Official CCRH domain; deep recruitment link not auto-confirmed.</t>
+          <t>AYUSH central recruitment portal; CCRH also advertises on its own AYUSH site. Replaces homepage.</t>
         </is>
       </c>
       <c r="J21" s="17" t="n">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="K21" s="11" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Portal</t>
         </is>
       </c>
     </row>
@@ -1517,12 +1517,12 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>https://ccryn.gov.in/</t>
+          <t>https://recruitment.ayush.gov.in/</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>https://ccryn.gov.in/</t>
+          <t>https://recruitment.ayush.gov.in/</t>
         </is>
       </c>
       <c r="G22" s="11" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>Official CCRYN domain; deep recruitment link not auto-confirmed.</t>
+          <t>AYUSH central recruitment portal; CCRYN also advertises on ccryn.gov.in. Replaces homepage.</t>
         </is>
       </c>
       <c r="J22" s="17" t="n">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K22" s="11" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Portal</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>https://ncismindia.org/</t>
+          <t>https://www.ncismindia.org/advertisements.php</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>https://ncismindia.org/</t>
+          <t>https://www.ncismindia.org/advertisements.php</t>
         </is>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -1586,12 +1586,12 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>CCIM superseded by NCISM (National Commission for Indian System of Medicine); link points to NCISM.</t>
+          <t>NCISM recruitment advertisements page (replaces homepage).</t>
         </is>
       </c>
       <c r="J23" s="17" t="n">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>https://pcimh.gov.in/</t>
+          <t>https://pcimh.gov.in/index.php/recruitment</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>https://pcimh.gov.in/</t>
+          <t>https://pcimh.gov.in/index.php/recruitment</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>PCIM&amp;H official site; dedicated recruitment page not auto-confirmed.</t>
+          <t>PCIM&amp;H recruitment page (replaces homepage).</t>
         </is>
       </c>
       <c r="J25" s="17" t="n">
@@ -2085,12 +2085,12 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>https://www.pci.nic.in/</t>
+          <t>https://www.pci.gov.in/</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>https://www.pci.nic.in/</t>
+          <t>https://www.pci.gov.in/</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>Pharmacy Council of India official site; deep recruitment link not auto-confirmed.</t>
+          <t>Domain corrected pci.nic.in -&gt; pci.gov.in. Site is a SPA exposing no stable recruitment-route URL; vacancy notices appear within portal. NEEDS MANUAL CONFIRMATION.</t>
         </is>
       </c>
       <c r="J33" s="17" t="n">
@@ -16976,12 +16976,12 @@
       </c>
       <c r="E556" s="11" t="inlineStr">
         <is>
-          <t>https://nests.tribal.gov.in/</t>
+          <t>https://www.emrs.tribal.gov.in/</t>
         </is>
       </c>
       <c r="F556" s="11" t="inlineStr">
         <is>
-          <t>https://nests.tribal.gov.in/</t>
+          <t>https://www.emrs.tribal.gov.in/</t>
         </is>
       </c>
       <c r="G556" s="11" t="inlineStr">
@@ -16996,7 +16996,7 @@
       </c>
       <c r="I556" s="11" t="inlineStr">
         <is>
-          <t>EMRS recruitment is conducted by NESTS (own portal), not the Ministry homepage.</t>
+          <t>Dedicated EMRS recruitment/exam portal (apply/admit-card/results), distinct from NESTS org homepage.</t>
         </is>
       </c>
       <c r="J556" s="17" t="n">

--- a/Master list - Ministries and Departments.xlsx
+++ b/Master list - Ministries and Departments.xlsx
@@ -17030,12 +17030,12 @@
       </c>
       <c r="E557" s="11" t="inlineStr">
         <is>
-          <t>https://ncst.nic.in/</t>
+          <t>https://ncst.nic.in/recruitments-vacancies</t>
         </is>
       </c>
       <c r="F557" s="11" t="inlineStr">
         <is>
-          <t>https://ncst.nic.in/</t>
+          <t>https://ncst.nic.in/recruitments-vacancies</t>
         </is>
       </c>
       <c r="G557" s="11" t="inlineStr">
@@ -17045,12 +17045,12 @@
       </c>
       <c r="H557" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I557" s="11" t="inlineStr">
         <is>
-          <t>NCST publishes vacancies on its own official site.</t>
+          <t>NCST recruitments &amp; vacancies page (replaces homepage).</t>
         </is>
       </c>
       <c r="J557" s="17" t="n">
@@ -17099,12 +17099,12 @@
       </c>
       <c r="H558" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I558" s="11" t="inlineStr">
         <is>
-          <t>NSTFDC official site; not reachable for deep-link confirmation from here.</t>
+          <t>NSTFDC site unreachable for deep-link confirmation from sandbox; recruitment notices are on the official site. NEEDS MANUAL CONFIRMATION.</t>
         </is>
       </c>
       <c r="J558" s="17" t="n">
@@ -17138,12 +17138,12 @@
       </c>
       <c r="E559" s="11" t="inlineStr">
         <is>
-          <t>https://trifed.tribal.gov.in/</t>
+          <t>https://trifed.tribal.gov.in/careers-list</t>
         </is>
       </c>
       <c r="F559" s="11" t="inlineStr">
         <is>
-          <t>https://trifed.tribal.gov.in/</t>
+          <t>https://trifed.tribal.gov.in/careers-list</t>
         </is>
       </c>
       <c r="G559" s="11" t="inlineStr">
@@ -17158,7 +17158,7 @@
       </c>
       <c r="I559" s="11" t="inlineStr">
         <is>
-          <t>TRIFED publishes its own recruitment (Careers) on its portal.</t>
+          <t>TRIFED careers list page (replaces homepage).</t>
         </is>
       </c>
       <c r="J559" s="17" t="n">
@@ -17246,12 +17246,12 @@
       </c>
       <c r="E561" s="11" t="inlineStr">
         <is>
-          <t>https://nests.tribal.gov.in/</t>
+          <t>https://www.emrs.tribal.gov.in/</t>
         </is>
       </c>
       <c r="F561" s="11" t="inlineStr">
         <is>
-          <t>https://nests.tribal.gov.in/</t>
+          <t>https://www.emrs.tribal.gov.in/</t>
         </is>
       </c>
       <c r="G561" s="11" t="inlineStr">
@@ -17266,7 +17266,7 @@
       </c>
       <c r="I561" s="11" t="inlineStr">
         <is>
-          <t>EMRS regional/field-unit recruitment via NESTS portal.</t>
+          <t>Dedicated EMRS recruitment/exam portal (apply/admit-card/results), distinct from NESTS org homepage.</t>
         </is>
       </c>
       <c r="J561" s="17" t="n">
@@ -17726,7 +17726,7 @@
       </c>
       <c r="I570" s="11" t="inlineStr">
         <is>
-          <t>CARA publishes recruitment on its own site; dedicated deep page not auto-confirmed.</t>
+          <t>CARA landing page surfaces current recruitment/deputation vacancy notices (PDFs); no separate recruitment route found. Flag for manual deep-link.</t>
         </is>
       </c>
       <c r="J570" s="17" t="n">
@@ -17760,12 +17760,12 @@
       </c>
       <c r="E571" s="11" t="inlineStr">
         <is>
-          <t>https://ncpcr.gov.in/</t>
+          <t>https://ncpcr.gov.in/index.php/recruitment</t>
         </is>
       </c>
       <c r="F571" s="11" t="inlineStr">
         <is>
-          <t>https://ncpcr.gov.in/</t>
+          <t>https://ncpcr.gov.in/index.php/recruitment</t>
         </is>
       </c>
       <c r="G571" s="11" t="inlineStr">
@@ -17775,12 +17775,12 @@
       </c>
       <c r="H571" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I571" s="11" t="inlineStr">
         <is>
-          <t>NCPCR publishes vacancies on its own official site.</t>
+          <t>NCPCR recruitment page (replaces homepage).</t>
         </is>
       </c>
       <c r="J571" s="17" t="n">
@@ -18274,12 +18274,12 @@
       </c>
       <c r="E581" s="11" t="inlineStr">
         <is>
-          <t>https://nyks.nic.in/</t>
+          <t>https://nyks.nic.in/resources/vacanciesNO.aspx</t>
         </is>
       </c>
       <c r="F581" s="11" t="inlineStr">
         <is>
-          <t>https://nyks.nic.in/</t>
+          <t>https://nyks.nic.in/resources/vacanciesNO.aspx</t>
         </is>
       </c>
       <c r="G581" s="11" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="H581" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I581" s="11" t="inlineStr">
         <is>
-          <t>NYKS publishes recruitment on its own official site.</t>
+          <t>NYKS vacancies page (replaces homepage).</t>
         </is>
       </c>
       <c r="J581" s="17" t="n">
@@ -18436,12 +18436,12 @@
       </c>
       <c r="E584" s="11" t="inlineStr">
         <is>
-          <t>https://www.lnipe.gov.in/</t>
+          <t>https://www.lnipe.in/</t>
         </is>
       </c>
       <c r="F584" s="11" t="inlineStr">
         <is>
-          <t>https://www.lnipe.gov.in/</t>
+          <t>https://www.lnipe.in/</t>
         </is>
       </c>
       <c r="G584" s="11" t="inlineStr">
@@ -18456,7 +18456,7 @@
       </c>
       <c r="I584" s="11" t="inlineStr">
         <is>
-          <t>LNIPE official site; deep recruitment link not reachable for confirmation from here.</t>
+          <t>Dedicated LNIPE recruitment/online-application portal; main institute site is lnipe.gov.in.</t>
         </is>
       </c>
       <c r="J584" s="17" t="n">
@@ -18464,7 +18464,7 @@
       </c>
       <c r="K584" s="11" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Portal</t>
         </is>
       </c>
     </row>
@@ -18559,12 +18559,12 @@
       </c>
       <c r="H586" s="11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I586" s="11" t="inlineStr">
         <is>
-          <t>NADA India official portal.</t>
+          <t>NADA recruitment posted on its official site (apply online via nadaindia.yas.gov.in); SPA prevented deep-link confirmation. Flag for manual deep-link.</t>
         </is>
       </c>
       <c r="J586" s="17" t="n">
@@ -18572,7 +18572,7 @@
       </c>
       <c r="K586" s="11" t="inlineStr">
         <is>
-          <t>Portal</t>
+          <t>Website</t>
         </is>
       </c>
     </row>
@@ -18896,12 +18896,12 @@
       </c>
       <c r="E593" s="11" t="inlineStr">
         <is>
-          <t>https://cmti.res.in/</t>
+          <t>https://cmti.res.in/career/</t>
         </is>
       </c>
       <c r="F593" s="11" t="inlineStr">
         <is>
-          <t>https://cmti.res.in/</t>
+          <t>https://cmti.res.in/career/</t>
         </is>
       </c>
       <c r="G593" s="11" t="inlineStr">
@@ -18911,12 +18911,12 @@
       </c>
       <c r="H593" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I593" s="11" t="inlineStr">
         <is>
-          <t>CMTI official site; careers page not reachable for confirmation from here.</t>
+          <t>CMTI Careers page (replaces homepage); active walk-in recruitment notices listed.</t>
         </is>
       </c>
       <c r="J593" s="17" t="n">
@@ -19762,12 +19762,12 @@
       </c>
       <c r="E610" s="11" t="inlineStr">
         <is>
-          <t>https://www.iittm.ac.in/</t>
+          <t>https://www.iittm.ac.in/Recruitment.html</t>
         </is>
       </c>
       <c r="F610" s="11" t="inlineStr">
         <is>
-          <t>https://www.iittm.ac.in/</t>
+          <t>https://www.iittm.ac.in/Recruitment.html</t>
         </is>
       </c>
       <c r="G610" s="11" t="inlineStr">
@@ -19777,12 +19777,12 @@
       </c>
       <c r="H610" s="11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I610" s="11" t="inlineStr">
         <is>
-          <t>IITTM posts vacancy advertisements as notifications on its site; Director-level posts also via Ministry of Tourism recruitment page.</t>
+          <t>IITTM recruitment page (replaces homepage); Director-level posts also advertised via tourism.gov.in/recruitment.</t>
         </is>
       </c>
       <c r="J610" s="17" t="n">

--- a/Master list - Ministries and Departments.xlsx
+++ b/Master list - Ministries and Departments.xlsx
@@ -2105,7 +2105,7 @@
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>Domain corrected pci.nic.in -&gt; pci.gov.in. Site is a SPA exposing no stable recruitment-route URL; vacancy notices appear within portal. NEEDS MANUAL CONFIRMATION.</t>
+          <t>Second pass: no stable recruitment-route URL found (pci.gov.in is a SPA; old pci.nic.in unreachable). Recruitment notices appear within the portal. STILL NEEDS MANUAL CONFIRMATION.</t>
         </is>
       </c>
       <c r="J33" s="17" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="I558" s="11" t="inlineStr">
         <is>
-          <t>NSTFDC site unreachable for deep-link confirmation from sandbox; recruitment notices are on the official site. NEEDS MANUAL CONFIRMATION.</t>
+          <t>Second pass: nstfdc.in unreachable from sandbox and not indexed for a recruitment route. Recruitment notices are on the official site. STILL NEEDS MANUAL CONFIRMATION.</t>
         </is>
       </c>
       <c r="J558" s="17" t="n">
@@ -17706,12 +17706,12 @@
       </c>
       <c r="E570" s="11" t="inlineStr">
         <is>
-          <t>https://cara.wcd.gov.in/</t>
+          <t>https://cara.wcd.gov.in/resource/Archive.html</t>
         </is>
       </c>
       <c r="F570" s="11" t="inlineStr">
         <is>
-          <t>https://cara.wcd.gov.in/</t>
+          <t>https://cara.wcd.gov.in/resource/Archive.html</t>
         </is>
       </c>
       <c r="G570" s="11" t="inlineStr">
@@ -17726,7 +17726,7 @@
       </c>
       <c r="I570" s="11" t="inlineStr">
         <is>
-          <t>CARA landing page surfaces current recruitment/deputation vacancy notices (PDFs); no separate recruitment route found. Flag for manual deep-link.</t>
+          <t>CARA recruitment listing page (posts open for application); replaces homepage. Confirmed live.</t>
         </is>
       </c>
       <c r="J570" s="17" t="n">
@@ -18544,12 +18544,12 @@
       </c>
       <c r="E586" s="11" t="inlineStr">
         <is>
-          <t>https://nadaindia.yas.gov.in/</t>
+          <t>https://nadaindia.yas.gov.in/career-opportunities/</t>
         </is>
       </c>
       <c r="F586" s="11" t="inlineStr">
         <is>
-          <t>https://nadaindia.yas.gov.in/</t>
+          <t>https://nadaindia.yas.gov.in/career-opportunities/</t>
         </is>
       </c>
       <c r="G586" s="11" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="I586" s="11" t="inlineStr">
         <is>
-          <t>NADA recruitment posted on its official site (apply online via nadaindia.yas.gov.in); SPA prevented deep-link confirmation. Flag for manual deep-link.</t>
+          <t>NADA 'Career Opportunities' page (per official site navigation). Domain network-blocked from sandbox, so slug is evidence-based, not curl-verified.</t>
         </is>
       </c>
       <c r="J586" s="17" t="n">

--- a/Master list - Ministries and Departments.xlsx
+++ b/Master list - Ministries and Departments.xlsx
@@ -17,9 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="dd-mm-yyyy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -2191,13 +2192,39 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E35" s="11" t="n"/>
-      <c r="F35" s="11" t="n"/>
-      <c r="G35" s="11" t="n"/>
-      <c r="H35" s="11" t="n"/>
-      <c r="I35" s="11" t="n"/>
-      <c r="J35" s="11" t="n"/>
-      <c r="K35" s="11" t="n"/>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>https://www.niper.gov.in/jobs</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>https://www.niper.gov.in/jobs</t>
+        </is>
+      </c>
+      <c r="G35" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H35" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I35" s="11" t="inlineStr">
+        <is>
+          <t>NIPER jobs page (NIPER Mohali; sister NIPER campuses recruit on their own institute sites).</t>
+        </is>
+      </c>
+      <c r="J35" s="17" t="n">
+        <v>46183</v>
+      </c>
+      <c r="K35" s="11" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="16">
       <c r="A36" s="4">
@@ -2247,13 +2274,39 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="n"/>
-      <c r="G37" s="11" t="n"/>
-      <c r="H37" s="11" t="n"/>
-      <c r="I37" s="11" t="n"/>
-      <c r="J37" s="11" t="n"/>
-      <c r="K37" s="11" t="n"/>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>https://www.civilaviation.gov.in/aviation-jobs</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>https://www.civilaviation.gov.in/aviation-jobs</t>
+        </is>
+      </c>
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I37" s="11" t="inlineStr">
+        <is>
+          <t>Ministry of Civil Aviation 'Aviation Jobs' page.</t>
+        </is>
+      </c>
+      <c r="J37" s="17" t="n">
+        <v>46183</v>
+      </c>
+      <c r="K37" s="11" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="16">
       <c r="A38" s="4">
@@ -2275,13 +2328,39 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E38" s="11" t="n"/>
-      <c r="F38" s="11" t="n"/>
-      <c r="G38" s="11" t="n"/>
-      <c r="H38" s="11" t="n"/>
-      <c r="I38" s="11" t="n"/>
-      <c r="J38" s="11" t="n"/>
-      <c r="K38" s="11" t="n"/>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>https://www.dgca.gov.in/digigov-portal/?page=jsp/dgca/homePage/instructions/RECRUITMENT.html</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>https://www.dgca.gov.in/digigov-portal/?page=jsp/dgca/homePage/instructions/RECRUITMENT.html</t>
+        </is>
+      </c>
+      <c r="G38" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>DGCA recruitment page.</t>
+        </is>
+      </c>
+      <c r="J38" s="17" t="n">
+        <v>46183</v>
+      </c>
+      <c r="K38" s="11" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="16">
       <c r="A39" s="4">
@@ -2303,13 +2382,39 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="11" t="n"/>
-      <c r="G39" s="11" t="n"/>
-      <c r="H39" s="11" t="n"/>
-      <c r="I39" s="11" t="n"/>
-      <c r="J39" s="11" t="n"/>
-      <c r="K39" s="11" t="n"/>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>https://www.civilaviation.gov.in/aviation-jobs</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr">
+        <is>
+          <t>https://www.civilaviation.gov.in/aviation-jobs</t>
+        </is>
+      </c>
+      <c r="G39" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H39" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>BCAS vacancies aggregated on MoCA Aviation Jobs page; BCAS recruits largely by deputation. Own site bcasindia.gov.in is a SPA with no dedicated recruitment route.</t>
+        </is>
+      </c>
+      <c r="J39" s="17" t="n">
+        <v>46183</v>
+      </c>
+      <c r="K39" s="11" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="16">
       <c r="A40" s="4">
@@ -2331,13 +2436,39 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="11" t="n"/>
-      <c r="G40" s="11" t="n"/>
-      <c r="H40" s="11" t="n"/>
-      <c r="I40" s="11" t="n"/>
-      <c r="J40" s="11" t="n"/>
-      <c r="K40" s="11" t="n"/>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>https://aaib.gov.in/</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr">
+        <is>
+          <t>https://aaib.gov.in/</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H40" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="inlineStr">
+        <is>
+          <t>AAIB posts vacancy circulars on its homepage (What's New); no dedicated recruitment route found. Flag for manual deep-link.</t>
+        </is>
+      </c>
+      <c r="J40" s="17" t="n">
+        <v>46183</v>
+      </c>
+      <c r="K40" s="11" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="16">
       <c r="A41" s="4">
@@ -2359,13 +2490,39 @@
           <t>Statutory Body</t>
         </is>
       </c>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="11" t="n"/>
-      <c r="G41" s="11" t="n"/>
-      <c r="H41" s="11" t="n"/>
-      <c r="I41" s="11" t="n"/>
-      <c r="J41" s="11" t="n"/>
-      <c r="K41" s="11" t="n"/>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>https://www.aai.aero/en/careers</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr">
+        <is>
+          <t>https://www.aai.aero/en/careers</t>
+        </is>
+      </c>
+      <c r="G41" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H41" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="inlineStr">
+        <is>
+          <t>Airports Authority of India careers section.</t>
+        </is>
+      </c>
+      <c r="J41" s="17" t="n">
+        <v>46183</v>
+      </c>
+      <c r="K41" s="11" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="16">
       <c r="A42" s="4">
@@ -2387,13 +2544,39 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="11" t="n"/>
-      <c r="G42" s="11" t="n"/>
-      <c r="H42" s="11" t="n"/>
-      <c r="I42" s="11" t="n"/>
-      <c r="J42" s="11" t="n"/>
-      <c r="K42" s="11" t="n"/>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>https://www.igrua.gov.in/careers</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr">
+        <is>
+          <t>https://www.igrua.gov.in/careers</t>
+        </is>
+      </c>
+      <c r="G42" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H42" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="inlineStr">
+        <is>
+          <t>IGRUA careers page.</t>
+        </is>
+      </c>
+      <c r="J42" s="17" t="n">
+        <v>46183</v>
+      </c>
+      <c r="K42" s="11" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="16">
       <c r="A43" s="4">
@@ -2415,13 +2598,39 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="11" t="n"/>
-      <c r="G43" s="11" t="n"/>
-      <c r="H43" s="11" t="n"/>
-      <c r="I43" s="11" t="n"/>
-      <c r="J43" s="11" t="n"/>
-      <c r="K43" s="11" t="n"/>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>https://www.rgnau.ac.in/en/careers.html</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr">
+        <is>
+          <t>https://www.rgnau.ac.in/en/careers.html</t>
+        </is>
+      </c>
+      <c r="G43" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="inlineStr">
+        <is>
+          <t>RGNAU careers page.</t>
+        </is>
+      </c>
+      <c r="J43" s="17" t="n">
+        <v>46183</v>
+      </c>
+      <c r="K43" s="11" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="16">
       <c r="A44" s="4">
@@ -2443,13 +2652,39 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="11" t="n"/>
-      <c r="G44" s="11" t="n"/>
-      <c r="H44" s="11" t="n"/>
-      <c r="I44" s="11" t="n"/>
-      <c r="J44" s="11" t="n"/>
-      <c r="K44" s="11" t="n"/>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>https://www.dgca.gov.in/digigov-portal/?page=jsp/dgca/homePage/instructions/RECRUITMENT.html</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr">
+        <is>
+          <t>https://www.dgca.gov.in/digigov-portal/?page=jsp/dgca/homePage/instructions/RECRUITMENT.html</t>
+        </is>
+      </c>
+      <c r="G44" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="inlineStr">
+        <is>
+          <t>DGCA Regional Airworthiness field units; recruitment via DGCA recruitment page.</t>
+        </is>
+      </c>
+      <c r="J44" s="17" t="n">
+        <v>46183</v>
+      </c>
+      <c r="K44" s="11" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="16">
       <c r="A45" s="4">
@@ -2499,13 +2734,39 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E46" s="11" t="n"/>
-      <c r="F46" s="11" t="n"/>
-      <c r="G46" s="11" t="n"/>
-      <c r="H46" s="11" t="n"/>
-      <c r="I46" s="11" t="n"/>
-      <c r="J46" s="11" t="n"/>
-      <c r="K46" s="11" t="n"/>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>https://coal.gov.in/public-information/advertisements</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr">
+        <is>
+          <t>https://coal.gov.in/public-information/advertisements</t>
+        </is>
+      </c>
+      <c r="G46" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H46" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>Ministry of Coal advertisements (incl. recruitment/vacancy circulars).</t>
+        </is>
+      </c>
+      <c r="J46" s="17" t="n">
+        <v>46183</v>
+      </c>
+      <c r="K46" s="11" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="16">
       <c r="A47" s="4">
@@ -2527,13 +2788,39 @@
           <t>Attached Office</t>
         </is>
       </c>
-      <c r="E47" s="11" t="n"/>
-      <c r="F47" s="11" t="n"/>
-      <c r="G47" s="11" t="n"/>
-      <c r="H47" s="11" t="n"/>
-      <c r="I47" s="11" t="n"/>
-      <c r="J47" s="11" t="n"/>
-      <c r="K47" s="11" t="n"/>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coalcontroller.gov.in/recruitment</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coalcontroller.gov.in/recruitment</t>
+        </is>
+      </c>
+      <c r="G47" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H47" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I47" s="11" t="inlineStr">
+        <is>
+          <t>Coal Controller Organisation recruitment page.</t>
+        </is>
+      </c>
+      <c r="J47" s="17" t="n">
+        <v>46183</v>
+      </c>
+      <c r="K47" s="11" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="16">
       <c r="A48" s="4">
@@ -2555,13 +2842,39 @@
           <t>Subordinate Office</t>
         </is>
       </c>
-      <c r="E48" s="11" t="n"/>
-      <c r="F48" s="11" t="n"/>
-      <c r="G48" s="11" t="n"/>
-      <c r="H48" s="11" t="n"/>
-      <c r="I48" s="11" t="n"/>
-      <c r="J48" s="11" t="n"/>
-      <c r="K48" s="11" t="n"/>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coalcontroller.gov.in/recruitment</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coalcontroller.gov.in/recruitment</t>
+        </is>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H48" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I48" s="11" t="inlineStr">
+        <is>
+          <t>Coal Controller's field offices; recruitment via Coal Controller Organisation.</t>
+        </is>
+      </c>
+      <c r="J48" s="17" t="n">
+        <v>46183</v>
+      </c>
+      <c r="K48" s="11" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="16">
       <c r="A49" s="4">
@@ -2583,13 +2896,39 @@
           <t>Autonomous Body</t>
         </is>
       </c>
-      <c r="E49" s="11" t="n"/>
-      <c r="F49" s="11" t="n"/>
-      <c r="G49" s="11" t="n"/>
-      <c r="H49" s="11" t="n"/>
-      <c r="I49" s="11" t="n"/>
-      <c r="J49" s="11" t="n"/>
-      <c r="K49" s="11" t="n"/>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>https://nioh.org/recruitments/</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr">
+        <is>
+          <t>https://nioh.org/recruitments/</t>
+        </is>
+      </c>
+      <c r="G49" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H49" s="11" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>NIMH merged with NIOH (ICMR) in 2019; recruitment via NIOH recruitments page.</t>
+        </is>
+      </c>
+      <c r="J49" s="17" t="n">
+        <v>46183</v>
+      </c>
+      <c r="K49" s="11" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="16">
       <c r="A50" s="4">
@@ -2611,13 +2950,39 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E50" s="11" t="n"/>
-      <c r="F50" s="11" t="n"/>
-      <c r="G50" s="11" t="n"/>
-      <c r="H50" s="11" t="n"/>
-      <c r="I50" s="11" t="n"/>
-      <c r="J50" s="11" t="n"/>
-      <c r="K50" s="11" t="n"/>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coalindia.in/career-cil/</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr">
+        <is>
+          <t>https://www.coalindia.in/career-cil/</t>
+        </is>
+      </c>
+      <c r="G50" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H50" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>Coal India Limited careers page.</t>
+        </is>
+      </c>
+      <c r="J50" s="17" t="n">
+        <v>46183</v>
+      </c>
+      <c r="K50" s="11" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="16">
       <c r="A51" s="4">
@@ -2639,13 +3004,39 @@
           <t>PSU / Board / Trust</t>
         </is>
       </c>
-      <c r="E51" s="11" t="n"/>
-      <c r="F51" s="11" t="n"/>
-      <c r="G51" s="11" t="n"/>
-      <c r="H51" s="11" t="n"/>
-      <c r="I51" s="11" t="n"/>
-      <c r="J51" s="11" t="n"/>
-      <c r="K51" s="11" t="n"/>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>https://www.scclmines.com/scclnew/careers.asp</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr">
+        <is>
+          <t>https://www.scclmines.com/scclnew/careersDep.asp</t>
+        </is>
+      </c>
+      <c r="G51" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H51" s="11" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>SCCL careers page; deputation vacancies are on a SEPARATE page (careersDep.asp).</t>
+        </is>
+      </c>
+      <c r="J51" s="17" t="n">
+        <v>46183</v>
+      </c>
+      <c r="K51" s="11" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="16">
       <c r="A52" s="4">
